--- a/output/2024-07-06.xlsx
+++ b/output/2024-07-06.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.47</v>
+        <v>3.57</v>
       </c>
       <c r="F14" t="n">
-        <v>10.03</v>
+        <v>10.68</v>
       </c>
       <c r="G14" t="n">
-        <v>290.8</v>
+        <v>287.1</v>
       </c>
       <c r="H14" t="n">
-        <v>39.1</v>
+        <v>44.4</v>
       </c>
       <c r="I14" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-80.06</v>
+        <v>-159.66</v>
       </c>
       <c r="K14" t="n">
-        <v>222.02</v>
+        <v>61.15</v>
       </c>
       <c r="L14" t="n">
-        <v>236.01</v>
+        <v>170.97</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:41:25</t>
+          <t>04:41:11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.8</v>
+        <v>3.73</v>
       </c>
       <c r="F15" t="n">
-        <v>11.08</v>
+        <v>11.23</v>
       </c>
       <c r="G15" t="n">
-        <v>282.2</v>
+        <v>283.8</v>
       </c>
       <c r="H15" t="n">
-        <v>40.5</v>
+        <v>44</v>
       </c>
       <c r="I15" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J15" t="n">
-        <v>60.29</v>
+        <v>-151.3</v>
       </c>
       <c r="K15" t="n">
-        <v>-77.23999999999999</v>
+        <v>-42.92</v>
       </c>
       <c r="L15" t="n">
-        <v>97.98999999999999</v>
+        <v>157.27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:43:06</t>
+          <t>04:43:16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="F16" t="n">
-        <v>11.38</v>
+        <v>10.12</v>
       </c>
       <c r="G16" t="n">
-        <v>279.1</v>
+        <v>275.9</v>
       </c>
       <c r="H16" t="n">
-        <v>41.8</v>
+        <v>39.4</v>
       </c>
       <c r="I16" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>208.51</v>
+        <v>-79.36</v>
       </c>
       <c r="K16" t="n">
-        <v>272.86</v>
+        <v>404.78</v>
       </c>
       <c r="L16" t="n">
-        <v>343.41</v>
+        <v>412.48</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:47:56</t>
+          <t>04:47:23</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.8</v>
+        <v>3.52</v>
       </c>
       <c r="F17" t="n">
-        <v>11.27</v>
+        <v>11.21</v>
       </c>
       <c r="G17" t="n">
-        <v>283.3</v>
+        <v>282.7</v>
       </c>
       <c r="H17" t="n">
-        <v>45.2</v>
+        <v>36</v>
       </c>
       <c r="I17" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="J17" t="n">
-        <v>-50.43</v>
+        <v>106.02</v>
       </c>
       <c r="K17" t="n">
-        <v>-93.83</v>
+        <v>109.98</v>
       </c>
       <c r="L17" t="n">
-        <v>106.52</v>
+        <v>152.76</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:49:51</t>
+          <t>04:48:34</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.37</v>
+        <v>3.99</v>
       </c>
       <c r="F18" t="n">
-        <v>10.94</v>
+        <v>10.97</v>
       </c>
       <c r="G18" t="n">
-        <v>278.7</v>
+        <v>280.2</v>
       </c>
       <c r="H18" t="n">
-        <v>38.4</v>
+        <v>35.4</v>
       </c>
       <c r="I18" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>-117.1</v>
+        <v>34.74</v>
       </c>
       <c r="K18" t="n">
-        <v>111.47</v>
+        <v>-25.31</v>
       </c>
       <c r="L18" t="n">
-        <v>161.68</v>
+        <v>42.98</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:50:56</t>
+          <t>04:50:22</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.76</v>
+        <v>3.34</v>
       </c>
       <c r="F19" t="n">
-        <v>10.68</v>
+        <v>11.31</v>
       </c>
       <c r="G19" t="n">
-        <v>276.6</v>
+        <v>282.6</v>
       </c>
       <c r="H19" t="n">
-        <v>37.2</v>
+        <v>47.8</v>
       </c>
       <c r="I19" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>213.04</v>
+        <v>-248.17</v>
       </c>
       <c r="K19" t="n">
-        <v>166.52</v>
+        <v>88.34</v>
       </c>
       <c r="L19" t="n">
-        <v>270.4</v>
+        <v>263.42</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:54:59</t>
+          <t>04:56:34</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>4.49</v>
+        <v>3.59</v>
       </c>
       <c r="F20" t="n">
-        <v>11.23</v>
+        <v>11.33</v>
       </c>
       <c r="G20" t="n">
-        <v>276.9</v>
+        <v>281.4</v>
       </c>
       <c r="H20" t="n">
-        <v>42.3</v>
+        <v>35.9</v>
       </c>
       <c r="I20" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-319.06</v>
+        <v>315.62</v>
       </c>
       <c r="K20" t="n">
-        <v>124.03</v>
+        <v>367.37</v>
       </c>
       <c r="L20" t="n">
-        <v>342.32</v>
+        <v>484.33</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:57:32</t>
+          <t>04:58:04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.51</v>
+        <v>3.11</v>
       </c>
       <c r="F21" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="G21" t="n">
-        <v>290.8</v>
+        <v>275.3</v>
       </c>
       <c r="H21" t="n">
-        <v>42.2</v>
+        <v>42.6</v>
       </c>
       <c r="I21" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J21" t="n">
-        <v>21.68</v>
+        <v>53.15</v>
       </c>
       <c r="K21" t="n">
-        <v>-41.02</v>
+        <v>-256.46</v>
       </c>
       <c r="L21" t="n">
-        <v>46.4</v>
+        <v>261.91</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:59:16</t>
+          <t>05:00:35</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.74</v>
+        <v>3.39</v>
       </c>
       <c r="F22" t="n">
-        <v>9.890000000000001</v>
+        <v>10.58</v>
       </c>
       <c r="G22" t="n">
-        <v>269.7</v>
+        <v>280.6</v>
       </c>
       <c r="H22" t="n">
-        <v>41.6</v>
+        <v>44.9</v>
       </c>
       <c r="I22" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>-755.63</v>
+        <v>175.2</v>
       </c>
       <c r="K22" t="n">
-        <v>-214.85</v>
+        <v>-145</v>
       </c>
       <c r="L22" t="n">
-        <v>785.58</v>
+        <v>227.42</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:03:34</t>
+          <t>05:05:54</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.78</v>
+        <v>3.45</v>
       </c>
       <c r="F23" t="n">
-        <v>11.31</v>
+        <v>10.42</v>
       </c>
       <c r="G23" t="n">
-        <v>284.9</v>
+        <v>278.9</v>
       </c>
       <c r="H23" t="n">
-        <v>45.7</v>
+        <v>36.3</v>
       </c>
       <c r="I23" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>277.73</v>
+        <v>-92.84</v>
       </c>
       <c r="K23" t="n">
-        <v>-121.97</v>
+        <v>559.02</v>
       </c>
       <c r="L23" t="n">
-        <v>303.33</v>
+        <v>566.6799999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:05:24</t>
+          <t>05:07:09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.57</v>
+        <v>3.26</v>
       </c>
       <c r="F24" t="n">
-        <v>10.63</v>
+        <v>10.94</v>
       </c>
       <c r="G24" t="n">
-        <v>272.1</v>
+        <v>272.6</v>
       </c>
       <c r="H24" t="n">
-        <v>34.2</v>
+        <v>40.8</v>
       </c>
       <c r="I24" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>-273.44</v>
+        <v>-6.23</v>
       </c>
       <c r="K24" t="n">
-        <v>-276.2</v>
+        <v>364.33</v>
       </c>
       <c r="L24" t="n">
-        <v>388.66</v>
+        <v>364.38</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:06:57</t>
+          <t>05:09:21</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>4.04</v>
+        <v>3.1</v>
       </c>
       <c r="F25" t="n">
-        <v>11.52</v>
+        <v>11.39</v>
       </c>
       <c r="G25" t="n">
-        <v>283.1</v>
+        <v>285.1</v>
       </c>
       <c r="H25" t="n">
-        <v>32.7</v>
+        <v>43.7</v>
       </c>
       <c r="I25" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>-541.25</v>
+        <v>156.75</v>
       </c>
       <c r="K25" t="n">
-        <v>-282.53</v>
+        <v>250.35</v>
       </c>
       <c r="L25" t="n">
-        <v>610.55</v>
+        <v>295.37</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:12:39</t>
+          <t>05:13:25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.54</v>
+        <v>3.65</v>
       </c>
       <c r="F26" t="n">
-        <v>10.33</v>
+        <v>11.05</v>
       </c>
       <c r="G26" t="n">
-        <v>295.6</v>
+        <v>263.3</v>
       </c>
       <c r="H26" t="n">
-        <v>41.8</v>
+        <v>40.9</v>
       </c>
       <c r="I26" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>18.63</v>
+        <v>402.38</v>
       </c>
       <c r="K26" t="n">
-        <v>-23.73</v>
+        <v>214.94</v>
       </c>
       <c r="L26" t="n">
-        <v>30.17</v>
+        <v>456.19</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:14:55</t>
+          <t>05:14:42</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.25</v>
+        <v>3.67</v>
       </c>
       <c r="F27" t="n">
-        <v>11.09</v>
+        <v>11.11</v>
       </c>
       <c r="G27" t="n">
-        <v>291</v>
+        <v>279.6</v>
       </c>
       <c r="H27" t="n">
-        <v>40.1</v>
+        <v>36.8</v>
       </c>
       <c r="I27" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>201.03</v>
+        <v>-218.47</v>
       </c>
       <c r="K27" t="n">
-        <v>176.59</v>
+        <v>28.5</v>
       </c>
       <c r="L27" t="n">
-        <v>267.58</v>
+        <v>220.32</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:16:21</t>
+          <t>05:16:50</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.85</v>
+        <v>3.52</v>
       </c>
       <c r="F28" t="n">
-        <v>11.18</v>
+        <v>10.5</v>
       </c>
       <c r="G28" t="n">
-        <v>274.9</v>
+        <v>264.9</v>
       </c>
       <c r="H28" t="n">
-        <v>34.8</v>
+        <v>41.1</v>
       </c>
       <c r="I28" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>200.71</v>
+        <v>-611.8200000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>-62.66</v>
+        <v>-612.38</v>
       </c>
       <c r="L28" t="n">
-        <v>210.26</v>
+        <v>865.64</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:24:16</t>
+          <t>05:27:19</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.49</v>
+        <v>3.35</v>
       </c>
       <c r="F29" t="n">
-        <v>10.39</v>
+        <v>10.64</v>
       </c>
       <c r="G29" t="n">
-        <v>298.1</v>
+        <v>270.3</v>
       </c>
       <c r="H29" t="n">
-        <v>47.3</v>
+        <v>39.1</v>
       </c>
       <c r="I29" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>51.55</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>14.58</v>
+        <v>100.58</v>
       </c>
       <c r="L29" t="n">
-        <v>53.57</v>
+        <v>101.02</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:26:16</t>
+          <t>05:29:38</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.99</v>
+        <v>4.27</v>
       </c>
       <c r="F30" t="n">
-        <v>11.17</v>
+        <v>10.86</v>
       </c>
       <c r="G30" t="n">
-        <v>283</v>
+        <v>274.7</v>
       </c>
       <c r="H30" t="n">
-        <v>43.2</v>
+        <v>32.7</v>
       </c>
       <c r="I30" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-134.97</v>
+        <v>-179.01</v>
       </c>
       <c r="K30" t="n">
-        <v>169.79</v>
+        <v>11.92</v>
       </c>
       <c r="L30" t="n">
-        <v>216.9</v>
+        <v>179.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:28:23</t>
+          <t>05:31:55</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4.36</v>
+        <v>4.79</v>
       </c>
       <c r="F31" t="n">
-        <v>11.4</v>
+        <v>11.25</v>
       </c>
       <c r="G31" t="n">
-        <v>267.7</v>
+        <v>290.7</v>
       </c>
       <c r="H31" t="n">
-        <v>46.7</v>
+        <v>34.9</v>
       </c>
       <c r="I31" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J31" t="n">
-        <v>-144.36</v>
+        <v>207.35</v>
       </c>
       <c r="K31" t="n">
-        <v>-59.5</v>
+        <v>-64.84</v>
       </c>
       <c r="L31" t="n">
-        <v>156.14</v>
+        <v>217.25</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:32:09</t>
+          <t>05:36:51</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>4.3</v>
+        <v>3.86</v>
       </c>
       <c r="F32" t="n">
-        <v>11.16</v>
+        <v>11.08</v>
       </c>
       <c r="G32" t="n">
-        <v>275.8</v>
+        <v>263</v>
       </c>
       <c r="H32" t="n">
-        <v>37.6</v>
+        <v>42.6</v>
       </c>
       <c r="I32" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="J32" t="n">
-        <v>17.46</v>
+        <v>129.74</v>
       </c>
       <c r="K32" t="n">
-        <v>133.31</v>
+        <v>61.35</v>
       </c>
       <c r="L32" t="n">
-        <v>134.45</v>
+        <v>143.51</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:33:32</t>
+          <t>05:38:30</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.8</v>
+        <v>3.36</v>
       </c>
       <c r="F33" t="n">
-        <v>11.37</v>
+        <v>11.5</v>
       </c>
       <c r="G33" t="n">
-        <v>274.4</v>
+        <v>285.4</v>
       </c>
       <c r="H33" t="n">
-        <v>35.9</v>
+        <v>41.6</v>
       </c>
       <c r="I33" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J33" t="n">
-        <v>-154.24</v>
+        <v>-2.21</v>
       </c>
       <c r="K33" t="n">
-        <v>320.22</v>
+        <v>150.62</v>
       </c>
       <c r="L33" t="n">
-        <v>355.42</v>
+        <v>150.64</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:36:05</t>
+          <t>05:40:15</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.63</v>
+        <v>4.76</v>
       </c>
       <c r="F34" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="G34" t="n">
-        <v>274.7</v>
+        <v>284.3</v>
       </c>
       <c r="H34" t="n">
-        <v>39.4</v>
+        <v>40.9</v>
       </c>
       <c r="I34" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>-15.58</v>
+        <v>406.89</v>
       </c>
       <c r="K34" t="n">
-        <v>-109.26</v>
+        <v>-141.77</v>
       </c>
       <c r="L34" t="n">
-        <v>110.37</v>
+        <v>430.88</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:40:51</t>
+          <t>05:45:45</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="F35" t="n">
-        <v>11.34</v>
+        <v>11.13</v>
       </c>
       <c r="G35" t="n">
-        <v>279.8</v>
+        <v>276.4</v>
       </c>
       <c r="H35" t="n">
-        <v>46</v>
+        <v>39.3</v>
       </c>
       <c r="I35" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>13.12</v>
+        <v>-346.23</v>
       </c>
       <c r="K35" t="n">
-        <v>-6.31</v>
+        <v>454.56</v>
       </c>
       <c r="L35" t="n">
-        <v>14.55</v>
+        <v>571.4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:42:42</t>
+          <t>05:46:41</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.9</v>
+        <v>4.38</v>
       </c>
       <c r="F36" t="n">
-        <v>11.23</v>
+        <v>11.18</v>
       </c>
       <c r="G36" t="n">
-        <v>282.8</v>
+        <v>280.5</v>
       </c>
       <c r="H36" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I36" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>-233.96</v>
+        <v>10.65</v>
       </c>
       <c r="K36" t="n">
-        <v>-522.28</v>
+        <v>-69.11</v>
       </c>
       <c r="L36" t="n">
-        <v>572.29</v>
+        <v>69.93000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:44:27</t>
+          <t>05:48:20</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="F37" t="n">
-        <v>10.33</v>
+        <v>11.41</v>
       </c>
       <c r="G37" t="n">
-        <v>277.4</v>
+        <v>283.7</v>
       </c>
       <c r="H37" t="n">
-        <v>41.4</v>
+        <v>39.1</v>
       </c>
       <c r="I37" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>-167.87</v>
+        <v>-99.09999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>-56.44</v>
+        <v>-175.6</v>
       </c>
       <c r="L37" t="n">
-        <v>177.1</v>
+        <v>201.64</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:48:54</t>
+          <t>05:52:25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.95</v>
+        <v>3.73</v>
       </c>
       <c r="F38" t="n">
-        <v>10.73</v>
+        <v>11.03</v>
       </c>
       <c r="G38" t="n">
-        <v>295.6</v>
+        <v>285.5</v>
       </c>
       <c r="H38" t="n">
-        <v>39.8</v>
+        <v>39.3</v>
       </c>
       <c r="I38" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>447.49</v>
+        <v>359.99</v>
       </c>
       <c r="K38" t="n">
-        <v>-69.34</v>
+        <v>304.13</v>
       </c>
       <c r="L38" t="n">
-        <v>452.84</v>
+        <v>471.26</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:49:58</t>
+          <t>05:54:27</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>4.01</v>
+        <v>3.71</v>
       </c>
       <c r="F39" t="n">
-        <v>10.87</v>
+        <v>10.89</v>
       </c>
       <c r="G39" t="n">
-        <v>288</v>
+        <v>283.7</v>
       </c>
       <c r="H39" t="n">
-        <v>44.5</v>
+        <v>39.5</v>
       </c>
       <c r="I39" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-164.27</v>
+        <v>22.23</v>
       </c>
       <c r="K39" t="n">
-        <v>-387.32</v>
+        <v>-125.03</v>
       </c>
       <c r="L39" t="n">
-        <v>420.72</v>
+        <v>126.99</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:51:23</t>
+          <t>05:55:57</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>4.9</v>
+        <v>3.33</v>
       </c>
       <c r="F40" t="n">
-        <v>10.03</v>
+        <v>11.09</v>
       </c>
       <c r="G40" t="n">
-        <v>280.3</v>
+        <v>287</v>
       </c>
       <c r="H40" t="n">
-        <v>38.4</v>
+        <v>38.6</v>
       </c>
       <c r="I40" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>-35.26</v>
+        <v>246.3</v>
       </c>
       <c r="K40" t="n">
-        <v>-105.84</v>
+        <v>65.5</v>
       </c>
       <c r="L40" t="n">
-        <v>111.56</v>
+        <v>254.86</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:56:36</t>
+          <t>05:59:50</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>4.65</v>
+        <v>4.57</v>
       </c>
       <c r="F41" t="n">
-        <v>11.01</v>
+        <v>11.19</v>
       </c>
       <c r="G41" t="n">
-        <v>276.3</v>
+        <v>270.9</v>
       </c>
       <c r="H41" t="n">
-        <v>35.7</v>
+        <v>38.8</v>
       </c>
       <c r="I41" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>-200.14</v>
+        <v>-304.21</v>
       </c>
       <c r="K41" t="n">
-        <v>361.79</v>
+        <v>-224.73</v>
       </c>
       <c r="L41" t="n">
-        <v>413.46</v>
+        <v>378.22</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05:58:24</t>
+          <t>06:01:39</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.94</v>
+        <v>4.08</v>
       </c>
       <c r="F42" t="n">
-        <v>11.16</v>
+        <v>10.05</v>
       </c>
       <c r="G42" t="n">
-        <v>282.6</v>
+        <v>284.5</v>
       </c>
       <c r="H42" t="n">
-        <v>41.5</v>
+        <v>31.1</v>
       </c>
       <c r="I42" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J42" t="n">
-        <v>-397.81</v>
+        <v>607.5599999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>-547.03</v>
+        <v>-50.75</v>
       </c>
       <c r="L42" t="n">
-        <v>676.39</v>
+        <v>609.6799999999999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:00:17</t>
+          <t>06:03:16</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.47</v>
+        <v>4.51</v>
       </c>
       <c r="F43" t="n">
-        <v>11.37</v>
+        <v>10.87</v>
       </c>
       <c r="G43" t="n">
-        <v>274.2</v>
+        <v>261.9</v>
       </c>
       <c r="H43" t="n">
-        <v>44.9</v>
+        <v>38.3</v>
       </c>
       <c r="I43" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>275.17</v>
+        <v>161.2</v>
       </c>
       <c r="K43" t="n">
-        <v>-104.21</v>
+        <v>-279.58</v>
       </c>
       <c r="L43" t="n">
-        <v>294.24</v>
+        <v>322.73</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:09:53</t>
+          <t>06:13:59</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.41</v>
+        <v>4.21</v>
       </c>
       <c r="F44" t="n">
-        <v>10.87</v>
+        <v>10.69</v>
       </c>
       <c r="G44" t="n">
-        <v>278</v>
+        <v>301.8</v>
       </c>
       <c r="H44" t="n">
-        <v>45.7</v>
+        <v>39.8</v>
       </c>
       <c r="I44" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>-56.06</v>
+        <v>125.08</v>
       </c>
       <c r="K44" t="n">
-        <v>36.22</v>
+        <v>-116.23</v>
       </c>
       <c r="L44" t="n">
-        <v>66.73999999999999</v>
+        <v>170.75</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:12:11</t>
+          <t>06:15:15</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.89</v>
+        <v>3.95</v>
       </c>
       <c r="F45" t="n">
-        <v>10.91</v>
+        <v>11.04</v>
       </c>
       <c r="G45" t="n">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="H45" t="n">
-        <v>42.7</v>
+        <v>44.2</v>
       </c>
       <c r="I45" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>-61.39</v>
+        <v>104.79</v>
       </c>
       <c r="K45" t="n">
-        <v>119.83</v>
+        <v>48.99</v>
       </c>
       <c r="L45" t="n">
-        <v>134.63</v>
+        <v>115.68</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:14:16</t>
+          <t>06:17:06</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>4.2</v>
+        <v>4.09</v>
       </c>
       <c r="F46" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="G46" t="n">
-        <v>289.6</v>
+        <v>276.1</v>
       </c>
       <c r="H46" t="n">
-        <v>34.1</v>
+        <v>38.5</v>
       </c>
       <c r="I46" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>209.55</v>
+        <v>302.91</v>
       </c>
       <c r="K46" t="n">
-        <v>-60.35</v>
+        <v>128.89</v>
       </c>
       <c r="L46" t="n">
-        <v>218.07</v>
+        <v>329.19</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:19:04</t>
+          <t>06:20:38</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.49</v>
+        <v>3.78</v>
       </c>
       <c r="F47" t="n">
-        <v>10.91</v>
+        <v>10.11</v>
       </c>
       <c r="G47" t="n">
-        <v>278.6</v>
+        <v>288</v>
       </c>
       <c r="H47" t="n">
-        <v>48.2</v>
+        <v>40.2</v>
       </c>
       <c r="I47" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>167.83</v>
+        <v>-110.03</v>
       </c>
       <c r="K47" t="n">
-        <v>-264.53</v>
+        <v>39.1</v>
       </c>
       <c r="L47" t="n">
-        <v>313.28</v>
+        <v>116.77</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:20:03</t>
+          <t>06:22:57</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.31</v>
+        <v>4.26</v>
       </c>
       <c r="F48" t="n">
-        <v>10.69</v>
+        <v>11.02</v>
       </c>
       <c r="G48" t="n">
-        <v>280.7</v>
+        <v>289.3</v>
       </c>
       <c r="H48" t="n">
-        <v>43</v>
+        <v>39.6</v>
       </c>
       <c r="I48" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-187.51</v>
+        <v>17.9</v>
       </c>
       <c r="K48" t="n">
-        <v>-38.53</v>
+        <v>337.07</v>
       </c>
       <c r="L48" t="n">
-        <v>191.43</v>
+        <v>337.55</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:22:02</t>
+          <t>06:25:24</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="F49" t="n">
-        <v>10.07</v>
+        <v>10.86</v>
       </c>
       <c r="G49" t="n">
-        <v>283</v>
+        <v>277.1</v>
       </c>
       <c r="H49" t="n">
-        <v>39.1</v>
+        <v>34.4</v>
       </c>
       <c r="I49" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>-293.67</v>
+        <v>59.36</v>
       </c>
       <c r="K49" t="n">
-        <v>148.96</v>
+        <v>-111.29</v>
       </c>
       <c r="L49" t="n">
-        <v>329.29</v>
+        <v>126.13</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:27:30</t>
+          <t>06:29:57</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.24</v>
+        <v>3.83</v>
       </c>
       <c r="F50" t="n">
-        <v>11.11</v>
+        <v>11</v>
       </c>
       <c r="G50" t="n">
-        <v>281.4</v>
+        <v>271.9</v>
       </c>
       <c r="H50" t="n">
-        <v>37.3</v>
+        <v>45.6</v>
       </c>
       <c r="I50" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>29.21</v>
+        <v>-372.87</v>
       </c>
       <c r="K50" t="n">
-        <v>276.88</v>
+        <v>-139.2</v>
       </c>
       <c r="L50" t="n">
-        <v>278.42</v>
+        <v>398.01</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:29:19</t>
+          <t>06:31:13</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.58</v>
+        <v>4.55</v>
       </c>
       <c r="F51" t="n">
-        <v>10.18</v>
+        <v>10.59</v>
       </c>
       <c r="G51" t="n">
-        <v>277.2</v>
+        <v>281.1</v>
       </c>
       <c r="H51" t="n">
         <v>40.2</v>
       </c>
       <c r="I51" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>299.92</v>
+        <v>-137.06</v>
       </c>
       <c r="K51" t="n">
-        <v>280.71</v>
+        <v>49.36</v>
       </c>
       <c r="L51" t="n">
-        <v>410.8</v>
+        <v>145.67</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:31:03</t>
+          <t>06:32:21</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.92</v>
+        <v>4.02</v>
       </c>
       <c r="F52" t="n">
-        <v>11.22</v>
+        <v>10.6</v>
       </c>
       <c r="G52" t="n">
-        <v>286.3</v>
+        <v>294.1</v>
       </c>
       <c r="H52" t="n">
-        <v>38.2</v>
+        <v>45</v>
       </c>
       <c r="I52" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J52" t="n">
-        <v>-455.01</v>
+        <v>106.34</v>
       </c>
       <c r="K52" t="n">
-        <v>322.68</v>
+        <v>234.97</v>
       </c>
       <c r="L52" t="n">
-        <v>557.8200000000001</v>
+        <v>257.91</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:35:33</t>
+          <t>06:37:06</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.16</v>
+        <v>4.15</v>
       </c>
       <c r="F53" t="n">
-        <v>10.73</v>
+        <v>10.98</v>
       </c>
       <c r="G53" t="n">
-        <v>291.6</v>
+        <v>293.3</v>
       </c>
       <c r="H53" t="n">
-        <v>38.5</v>
+        <v>43.9</v>
       </c>
       <c r="I53" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>61.61</v>
+        <v>-822.41</v>
       </c>
       <c r="K53" t="n">
-        <v>-284.96</v>
+        <v>-490.38</v>
       </c>
       <c r="L53" t="n">
-        <v>291.55</v>
+        <v>957.52</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:37:04</t>
+          <t>06:38:06</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.2</v>
+        <v>4.04</v>
       </c>
       <c r="F54" t="n">
-        <v>11.8</v>
+        <v>10.7</v>
       </c>
       <c r="G54" t="n">
-        <v>279.9</v>
+        <v>270.3</v>
       </c>
       <c r="H54" t="n">
-        <v>42.1</v>
+        <v>43.4</v>
       </c>
       <c r="I54" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J54" t="n">
-        <v>249.72</v>
+        <v>334.16</v>
       </c>
       <c r="K54" t="n">
-        <v>253.61</v>
+        <v>-192.3</v>
       </c>
       <c r="L54" t="n">
-        <v>355.92</v>
+        <v>385.55</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:37:49</t>
+          <t>06:40:03</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.42</v>
+        <v>4.35</v>
       </c>
       <c r="F55" t="n">
-        <v>10.28</v>
+        <v>10.22</v>
       </c>
       <c r="G55" t="n">
-        <v>279.2</v>
+        <v>280.5</v>
       </c>
       <c r="H55" t="n">
-        <v>38.1</v>
+        <v>43.5</v>
       </c>
       <c r="I55" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>-718.85</v>
+        <v>-81.61</v>
       </c>
       <c r="K55" t="n">
-        <v>-168.79</v>
+        <v>144.64</v>
       </c>
       <c r="L55" t="n">
-        <v>738.4</v>
+        <v>166.08</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:42:31</t>
+          <t>06:45:04</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="F56" t="n">
-        <v>10.36</v>
+        <v>10.72</v>
       </c>
       <c r="G56" t="n">
-        <v>289.2</v>
+        <v>273.4</v>
       </c>
       <c r="H56" t="n">
-        <v>45.1</v>
+        <v>40.2</v>
       </c>
       <c r="I56" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>-594.39</v>
+        <v>195.19</v>
       </c>
       <c r="K56" t="n">
-        <v>-350.8</v>
+        <v>439.97</v>
       </c>
       <c r="L56" t="n">
-        <v>690.1799999999999</v>
+        <v>481.32</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:43:24</t>
+          <t>06:46:18</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.98</v>
+        <v>3.85</v>
       </c>
       <c r="F57" t="n">
-        <v>10.79</v>
+        <v>10.7</v>
       </c>
       <c r="G57" t="n">
-        <v>286.8</v>
+        <v>279.4</v>
       </c>
       <c r="H57" t="n">
-        <v>42.2</v>
+        <v>40.8</v>
       </c>
       <c r="I57" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>712.8099999999999</v>
+        <v>-409.48</v>
       </c>
       <c r="K57" t="n">
-        <v>-888.85</v>
+        <v>-62.14</v>
       </c>
       <c r="L57" t="n">
-        <v>1139.37</v>
+        <v>414.16</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:44:50</t>
+          <t>06:48:27</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="F58" t="n">
-        <v>10.48</v>
+        <v>10.83</v>
       </c>
       <c r="G58" t="n">
-        <v>269.3</v>
+        <v>291.8</v>
       </c>
       <c r="H58" t="n">
-        <v>39</v>
+        <v>41.5</v>
       </c>
       <c r="I58" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>629.4</v>
+        <v>327.44</v>
       </c>
       <c r="K58" t="n">
-        <v>-572.49</v>
+        <v>-412.82</v>
       </c>
       <c r="L58" t="n">
-        <v>850.8200000000001</v>
+        <v>526.91</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:54:26</t>
+          <t>06:58:02</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.76</v>
+        <v>4.24</v>
       </c>
       <c r="F59" t="n">
-        <v>10.99</v>
+        <v>10.9</v>
       </c>
       <c r="G59" t="n">
-        <v>281.4</v>
+        <v>270.7</v>
       </c>
       <c r="H59" t="n">
-        <v>41.8</v>
+        <v>39.5</v>
       </c>
       <c r="I59" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>-24.76</v>
+        <v>289.15</v>
       </c>
       <c r="K59" t="n">
-        <v>-118.96</v>
+        <v>14.9</v>
       </c>
       <c r="L59" t="n">
-        <v>121.51</v>
+        <v>289.53</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:56:44</t>
+          <t>06:59:48</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.44</v>
+        <v>4.61</v>
       </c>
       <c r="F60" t="n">
-        <v>11.26</v>
+        <v>11.55</v>
       </c>
       <c r="G60" t="n">
-        <v>279.8</v>
+        <v>265.4</v>
       </c>
       <c r="H60" t="n">
-        <v>41</v>
+        <v>38.6</v>
       </c>
       <c r="I60" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>39.36</v>
+        <v>202.07</v>
       </c>
       <c r="K60" t="n">
-        <v>67.34999999999999</v>
+        <v>80.01000000000001</v>
       </c>
       <c r="L60" t="n">
-        <v>78.01000000000001</v>
+        <v>217.33</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06:58:52</t>
+          <t>07:01:47</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.61</v>
+        <v>4.83</v>
       </c>
       <c r="F61" t="n">
-        <v>10.79</v>
+        <v>10.94</v>
       </c>
       <c r="G61" t="n">
-        <v>279.8</v>
+        <v>275.1</v>
       </c>
       <c r="H61" t="n">
-        <v>33.2</v>
+        <v>38</v>
       </c>
       <c r="I61" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>-186.34</v>
+        <v>203.21</v>
       </c>
       <c r="K61" t="n">
-        <v>-33.74</v>
+        <v>129.64</v>
       </c>
       <c r="L61" t="n">
-        <v>189.37</v>
+        <v>241.04</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:03:26</t>
+          <t>07:05:41</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.97</v>
+        <v>3.68</v>
       </c>
       <c r="F62" t="n">
-        <v>10.95</v>
+        <v>11</v>
       </c>
       <c r="G62" t="n">
-        <v>281.4</v>
+        <v>281.1</v>
       </c>
       <c r="H62" t="n">
-        <v>37.4</v>
+        <v>39.4</v>
       </c>
       <c r="I62" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>9.65</v>
+        <v>134.87</v>
       </c>
       <c r="K62" t="n">
-        <v>-385.17</v>
+        <v>-107.08</v>
       </c>
       <c r="L62" t="n">
-        <v>385.29</v>
+        <v>172.2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:04:20</t>
+          <t>07:06:55</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.07</v>
+        <v>4.26</v>
       </c>
       <c r="F63" t="n">
-        <v>11.41</v>
+        <v>10.22</v>
       </c>
       <c r="G63" t="n">
-        <v>272.9</v>
+        <v>295.6</v>
       </c>
       <c r="H63" t="n">
-        <v>45</v>
+        <v>39.7</v>
       </c>
       <c r="I63" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>-316.97</v>
+        <v>-22.85</v>
       </c>
       <c r="K63" t="n">
-        <v>136.66</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>345.17</v>
+        <v>72.28</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:07:07</t>
+          <t>07:07:52</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>5.05</v>
+        <v>3.94</v>
       </c>
       <c r="F64" t="n">
-        <v>11.53</v>
+        <v>10.51</v>
       </c>
       <c r="G64" t="n">
-        <v>276.6</v>
+        <v>291.4</v>
       </c>
       <c r="H64" t="n">
-        <v>46.6</v>
+        <v>34.6</v>
       </c>
       <c r="I64" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>-21.4</v>
+        <v>332.57</v>
       </c>
       <c r="K64" t="n">
-        <v>0.48</v>
+        <v>-115.71</v>
       </c>
       <c r="L64" t="n">
-        <v>21.41</v>
+        <v>352.12</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:11:22</t>
+          <t>07:13:00</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.84</v>
+        <v>4.42</v>
       </c>
       <c r="F65" t="n">
-        <v>10.73</v>
+        <v>11.02</v>
       </c>
       <c r="G65" t="n">
-        <v>276.5</v>
+        <v>275.1</v>
       </c>
       <c r="H65" t="n">
-        <v>34.9</v>
+        <v>34.8</v>
       </c>
       <c r="I65" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>-175.79</v>
+        <v>-217.65</v>
       </c>
       <c r="K65" t="n">
-        <v>775.53</v>
+        <v>-121.08</v>
       </c>
       <c r="L65" t="n">
-        <v>795.2</v>
+        <v>249.06</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:12:39</t>
+          <t>07:14:35</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.56</v>
+        <v>4.45</v>
       </c>
       <c r="F66" t="n">
-        <v>11.27</v>
+        <v>10.69</v>
       </c>
       <c r="G66" t="n">
-        <v>281.4</v>
+        <v>274</v>
       </c>
       <c r="H66" t="n">
-        <v>39</v>
+        <v>42.8</v>
       </c>
       <c r="I66" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>58.35</v>
+        <v>283.39</v>
       </c>
       <c r="K66" t="n">
-        <v>96.92</v>
+        <v>-56.74</v>
       </c>
       <c r="L66" t="n">
-        <v>113.13</v>
+        <v>289.01</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:14:35</t>
+          <t>07:16:09</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.69</v>
+        <v>4.3</v>
       </c>
       <c r="F67" t="n">
-        <v>10.42</v>
+        <v>10.91</v>
       </c>
       <c r="G67" t="n">
-        <v>278</v>
+        <v>289.4</v>
       </c>
       <c r="H67" t="n">
-        <v>38</v>
+        <v>40.7</v>
       </c>
       <c r="I67" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>-129.69</v>
+        <v>-347.01</v>
       </c>
       <c r="K67" t="n">
-        <v>114.56</v>
+        <v>-458.79</v>
       </c>
       <c r="L67" t="n">
-        <v>173.04</v>
+        <v>575.25</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:18:36</t>
+          <t>07:21:56</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.39</v>
+        <v>4.76</v>
       </c>
       <c r="F68" t="n">
-        <v>10.8</v>
+        <v>10.54</v>
       </c>
       <c r="G68" t="n">
-        <v>293</v>
+        <v>270.8</v>
       </c>
       <c r="H68" t="n">
-        <v>49</v>
+        <v>40.9</v>
       </c>
       <c r="I68" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-347.41</v>
+        <v>605.75</v>
       </c>
       <c r="K68" t="n">
-        <v>-259.58</v>
+        <v>-239.61</v>
       </c>
       <c r="L68" t="n">
-        <v>433.67</v>
+        <v>651.42</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:20:56</t>
+          <t>07:24:11</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.72</v>
+        <v>4.57</v>
       </c>
       <c r="F69" t="n">
-        <v>10.22</v>
+        <v>11.4</v>
       </c>
       <c r="G69" t="n">
-        <v>290.4</v>
+        <v>277.2</v>
       </c>
       <c r="H69" t="n">
-        <v>41.1</v>
+        <v>47.5</v>
       </c>
       <c r="I69" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>-334.9</v>
+        <v>-362.85</v>
       </c>
       <c r="K69" t="n">
-        <v>43.39</v>
+        <v>134.26</v>
       </c>
       <c r="L69" t="n">
-        <v>337.7</v>
+        <v>386.89</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:23:10</t>
+          <t>07:26:41</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.69</v>
+        <v>4.33</v>
       </c>
       <c r="F70" t="n">
-        <v>10.24</v>
+        <v>11.45</v>
       </c>
       <c r="G70" t="n">
-        <v>277.8</v>
+        <v>280</v>
       </c>
       <c r="H70" t="n">
-        <v>40.8</v>
+        <v>41.3</v>
       </c>
       <c r="I70" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>-118.41</v>
+        <v>344.08</v>
       </c>
       <c r="K70" t="n">
-        <v>-336.79</v>
+        <v>-1271.56</v>
       </c>
       <c r="L70" t="n">
-        <v>357</v>
+        <v>1317.29</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:29:22</t>
+          <t>07:30:28</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.84</v>
+        <v>5.08</v>
       </c>
       <c r="F71" t="n">
-        <v>10.99</v>
+        <v>10.79</v>
       </c>
       <c r="G71" t="n">
-        <v>287.7</v>
+        <v>286.2</v>
       </c>
       <c r="H71" t="n">
-        <v>37.3</v>
+        <v>41.1</v>
       </c>
       <c r="I71" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>269.93</v>
+        <v>291.61</v>
       </c>
       <c r="K71" t="n">
-        <v>193.01</v>
+        <v>331.33</v>
       </c>
       <c r="L71" t="n">
-        <v>331.84</v>
+        <v>441.38</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:31:58</t>
+          <t>07:32:41</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.19</v>
+        <v>4.53</v>
       </c>
       <c r="F72" t="n">
-        <v>10.54</v>
+        <v>11.3</v>
       </c>
       <c r="G72" t="n">
-        <v>276.9</v>
+        <v>279.9</v>
       </c>
       <c r="H72" t="n">
-        <v>37.4</v>
+        <v>44.2</v>
       </c>
       <c r="I72" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>405.43</v>
+        <v>703.62</v>
       </c>
       <c r="K72" t="n">
-        <v>-596.39</v>
+        <v>470.98</v>
       </c>
       <c r="L72" t="n">
-        <v>721.15</v>
+        <v>846.7</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:34:09</t>
+          <t>07:34:03</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.26</v>
+        <v>4.14</v>
       </c>
       <c r="F73" t="n">
-        <v>11.06</v>
+        <v>11.65</v>
       </c>
       <c r="G73" t="n">
-        <v>291.1</v>
+        <v>275.2</v>
       </c>
       <c r="H73" t="n">
-        <v>35.9</v>
+        <v>42.6</v>
       </c>
       <c r="I73" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-410.03</v>
+        <v>-442.06</v>
       </c>
       <c r="K73" t="n">
-        <v>82.23999999999999</v>
+        <v>-110</v>
       </c>
       <c r="L73" t="n">
-        <v>418.2</v>
+        <v>455.54</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:46:33</t>
+          <t>07:42:41</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>5.03</v>
+        <v>4.14</v>
       </c>
       <c r="F74" t="n">
-        <v>10.89</v>
+        <v>11.01</v>
       </c>
       <c r="G74" t="n">
-        <v>279.3</v>
+        <v>274.8</v>
       </c>
       <c r="H74" t="n">
-        <v>38.6</v>
+        <v>38.8</v>
       </c>
       <c r="I74" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>25.93</v>
+        <v>-149.32</v>
       </c>
       <c r="K74" t="n">
-        <v>47.83</v>
+        <v>-240.78</v>
       </c>
       <c r="L74" t="n">
-        <v>54.41</v>
+        <v>283.32</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:47:18</t>
+          <t>07:44:38</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.57</v>
+        <v>4.5</v>
       </c>
       <c r="F75" t="n">
-        <v>11.28</v>
+        <v>11.3</v>
       </c>
       <c r="G75" t="n">
-        <v>281</v>
+        <v>293.4</v>
       </c>
       <c r="H75" t="n">
-        <v>44.2</v>
+        <v>42.3</v>
       </c>
       <c r="I75" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>400.64</v>
+        <v>452.42</v>
       </c>
       <c r="K75" t="n">
-        <v>28</v>
+        <v>-257.13</v>
       </c>
       <c r="L75" t="n">
-        <v>401.61</v>
+        <v>520.38</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:48:51</t>
+          <t>07:46:47</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4.03</v>
+        <v>3.63</v>
       </c>
       <c r="F76" t="n">
-        <v>10.6</v>
+        <v>11.18</v>
       </c>
       <c r="G76" t="n">
-        <v>270.4</v>
+        <v>280.2</v>
       </c>
       <c r="H76" t="n">
-        <v>46.3</v>
+        <v>42.1</v>
       </c>
       <c r="I76" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>110.24</v>
+        <v>-89.56999999999999</v>
       </c>
       <c r="K76" t="n">
-        <v>-75.3</v>
+        <v>-66.92</v>
       </c>
       <c r="L76" t="n">
-        <v>133.5</v>
+        <v>111.81</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:52:30</t>
+          <t>07:51:59</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.91</v>
+        <v>4.35</v>
       </c>
       <c r="F77" t="n">
-        <v>10.44</v>
+        <v>10.82</v>
       </c>
       <c r="G77" t="n">
-        <v>275.3</v>
+        <v>285.4</v>
       </c>
       <c r="H77" t="n">
-        <v>41.1</v>
+        <v>38.9</v>
       </c>
       <c r="I77" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-105.35</v>
+        <v>-176.11</v>
       </c>
       <c r="K77" t="n">
-        <v>-213.1</v>
+        <v>-203.49</v>
       </c>
       <c r="L77" t="n">
-        <v>237.71</v>
+        <v>269.12</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:53:41</t>
+          <t>07:53:19</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.29</v>
+        <v>4.53</v>
       </c>
       <c r="F78" t="n">
-        <v>10.88</v>
+        <v>11.67</v>
       </c>
       <c r="G78" t="n">
-        <v>282.5</v>
+        <v>291.5</v>
       </c>
       <c r="H78" t="n">
-        <v>48.6</v>
+        <v>36.6</v>
       </c>
       <c r="I78" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J78" t="n">
-        <v>357.16</v>
+        <v>226.18</v>
       </c>
       <c r="K78" t="n">
-        <v>-8.06</v>
+        <v>-372.13</v>
       </c>
       <c r="L78" t="n">
-        <v>357.25</v>
+        <v>435.47</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:54:57</t>
+          <t>07:54:43</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.51</v>
+        <v>4.8</v>
       </c>
       <c r="F79" t="n">
-        <v>11.21</v>
+        <v>10.58</v>
       </c>
       <c r="G79" t="n">
-        <v>276.1</v>
+        <v>280.3</v>
       </c>
       <c r="H79" t="n">
-        <v>46.2</v>
+        <v>36.3</v>
       </c>
       <c r="I79" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>-52.48</v>
+        <v>321.51</v>
       </c>
       <c r="K79" t="n">
-        <v>124.62</v>
+        <v>-17.67</v>
       </c>
       <c r="L79" t="n">
-        <v>135.22</v>
+        <v>321.99</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:00:03</t>
+          <t>07:59:22</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>5.31</v>
+        <v>5.17</v>
       </c>
       <c r="F80" t="n">
-        <v>10.71</v>
+        <v>10.79</v>
       </c>
       <c r="G80" t="n">
-        <v>280.2</v>
+        <v>267.8</v>
       </c>
       <c r="H80" t="n">
-        <v>43</v>
+        <v>46.1</v>
       </c>
       <c r="I80" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>114.92</v>
+        <v>394.7</v>
       </c>
       <c r="K80" t="n">
-        <v>162.73</v>
+        <v>50.47</v>
       </c>
       <c r="L80" t="n">
-        <v>199.22</v>
+        <v>397.91</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:01:31</t>
+          <t>08:01:13</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.62</v>
+        <v>3.71</v>
       </c>
       <c r="F81" t="n">
-        <v>10.77</v>
+        <v>10.78</v>
       </c>
       <c r="G81" t="n">
         <v>287.2</v>
       </c>
       <c r="H81" t="n">
-        <v>42.4</v>
+        <v>43.8</v>
       </c>
       <c r="I81" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>135.59</v>
+        <v>140.69</v>
       </c>
       <c r="K81" t="n">
-        <v>272.1</v>
+        <v>-246.54</v>
       </c>
       <c r="L81" t="n">
-        <v>304.01</v>
+        <v>283.85</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:04:04</t>
+          <t>08:02:11</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.2</v>
+        <v>4.61</v>
       </c>
       <c r="F82" t="n">
-        <v>10.95</v>
+        <v>10.94</v>
       </c>
       <c r="G82" t="n">
-        <v>273.8</v>
+        <v>284</v>
       </c>
       <c r="H82" t="n">
-        <v>34.1</v>
+        <v>39</v>
       </c>
       <c r="I82" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-188.38</v>
+        <v>-358.2</v>
       </c>
       <c r="K82" t="n">
-        <v>-222.83</v>
+        <v>159.22</v>
       </c>
       <c r="L82" t="n">
-        <v>291.78</v>
+        <v>391.99</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:09:06</t>
+          <t>08:08:13</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.23</v>
+        <v>4.82</v>
       </c>
       <c r="F83" t="n">
-        <v>10.9</v>
+        <v>10.93</v>
       </c>
       <c r="G83" t="n">
-        <v>278.9</v>
+        <v>287.9</v>
       </c>
       <c r="H83" t="n">
-        <v>44.6</v>
+        <v>39.7</v>
       </c>
       <c r="I83" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>-242.89</v>
+        <v>222.1</v>
       </c>
       <c r="K83" t="n">
-        <v>-159.31</v>
+        <v>-538.98</v>
       </c>
       <c r="L83" t="n">
-        <v>290.47</v>
+        <v>582.9400000000001</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:10:50</t>
+          <t>08:10:22</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.49</v>
+        <v>4.57</v>
       </c>
       <c r="F84" t="n">
-        <v>10.83</v>
+        <v>10.62</v>
       </c>
       <c r="G84" t="n">
-        <v>283.1</v>
+        <v>282.2</v>
       </c>
       <c r="H84" t="n">
-        <v>41.2</v>
+        <v>38.3</v>
       </c>
       <c r="I84" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>16.11</v>
+        <v>-39.08</v>
       </c>
       <c r="K84" t="n">
-        <v>360.94</v>
+        <v>-210.21</v>
       </c>
       <c r="L84" t="n">
-        <v>361.3</v>
+        <v>213.81</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:13:30</t>
+          <t>08:13:04</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.04</v>
+        <v>5.56</v>
       </c>
       <c r="F85" t="n">
-        <v>11.36</v>
+        <v>10.78</v>
       </c>
       <c r="G85" t="n">
-        <v>274.8</v>
+        <v>285.4</v>
       </c>
       <c r="H85" t="n">
-        <v>41.7</v>
+        <v>45.7</v>
       </c>
       <c r="I85" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>-90.84</v>
+        <v>3.63</v>
       </c>
       <c r="K85" t="n">
-        <v>121.26</v>
+        <v>475.9</v>
       </c>
       <c r="L85" t="n">
-        <v>151.51</v>
+        <v>475.92</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:18:52</t>
+          <t>08:16:49</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.55</v>
+        <v>4.61</v>
       </c>
       <c r="F86" t="n">
-        <v>10.72</v>
+        <v>10.78</v>
       </c>
       <c r="G86" t="n">
-        <v>274.6</v>
+        <v>288.3</v>
       </c>
       <c r="H86" t="n">
-        <v>37.3</v>
+        <v>43.6</v>
       </c>
       <c r="I86" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>10.86</v>
+        <v>204.97</v>
       </c>
       <c r="K86" t="n">
-        <v>169.73</v>
+        <v>-305.22</v>
       </c>
       <c r="L86" t="n">
-        <v>170.07</v>
+        <v>367.65</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:20:26</t>
+          <t>08:18:56</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.44</v>
+        <v>4.94</v>
       </c>
       <c r="F87" t="n">
-        <v>10.67</v>
+        <v>11.02</v>
       </c>
       <c r="G87" t="n">
-        <v>272.5</v>
+        <v>274.2</v>
       </c>
       <c r="H87" t="n">
-        <v>38.6</v>
+        <v>39.5</v>
       </c>
       <c r="I87" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>586.22</v>
+        <v>483.62</v>
       </c>
       <c r="K87" t="n">
-        <v>-645.88</v>
+        <v>356.74</v>
       </c>
       <c r="L87" t="n">
-        <v>872.25</v>
+        <v>600.96</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:22:21</t>
+          <t>08:20:48</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.44</v>
+        <v>3.91</v>
       </c>
       <c r="F88" t="n">
-        <v>10.5</v>
+        <v>10.7</v>
       </c>
       <c r="G88" t="n">
-        <v>279.2</v>
+        <v>280.5</v>
       </c>
       <c r="H88" t="n">
-        <v>37.1</v>
+        <v>40.8</v>
       </c>
       <c r="I88" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>428.89</v>
+        <v>469.5</v>
       </c>
       <c r="K88" t="n">
-        <v>-527.15</v>
+        <v>718.33</v>
       </c>
       <c r="L88" t="n">
-        <v>679.58</v>
+        <v>858.15</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-06.xlsx
+++ b/output/2024-07-06.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-159.66</v>
+        <v>-174.39</v>
       </c>
       <c r="K14" t="n">
-        <v>61.15</v>
+        <v>66.8</v>
       </c>
       <c r="L14" t="n">
-        <v>170.97</v>
+        <v>186.74</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>28</v>
       </c>
       <c r="J15" t="n">
-        <v>-151.3</v>
+        <v>-141.22</v>
       </c>
       <c r="K15" t="n">
-        <v>-42.92</v>
+        <v>-40.06</v>
       </c>
       <c r="L15" t="n">
-        <v>157.27</v>
+        <v>146.79</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>-79.36</v>
+        <v>-70.77</v>
       </c>
       <c r="K16" t="n">
-        <v>404.78</v>
+        <v>360.99</v>
       </c>
       <c r="L16" t="n">
-        <v>412.48</v>
+        <v>367.87</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>28</v>
       </c>
       <c r="J17" t="n">
-        <v>106.02</v>
+        <v>103.93</v>
       </c>
       <c r="K17" t="n">
-        <v>109.98</v>
+        <v>107.82</v>
       </c>
       <c r="L17" t="n">
-        <v>152.76</v>
+        <v>149.76</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>34.74</v>
+        <v>79.88</v>
       </c>
       <c r="K18" t="n">
-        <v>-25.31</v>
+        <v>-58.21</v>
       </c>
       <c r="L18" t="n">
-        <v>42.98</v>
+        <v>98.84999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-248.17</v>
+        <v>-221.38</v>
       </c>
       <c r="K19" t="n">
-        <v>88.34</v>
+        <v>78.8</v>
       </c>
       <c r="L19" t="n">
-        <v>263.42</v>
+        <v>234.99</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>315.62</v>
+        <v>320.31</v>
       </c>
       <c r="K20" t="n">
-        <v>367.37</v>
+        <v>372.82</v>
       </c>
       <c r="L20" t="n">
-        <v>484.33</v>
+        <v>491.52</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>28</v>
       </c>
       <c r="J21" t="n">
-        <v>53.15</v>
+        <v>49.37</v>
       </c>
       <c r="K21" t="n">
-        <v>-256.46</v>
+        <v>-238.24</v>
       </c>
       <c r="L21" t="n">
-        <v>261.91</v>
+        <v>243.3</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>175.2</v>
+        <v>195.87</v>
       </c>
       <c r="K22" t="n">
-        <v>-145</v>
+        <v>-162.11</v>
       </c>
       <c r="L22" t="n">
-        <v>227.42</v>
+        <v>254.26</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>-92.84</v>
+        <v>-92.48</v>
       </c>
       <c r="K23" t="n">
-        <v>559.02</v>
+        <v>556.86</v>
       </c>
       <c r="L23" t="n">
-        <v>566.6799999999999</v>
+        <v>564.48</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>-6.23</v>
+        <v>-7.28</v>
       </c>
       <c r="K24" t="n">
-        <v>364.33</v>
+        <v>425.86</v>
       </c>
       <c r="L24" t="n">
-        <v>364.38</v>
+        <v>425.92</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>156.75</v>
+        <v>163.23</v>
       </c>
       <c r="K25" t="n">
-        <v>250.35</v>
+        <v>260.69</v>
       </c>
       <c r="L25" t="n">
-        <v>295.37</v>
+        <v>307.58</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>402.38</v>
+        <v>557.85</v>
       </c>
       <c r="K26" t="n">
-        <v>214.94</v>
+        <v>297.99</v>
       </c>
       <c r="L26" t="n">
-        <v>456.19</v>
+        <v>632.45</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>-218.47</v>
+        <v>-361.39</v>
       </c>
       <c r="K27" t="n">
-        <v>28.5</v>
+        <v>47.14</v>
       </c>
       <c r="L27" t="n">
-        <v>220.32</v>
+        <v>364.45</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-611.8200000000001</v>
+        <v>-624.83</v>
       </c>
       <c r="K28" t="n">
-        <v>-612.38</v>
+        <v>-625.39</v>
       </c>
       <c r="L28" t="n">
-        <v>865.64</v>
+        <v>884.04</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>-9.390000000000001</v>
+        <v>-10.05</v>
       </c>
       <c r="K29" t="n">
-        <v>100.58</v>
+        <v>107.67</v>
       </c>
       <c r="L29" t="n">
-        <v>101.02</v>
+        <v>108.14</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-179.01</v>
+        <v>-218.82</v>
       </c>
       <c r="K30" t="n">
-        <v>11.92</v>
+        <v>14.57</v>
       </c>
       <c r="L30" t="n">
-        <v>179.4</v>
+        <v>219.31</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>27</v>
       </c>
       <c r="J31" t="n">
-        <v>207.35</v>
+        <v>214.02</v>
       </c>
       <c r="K31" t="n">
-        <v>-64.84</v>
+        <v>-66.92</v>
       </c>
       <c r="L31" t="n">
-        <v>217.25</v>
+        <v>224.24</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>28</v>
       </c>
       <c r="J32" t="n">
-        <v>129.74</v>
+        <v>140.85</v>
       </c>
       <c r="K32" t="n">
-        <v>61.35</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>143.51</v>
+        <v>155.8</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>28</v>
       </c>
       <c r="J33" t="n">
-        <v>-2.21</v>
+        <v>-2.1</v>
       </c>
       <c r="K33" t="n">
-        <v>150.62</v>
+        <v>143.35</v>
       </c>
       <c r="L33" t="n">
-        <v>150.64</v>
+        <v>143.36</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>406.89</v>
+        <v>423.21</v>
       </c>
       <c r="K34" t="n">
-        <v>-141.77</v>
+        <v>-147.45</v>
       </c>
       <c r="L34" t="n">
-        <v>430.88</v>
+        <v>448.16</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>-346.23</v>
+        <v>-367.36</v>
       </c>
       <c r="K35" t="n">
-        <v>454.56</v>
+        <v>482.29</v>
       </c>
       <c r="L35" t="n">
-        <v>571.4</v>
+        <v>606.26</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>10.65</v>
+        <v>27.08</v>
       </c>
       <c r="K36" t="n">
-        <v>-69.11</v>
+        <v>-175.66</v>
       </c>
       <c r="L36" t="n">
-        <v>69.93000000000001</v>
+        <v>177.74</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>-99.09999999999999</v>
+        <v>-132.71</v>
       </c>
       <c r="K37" t="n">
-        <v>-175.6</v>
+        <v>-235.16</v>
       </c>
       <c r="L37" t="n">
-        <v>201.64</v>
+        <v>270.02</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>359.99</v>
+        <v>449.74</v>
       </c>
       <c r="K38" t="n">
-        <v>304.13</v>
+        <v>379.95</v>
       </c>
       <c r="L38" t="n">
-        <v>471.26</v>
+        <v>588.76</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>22.23</v>
+        <v>47.4</v>
       </c>
       <c r="K39" t="n">
-        <v>-125.03</v>
+        <v>-266.56</v>
       </c>
       <c r="L39" t="n">
-        <v>126.99</v>
+        <v>270.74</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>246.3</v>
+        <v>311.07</v>
       </c>
       <c r="K40" t="n">
-        <v>65.5</v>
+        <v>82.73</v>
       </c>
       <c r="L40" t="n">
-        <v>254.86</v>
+        <v>321.88</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>-304.21</v>
+        <v>-423.72</v>
       </c>
       <c r="K41" t="n">
-        <v>-224.73</v>
+        <v>-313.01</v>
       </c>
       <c r="L41" t="n">
-        <v>378.22</v>
+        <v>526.8</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>22</v>
       </c>
       <c r="J42" t="n">
-        <v>607.5599999999999</v>
+        <v>828.91</v>
       </c>
       <c r="K42" t="n">
-        <v>-50.75</v>
+        <v>-69.23</v>
       </c>
       <c r="L42" t="n">
-        <v>609.6799999999999</v>
+        <v>831.79</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>161.2</v>
+        <v>282.22</v>
       </c>
       <c r="K43" t="n">
-        <v>-279.58</v>
+        <v>-489.5</v>
       </c>
       <c r="L43" t="n">
-        <v>322.73</v>
+        <v>565.03</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>125.08</v>
+        <v>151.18</v>
       </c>
       <c r="K44" t="n">
-        <v>-116.23</v>
+        <v>-140.47</v>
       </c>
       <c r="L44" t="n">
-        <v>170.75</v>
+        <v>206.37</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>104.79</v>
+        <v>138.1</v>
       </c>
       <c r="K45" t="n">
-        <v>48.99</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>115.68</v>
+        <v>152.45</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>302.91</v>
+        <v>264.33</v>
       </c>
       <c r="K46" t="n">
-        <v>128.89</v>
+        <v>112.48</v>
       </c>
       <c r="L46" t="n">
-        <v>329.19</v>
+        <v>287.26</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>-110.03</v>
+        <v>-142.57</v>
       </c>
       <c r="K47" t="n">
-        <v>39.1</v>
+        <v>50.66</v>
       </c>
       <c r="L47" t="n">
-        <v>116.77</v>
+        <v>151.3</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>17.9</v>
+        <v>18.29</v>
       </c>
       <c r="K48" t="n">
-        <v>337.07</v>
+        <v>344.54</v>
       </c>
       <c r="L48" t="n">
-        <v>337.55</v>
+        <v>345.03</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>59.36</v>
+        <v>81.04000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>-111.29</v>
+        <v>-151.93</v>
       </c>
       <c r="L49" t="n">
-        <v>126.13</v>
+        <v>172.19</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>-372.87</v>
+        <v>-401.8</v>
       </c>
       <c r="K50" t="n">
-        <v>-139.2</v>
+        <v>-150</v>
       </c>
       <c r="L50" t="n">
-        <v>398.01</v>
+        <v>428.88</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-137.06</v>
+        <v>-270.9</v>
       </c>
       <c r="K51" t="n">
-        <v>49.36</v>
+        <v>97.56</v>
       </c>
       <c r="L51" t="n">
-        <v>145.67</v>
+        <v>287.93</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>28</v>
       </c>
       <c r="J52" t="n">
-        <v>106.34</v>
+        <v>116.76</v>
       </c>
       <c r="K52" t="n">
-        <v>234.97</v>
+        <v>257.98</v>
       </c>
       <c r="L52" t="n">
-        <v>257.91</v>
+        <v>283.18</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>-822.41</v>
+        <v>-834.5700000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>-490.38</v>
+        <v>-497.63</v>
       </c>
       <c r="L53" t="n">
-        <v>957.52</v>
+        <v>971.67</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>27</v>
       </c>
       <c r="J54" t="n">
-        <v>334.16</v>
+        <v>397.58</v>
       </c>
       <c r="K54" t="n">
-        <v>-192.3</v>
+        <v>-228.8</v>
       </c>
       <c r="L54" t="n">
-        <v>385.55</v>
+        <v>458.72</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>-81.61</v>
+        <v>-166.01</v>
       </c>
       <c r="K55" t="n">
-        <v>144.64</v>
+        <v>294.24</v>
       </c>
       <c r="L55" t="n">
-        <v>166.08</v>
+        <v>337.84</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>195.19</v>
+        <v>241.21</v>
       </c>
       <c r="K56" t="n">
-        <v>439.97</v>
+        <v>543.6900000000001</v>
       </c>
       <c r="L56" t="n">
-        <v>481.32</v>
+        <v>594.8</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>-409.48</v>
+        <v>-529.33</v>
       </c>
       <c r="K57" t="n">
-        <v>-62.14</v>
+        <v>-80.33</v>
       </c>
       <c r="L57" t="n">
-        <v>414.16</v>
+        <v>535.39</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>327.44</v>
+        <v>424.58</v>
       </c>
       <c r="K58" t="n">
-        <v>-412.82</v>
+        <v>-535.28</v>
       </c>
       <c r="L58" t="n">
-        <v>526.91</v>
+        <v>683.22</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>289.15</v>
+        <v>301.59</v>
       </c>
       <c r="K59" t="n">
-        <v>14.9</v>
+        <v>15.54</v>
       </c>
       <c r="L59" t="n">
-        <v>289.53</v>
+        <v>301.99</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>202.07</v>
+        <v>195.85</v>
       </c>
       <c r="K60" t="n">
-        <v>80.01000000000001</v>
+        <v>77.55</v>
       </c>
       <c r="L60" t="n">
-        <v>217.33</v>
+        <v>210.64</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>203.21</v>
+        <v>228.2</v>
       </c>
       <c r="K61" t="n">
-        <v>129.64</v>
+        <v>145.59</v>
       </c>
       <c r="L61" t="n">
-        <v>241.04</v>
+        <v>270.69</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>134.87</v>
+        <v>132.05</v>
       </c>
       <c r="K62" t="n">
-        <v>-107.08</v>
+        <v>-104.84</v>
       </c>
       <c r="L62" t="n">
-        <v>172.2</v>
+        <v>168.61</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>-22.85</v>
+        <v>-38.62</v>
       </c>
       <c r="K63" t="n">
-        <v>68.56999999999999</v>
+        <v>115.89</v>
       </c>
       <c r="L63" t="n">
-        <v>72.28</v>
+        <v>122.16</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>332.57</v>
+        <v>319.43</v>
       </c>
       <c r="K64" t="n">
-        <v>-115.71</v>
+        <v>-111.14</v>
       </c>
       <c r="L64" t="n">
-        <v>352.12</v>
+        <v>338.21</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>-217.65</v>
+        <v>-265.52</v>
       </c>
       <c r="K65" t="n">
-        <v>-121.08</v>
+        <v>-147.72</v>
       </c>
       <c r="L65" t="n">
-        <v>249.06</v>
+        <v>303.85</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>283.39</v>
+        <v>327.88</v>
       </c>
       <c r="K66" t="n">
-        <v>-56.74</v>
+        <v>-65.64</v>
       </c>
       <c r="L66" t="n">
-        <v>289.01</v>
+        <v>334.38</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>-347.01</v>
+        <v>-311.08</v>
       </c>
       <c r="K67" t="n">
-        <v>-458.79</v>
+        <v>-411.29</v>
       </c>
       <c r="L67" t="n">
-        <v>575.25</v>
+        <v>515.6799999999999</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>605.75</v>
+        <v>786.98</v>
       </c>
       <c r="K68" t="n">
-        <v>-239.61</v>
+        <v>-311.3</v>
       </c>
       <c r="L68" t="n">
-        <v>651.42</v>
+        <v>846.3099999999999</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>-362.85</v>
+        <v>-442.51</v>
       </c>
       <c r="K69" t="n">
-        <v>134.26</v>
+        <v>163.74</v>
       </c>
       <c r="L69" t="n">
-        <v>386.89</v>
+        <v>471.83</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>344.08</v>
+        <v>357.36</v>
       </c>
       <c r="K70" t="n">
-        <v>-1271.56</v>
+        <v>-1320.65</v>
       </c>
       <c r="L70" t="n">
-        <v>1317.29</v>
+        <v>1368.15</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>291.61</v>
+        <v>487.63</v>
       </c>
       <c r="K71" t="n">
-        <v>331.33</v>
+        <v>554.05</v>
       </c>
       <c r="L71" t="n">
-        <v>441.38</v>
+        <v>738.0700000000001</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>703.62</v>
+        <v>775.27</v>
       </c>
       <c r="K72" t="n">
-        <v>470.98</v>
+        <v>518.9400000000001</v>
       </c>
       <c r="L72" t="n">
-        <v>846.7</v>
+        <v>932.92</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-442.06</v>
+        <v>-613.8</v>
       </c>
       <c r="K73" t="n">
-        <v>-110</v>
+        <v>-152.73</v>
       </c>
       <c r="L73" t="n">
-        <v>455.54</v>
+        <v>632.52</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>-149.32</v>
+        <v>-149.62</v>
       </c>
       <c r="K74" t="n">
-        <v>-240.78</v>
+        <v>-241.27</v>
       </c>
       <c r="L74" t="n">
-        <v>283.32</v>
+        <v>283.9</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>452.42</v>
+        <v>403.28</v>
       </c>
       <c r="K75" t="n">
-        <v>-257.13</v>
+        <v>-229.21</v>
       </c>
       <c r="L75" t="n">
-        <v>520.38</v>
+        <v>463.87</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>-89.56999999999999</v>
+        <v>-93.44</v>
       </c>
       <c r="K76" t="n">
-        <v>-66.92</v>
+        <v>-69.81</v>
       </c>
       <c r="L76" t="n">
-        <v>111.81</v>
+        <v>116.64</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-176.11</v>
+        <v>-199.96</v>
       </c>
       <c r="K77" t="n">
-        <v>-203.49</v>
+        <v>-231.06</v>
       </c>
       <c r="L77" t="n">
-        <v>269.12</v>
+        <v>305.57</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>28</v>
       </c>
       <c r="J78" t="n">
-        <v>226.18</v>
+        <v>194.03</v>
       </c>
       <c r="K78" t="n">
-        <v>-372.13</v>
+        <v>-319.23</v>
       </c>
       <c r="L78" t="n">
-        <v>435.47</v>
+        <v>373.57</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>321.51</v>
+        <v>328.21</v>
       </c>
       <c r="K79" t="n">
-        <v>-17.67</v>
+        <v>-18.04</v>
       </c>
       <c r="L79" t="n">
-        <v>321.99</v>
+        <v>328.71</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>394.7</v>
+        <v>492.73</v>
       </c>
       <c r="K80" t="n">
-        <v>50.47</v>
+        <v>63</v>
       </c>
       <c r="L80" t="n">
-        <v>397.91</v>
+        <v>496.74</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>140.69</v>
+        <v>164.7</v>
       </c>
       <c r="K81" t="n">
-        <v>-246.54</v>
+        <v>-288.63</v>
       </c>
       <c r="L81" t="n">
-        <v>283.85</v>
+        <v>332.32</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-358.2</v>
+        <v>-409.48</v>
       </c>
       <c r="K82" t="n">
-        <v>159.22</v>
+        <v>182.02</v>
       </c>
       <c r="L82" t="n">
-        <v>391.99</v>
+        <v>448.11</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>222.1</v>
+        <v>262.39</v>
       </c>
       <c r="K83" t="n">
-        <v>-538.98</v>
+        <v>-636.75</v>
       </c>
       <c r="L83" t="n">
-        <v>582.9400000000001</v>
+        <v>688.6900000000001</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>-39.08</v>
+        <v>-61.16</v>
       </c>
       <c r="K84" t="n">
-        <v>-210.21</v>
+        <v>-328.99</v>
       </c>
       <c r="L84" t="n">
-        <v>213.81</v>
+        <v>334.62</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>3.63</v>
+        <v>5.12</v>
       </c>
       <c r="K85" t="n">
-        <v>475.9</v>
+        <v>671.13</v>
       </c>
       <c r="L85" t="n">
-        <v>475.92</v>
+        <v>671.15</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>204.97</v>
+        <v>342.13</v>
       </c>
       <c r="K86" t="n">
-        <v>-305.22</v>
+        <v>-509.48</v>
       </c>
       <c r="L86" t="n">
-        <v>367.65</v>
+        <v>613.6900000000001</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>483.62</v>
+        <v>696.28</v>
       </c>
       <c r="K87" t="n">
-        <v>356.74</v>
+        <v>513.61</v>
       </c>
       <c r="L87" t="n">
-        <v>600.96</v>
+        <v>865.22</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>469.5</v>
+        <v>501.07</v>
       </c>
       <c r="K88" t="n">
-        <v>718.33</v>
+        <v>766.63</v>
       </c>
       <c r="L88" t="n">
-        <v>858.15</v>
+        <v>915.85</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-06.xlsx
+++ b/output/2024-07-06.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-174.39</v>
+        <v>-127.68</v>
       </c>
       <c r="K14" t="n">
-        <v>66.8</v>
+        <v>48.9</v>
       </c>
       <c r="L14" t="n">
-        <v>186.74</v>
+        <v>136.73</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>28</v>
       </c>
       <c r="J15" t="n">
-        <v>-141.22</v>
+        <v>-128.49</v>
       </c>
       <c r="K15" t="n">
-        <v>-40.06</v>
+        <v>-36.45</v>
       </c>
       <c r="L15" t="n">
-        <v>146.79</v>
+        <v>133.56</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>-70.77</v>
+        <v>-53.67</v>
       </c>
       <c r="K16" t="n">
-        <v>360.99</v>
+        <v>273.76</v>
       </c>
       <c r="L16" t="n">
-        <v>367.87</v>
+        <v>278.97</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>28</v>
       </c>
       <c r="J17" t="n">
-        <v>103.93</v>
+        <v>91.31</v>
       </c>
       <c r="K17" t="n">
-        <v>107.82</v>
+        <v>94.72</v>
       </c>
       <c r="L17" t="n">
-        <v>149.76</v>
+        <v>131.57</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>79.88</v>
+        <v>65.23999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>-58.21</v>
+        <v>-47.54</v>
       </c>
       <c r="L18" t="n">
-        <v>98.84999999999999</v>
+        <v>80.73</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-221.38</v>
+        <v>-173.96</v>
       </c>
       <c r="K19" t="n">
-        <v>78.8</v>
+        <v>61.92</v>
       </c>
       <c r="L19" t="n">
-        <v>234.99</v>
+        <v>184.65</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>320.31</v>
+        <v>200.56</v>
       </c>
       <c r="K20" t="n">
-        <v>372.82</v>
+        <v>233.45</v>
       </c>
       <c r="L20" t="n">
-        <v>491.52</v>
+        <v>307.77</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>28</v>
       </c>
       <c r="J21" t="n">
-        <v>49.37</v>
+        <v>38.68</v>
       </c>
       <c r="K21" t="n">
-        <v>-238.24</v>
+        <v>-186.63</v>
       </c>
       <c r="L21" t="n">
-        <v>243.3</v>
+        <v>190.6</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>195.87</v>
+        <v>138.2</v>
       </c>
       <c r="K22" t="n">
-        <v>-162.11</v>
+        <v>-114.37</v>
       </c>
       <c r="L22" t="n">
-        <v>254.26</v>
+        <v>179.39</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>-92.48</v>
+        <v>-57.56</v>
       </c>
       <c r="K23" t="n">
-        <v>556.86</v>
+        <v>346.59</v>
       </c>
       <c r="L23" t="n">
-        <v>564.48</v>
+        <v>351.34</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>-7.28</v>
+        <v>-4.25</v>
       </c>
       <c r="K24" t="n">
-        <v>425.86</v>
+        <v>248.84</v>
       </c>
       <c r="L24" t="n">
-        <v>425.92</v>
+        <v>248.88</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>163.23</v>
+        <v>113.3</v>
       </c>
       <c r="K25" t="n">
-        <v>260.69</v>
+        <v>180.96</v>
       </c>
       <c r="L25" t="n">
-        <v>307.58</v>
+        <v>213.51</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>557.85</v>
+        <v>282.85</v>
       </c>
       <c r="K26" t="n">
-        <v>297.99</v>
+        <v>151.09</v>
       </c>
       <c r="L26" t="n">
-        <v>632.45</v>
+        <v>320.68</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>-361.39</v>
+        <v>-212.81</v>
       </c>
       <c r="K27" t="n">
-        <v>47.14</v>
+        <v>27.76</v>
       </c>
       <c r="L27" t="n">
-        <v>364.45</v>
+        <v>214.62</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-624.83</v>
+        <v>-355.04</v>
       </c>
       <c r="K28" t="n">
-        <v>-625.39</v>
+        <v>-355.36</v>
       </c>
       <c r="L28" t="n">
-        <v>884.04</v>
+        <v>502.33</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>-10.05</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>107.67</v>
+        <v>96.04000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>108.14</v>
+        <v>96.45</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-218.82</v>
+        <v>-154.51</v>
       </c>
       <c r="K30" t="n">
-        <v>14.57</v>
+        <v>10.29</v>
       </c>
       <c r="L30" t="n">
-        <v>219.31</v>
+        <v>154.85</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>27</v>
       </c>
       <c r="J31" t="n">
-        <v>214.02</v>
+        <v>177.73</v>
       </c>
       <c r="K31" t="n">
-        <v>-66.92</v>
+        <v>-55.57</v>
       </c>
       <c r="L31" t="n">
-        <v>224.24</v>
+        <v>186.21</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>28</v>
       </c>
       <c r="J32" t="n">
-        <v>140.85</v>
+        <v>121.14</v>
       </c>
       <c r="K32" t="n">
-        <v>66.59999999999999</v>
+        <v>57.28</v>
       </c>
       <c r="L32" t="n">
-        <v>155.8</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>28</v>
       </c>
       <c r="J33" t="n">
-        <v>-2.1</v>
+        <v>-1.87</v>
       </c>
       <c r="K33" t="n">
-        <v>143.35</v>
+        <v>127.44</v>
       </c>
       <c r="L33" t="n">
-        <v>143.36</v>
+        <v>127.46</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>423.21</v>
+        <v>291.06</v>
       </c>
       <c r="K34" t="n">
-        <v>-147.45</v>
+        <v>-101.41</v>
       </c>
       <c r="L34" t="n">
-        <v>448.16</v>
+        <v>308.22</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>-367.36</v>
+        <v>-230.1</v>
       </c>
       <c r="K35" t="n">
-        <v>482.29</v>
+        <v>302.09</v>
       </c>
       <c r="L35" t="n">
-        <v>606.26</v>
+        <v>379.74</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>27.08</v>
+        <v>18.29</v>
       </c>
       <c r="K36" t="n">
-        <v>-175.66</v>
+        <v>-118.67</v>
       </c>
       <c r="L36" t="n">
-        <v>177.74</v>
+        <v>120.07</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>-132.71</v>
+        <v>-83.48</v>
       </c>
       <c r="K37" t="n">
-        <v>-235.16</v>
+        <v>-147.93</v>
       </c>
       <c r="L37" t="n">
-        <v>270.02</v>
+        <v>169.86</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>449.74</v>
+        <v>239.54</v>
       </c>
       <c r="K38" t="n">
-        <v>379.95</v>
+        <v>202.37</v>
       </c>
       <c r="L38" t="n">
-        <v>588.76</v>
+        <v>313.58</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>47.4</v>
+        <v>26.99</v>
       </c>
       <c r="K39" t="n">
-        <v>-266.56</v>
+        <v>-151.78</v>
       </c>
       <c r="L39" t="n">
-        <v>270.74</v>
+        <v>154.16</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>311.07</v>
+        <v>195.03</v>
       </c>
       <c r="K40" t="n">
-        <v>82.73</v>
+        <v>51.87</v>
       </c>
       <c r="L40" t="n">
-        <v>321.88</v>
+        <v>201.81</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>-423.72</v>
+        <v>-251.96</v>
       </c>
       <c r="K41" t="n">
-        <v>-313.01</v>
+        <v>-186.13</v>
       </c>
       <c r="L41" t="n">
-        <v>526.8</v>
+        <v>313.25</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>22</v>
       </c>
       <c r="J42" t="n">
-        <v>828.91</v>
+        <v>400.96</v>
       </c>
       <c r="K42" t="n">
-        <v>-69.23</v>
+        <v>-33.49</v>
       </c>
       <c r="L42" t="n">
-        <v>831.79</v>
+        <v>402.36</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>282.22</v>
+        <v>143.52</v>
       </c>
       <c r="K43" t="n">
-        <v>-489.5</v>
+        <v>-248.92</v>
       </c>
       <c r="L43" t="n">
-        <v>565.03</v>
+        <v>287.33</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>151.18</v>
+        <v>110.48</v>
       </c>
       <c r="K44" t="n">
-        <v>-140.47</v>
+        <v>-102.66</v>
       </c>
       <c r="L44" t="n">
-        <v>206.37</v>
+        <v>150.82</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>138.1</v>
+        <v>105.68</v>
       </c>
       <c r="K45" t="n">
-        <v>64.56999999999999</v>
+        <v>49.41</v>
       </c>
       <c r="L45" t="n">
-        <v>152.45</v>
+        <v>116.66</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>264.33</v>
+        <v>216.54</v>
       </c>
       <c r="K46" t="n">
-        <v>112.48</v>
+        <v>92.14</v>
       </c>
       <c r="L46" t="n">
-        <v>287.26</v>
+        <v>235.33</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>-142.57</v>
+        <v>-112.99</v>
       </c>
       <c r="K47" t="n">
-        <v>50.66</v>
+        <v>40.15</v>
       </c>
       <c r="L47" t="n">
-        <v>151.3</v>
+        <v>119.91</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>18.29</v>
+        <v>13.13</v>
       </c>
       <c r="K48" t="n">
-        <v>344.54</v>
+        <v>247.28</v>
       </c>
       <c r="L48" t="n">
-        <v>345.03</v>
+        <v>247.63</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>81.04000000000001</v>
+        <v>62.86</v>
       </c>
       <c r="K49" t="n">
-        <v>-151.93</v>
+        <v>-117.83</v>
       </c>
       <c r="L49" t="n">
-        <v>172.19</v>
+        <v>133.55</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>-401.8</v>
+        <v>-257.34</v>
       </c>
       <c r="K50" t="n">
-        <v>-150</v>
+        <v>-96.06999999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>428.88</v>
+        <v>274.69</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-270.9</v>
+        <v>-158.05</v>
       </c>
       <c r="K51" t="n">
-        <v>97.56</v>
+        <v>56.92</v>
       </c>
       <c r="L51" t="n">
-        <v>287.93</v>
+        <v>167.99</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>28</v>
       </c>
       <c r="J52" t="n">
-        <v>116.76</v>
+        <v>87.16</v>
       </c>
       <c r="K52" t="n">
-        <v>257.98</v>
+        <v>192.58</v>
       </c>
       <c r="L52" t="n">
-        <v>283.18</v>
+        <v>211.39</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>-834.5700000000001</v>
+        <v>-483</v>
       </c>
       <c r="K53" t="n">
-        <v>-497.63</v>
+        <v>-288</v>
       </c>
       <c r="L53" t="n">
-        <v>971.67</v>
+        <v>562.34</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>27</v>
       </c>
       <c r="J54" t="n">
-        <v>397.58</v>
+        <v>250.47</v>
       </c>
       <c r="K54" t="n">
-        <v>-228.8</v>
+        <v>-144.14</v>
       </c>
       <c r="L54" t="n">
-        <v>458.72</v>
+        <v>288.99</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>-166.01</v>
+        <v>-95.34</v>
       </c>
       <c r="K55" t="n">
-        <v>294.24</v>
+        <v>168.98</v>
       </c>
       <c r="L55" t="n">
-        <v>337.84</v>
+        <v>194.02</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>241.21</v>
+        <v>140.61</v>
       </c>
       <c r="K56" t="n">
-        <v>543.6900000000001</v>
+        <v>316.94</v>
       </c>
       <c r="L56" t="n">
-        <v>594.8</v>
+        <v>346.73</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>-529.33</v>
+        <v>-309.65</v>
       </c>
       <c r="K57" t="n">
-        <v>-80.33</v>
+        <v>-46.99</v>
       </c>
       <c r="L57" t="n">
-        <v>535.39</v>
+        <v>313.19</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>424.58</v>
+        <v>240.84</v>
       </c>
       <c r="K58" t="n">
-        <v>-535.28</v>
+        <v>-303.63</v>
       </c>
       <c r="L58" t="n">
-        <v>683.22</v>
+        <v>387.55</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>301.59</v>
+        <v>213.22</v>
       </c>
       <c r="K59" t="n">
-        <v>15.54</v>
+        <v>10.98</v>
       </c>
       <c r="L59" t="n">
-        <v>301.99</v>
+        <v>213.5</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>195.85</v>
+        <v>171.2</v>
       </c>
       <c r="K60" t="n">
-        <v>77.55</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="L60" t="n">
-        <v>210.64</v>
+        <v>184.13</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>228.2</v>
+        <v>168.45</v>
       </c>
       <c r="K61" t="n">
-        <v>145.59</v>
+        <v>107.47</v>
       </c>
       <c r="L61" t="n">
-        <v>270.69</v>
+        <v>199.82</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>132.05</v>
+        <v>114.79</v>
       </c>
       <c r="K62" t="n">
-        <v>-104.84</v>
+        <v>-91.13</v>
       </c>
       <c r="L62" t="n">
-        <v>168.61</v>
+        <v>146.56</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>-38.62</v>
+        <v>-32.56</v>
       </c>
       <c r="K63" t="n">
-        <v>115.89</v>
+        <v>97.73</v>
       </c>
       <c r="L63" t="n">
-        <v>122.16</v>
+        <v>103.01</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>319.43</v>
+        <v>232.8</v>
       </c>
       <c r="K64" t="n">
-        <v>-111.14</v>
+        <v>-81</v>
       </c>
       <c r="L64" t="n">
-        <v>338.21</v>
+        <v>246.49</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>-265.52</v>
+        <v>-186.73</v>
       </c>
       <c r="K65" t="n">
-        <v>-147.72</v>
+        <v>-103.88</v>
       </c>
       <c r="L65" t="n">
-        <v>303.85</v>
+        <v>213.68</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>327.88</v>
+        <v>230.35</v>
       </c>
       <c r="K66" t="n">
-        <v>-65.64</v>
+        <v>-46.12</v>
       </c>
       <c r="L66" t="n">
-        <v>334.38</v>
+        <v>234.92</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>-311.08</v>
+        <v>-229.75</v>
       </c>
       <c r="K67" t="n">
-        <v>-411.29</v>
+        <v>-303.76</v>
       </c>
       <c r="L67" t="n">
-        <v>515.6799999999999</v>
+        <v>380.87</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>786.98</v>
+        <v>404.73</v>
       </c>
       <c r="K68" t="n">
-        <v>-311.3</v>
+        <v>-160.09</v>
       </c>
       <c r="L68" t="n">
-        <v>846.3099999999999</v>
+        <v>435.24</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>-442.51</v>
+        <v>-286.38</v>
       </c>
       <c r="K69" t="n">
-        <v>163.74</v>
+        <v>105.97</v>
       </c>
       <c r="L69" t="n">
-        <v>471.83</v>
+        <v>305.36</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>357.36</v>
+        <v>191.48</v>
       </c>
       <c r="K70" t="n">
-        <v>-1320.65</v>
+        <v>-707.62</v>
       </c>
       <c r="L70" t="n">
-        <v>1368.15</v>
+        <v>733.0700000000001</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>487.63</v>
+        <v>241.09</v>
       </c>
       <c r="K71" t="n">
-        <v>554.05</v>
+        <v>273.93</v>
       </c>
       <c r="L71" t="n">
-        <v>738.0700000000001</v>
+        <v>364.92</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>775.27</v>
+        <v>442.22</v>
       </c>
       <c r="K72" t="n">
-        <v>518.9400000000001</v>
+        <v>296.01</v>
       </c>
       <c r="L72" t="n">
-        <v>932.92</v>
+        <v>532.14</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-613.8</v>
+        <v>-328.13</v>
       </c>
       <c r="K73" t="n">
-        <v>-152.73</v>
+        <v>-81.65000000000001</v>
       </c>
       <c r="L73" t="n">
-        <v>632.52</v>
+        <v>338.14</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>-149.62</v>
+        <v>-109.68</v>
       </c>
       <c r="K74" t="n">
-        <v>-241.27</v>
+        <v>-176.87</v>
       </c>
       <c r="L74" t="n">
-        <v>283.9</v>
+        <v>208.12</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>403.28</v>
+        <v>301.32</v>
       </c>
       <c r="K75" t="n">
-        <v>-229.21</v>
+        <v>-171.25</v>
       </c>
       <c r="L75" t="n">
-        <v>463.87</v>
+        <v>346.58</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>-93.44</v>
+        <v>-85.53</v>
       </c>
       <c r="K76" t="n">
-        <v>-69.81</v>
+        <v>-63.89</v>
       </c>
       <c r="L76" t="n">
-        <v>116.64</v>
+        <v>106.76</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-199.96</v>
+        <v>-138.2</v>
       </c>
       <c r="K77" t="n">
-        <v>-231.06</v>
+        <v>-159.69</v>
       </c>
       <c r="L77" t="n">
-        <v>305.57</v>
+        <v>211.19</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>28</v>
       </c>
       <c r="J78" t="n">
-        <v>194.03</v>
+        <v>162.27</v>
       </c>
       <c r="K78" t="n">
-        <v>-319.23</v>
+        <v>-266.99</v>
       </c>
       <c r="L78" t="n">
-        <v>373.57</v>
+        <v>312.44</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>328.21</v>
+        <v>251.36</v>
       </c>
       <c r="K79" t="n">
-        <v>-18.04</v>
+        <v>-13.81</v>
       </c>
       <c r="L79" t="n">
-        <v>328.71</v>
+        <v>251.74</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>492.73</v>
+        <v>301.45</v>
       </c>
       <c r="K80" t="n">
-        <v>63</v>
+        <v>38.55</v>
       </c>
       <c r="L80" t="n">
-        <v>496.74</v>
+        <v>303.9</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>164.7</v>
+        <v>106.07</v>
       </c>
       <c r="K81" t="n">
-        <v>-288.63</v>
+        <v>-185.87</v>
       </c>
       <c r="L81" t="n">
-        <v>332.32</v>
+        <v>214.01</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-409.48</v>
+        <v>-264</v>
       </c>
       <c r="K82" t="n">
-        <v>182.02</v>
+        <v>117.35</v>
       </c>
       <c r="L82" t="n">
-        <v>448.11</v>
+        <v>288.91</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>262.39</v>
+        <v>155.05</v>
       </c>
       <c r="K83" t="n">
-        <v>-636.75</v>
+        <v>-376.26</v>
       </c>
       <c r="L83" t="n">
-        <v>688.6900000000001</v>
+        <v>406.96</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>-61.16</v>
+        <v>-39.58</v>
       </c>
       <c r="K84" t="n">
-        <v>-328.99</v>
+        <v>-212.91</v>
       </c>
       <c r="L84" t="n">
-        <v>334.62</v>
+        <v>216.56</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>5.12</v>
+        <v>2.86</v>
       </c>
       <c r="K85" t="n">
-        <v>671.13</v>
+        <v>374.48</v>
       </c>
       <c r="L85" t="n">
-        <v>671.15</v>
+        <v>374.5</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>342.13</v>
+        <v>172.6</v>
       </c>
       <c r="K86" t="n">
-        <v>-509.48</v>
+        <v>-257.02</v>
       </c>
       <c r="L86" t="n">
-        <v>613.6900000000001</v>
+        <v>309.59</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>696.28</v>
+        <v>345.59</v>
       </c>
       <c r="K87" t="n">
-        <v>513.61</v>
+        <v>254.92</v>
       </c>
       <c r="L87" t="n">
-        <v>865.22</v>
+        <v>429.43</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>501.07</v>
+        <v>280.59</v>
       </c>
       <c r="K88" t="n">
-        <v>766.63</v>
+        <v>429.29</v>
       </c>
       <c r="L88" t="n">
-        <v>915.85</v>
+        <v>512.86</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-06.xlsx
+++ b/output/2024-07-06.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-127.68</v>
+        <v>-127.12</v>
       </c>
       <c r="K14" t="n">
-        <v>48.9</v>
+        <v>48.69</v>
       </c>
       <c r="L14" t="n">
-        <v>136.73</v>
+        <v>136.13</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>28</v>
       </c>
       <c r="J15" t="n">
-        <v>-128.49</v>
+        <v>-124.4</v>
       </c>
       <c r="K15" t="n">
-        <v>-36.45</v>
+        <v>-35.29</v>
       </c>
       <c r="L15" t="n">
-        <v>133.56</v>
+        <v>129.31</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>-53.67</v>
+        <v>-53.18</v>
       </c>
       <c r="K16" t="n">
-        <v>273.76</v>
+        <v>271.25</v>
       </c>
       <c r="L16" t="n">
-        <v>278.97</v>
+        <v>276.42</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>28</v>
       </c>
       <c r="J17" t="n">
-        <v>91.31</v>
+        <v>90.01000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>94.72</v>
+        <v>93.37</v>
       </c>
       <c r="L17" t="n">
-        <v>131.57</v>
+        <v>129.69</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>65.23999999999999</v>
+        <v>64.36</v>
       </c>
       <c r="K18" t="n">
-        <v>-47.54</v>
+        <v>-46.9</v>
       </c>
       <c r="L18" t="n">
-        <v>80.73</v>
+        <v>79.63</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-173.96</v>
+        <v>-177.58</v>
       </c>
       <c r="K19" t="n">
-        <v>61.92</v>
+        <v>63.21</v>
       </c>
       <c r="L19" t="n">
-        <v>184.65</v>
+        <v>188.5</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>200.56</v>
+        <v>209.55</v>
       </c>
       <c r="K20" t="n">
-        <v>233.45</v>
+        <v>243.91</v>
       </c>
       <c r="L20" t="n">
-        <v>307.77</v>
+        <v>321.56</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>28</v>
       </c>
       <c r="J21" t="n">
-        <v>38.68</v>
+        <v>39.73</v>
       </c>
       <c r="K21" t="n">
-        <v>-186.63</v>
+        <v>-191.71</v>
       </c>
       <c r="L21" t="n">
-        <v>190.6</v>
+        <v>195.79</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>138.2</v>
+        <v>144.01</v>
       </c>
       <c r="K22" t="n">
-        <v>-114.37</v>
+        <v>-119.19</v>
       </c>
       <c r="L22" t="n">
-        <v>179.39</v>
+        <v>186.94</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>-57.56</v>
+        <v>-60.53</v>
       </c>
       <c r="K23" t="n">
-        <v>346.59</v>
+        <v>364.47</v>
       </c>
       <c r="L23" t="n">
-        <v>351.34</v>
+        <v>369.47</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.25</v>
+        <v>-4.54</v>
       </c>
       <c r="K24" t="n">
-        <v>248.84</v>
+        <v>265.56</v>
       </c>
       <c r="L24" t="n">
-        <v>248.88</v>
+        <v>265.59</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>113.3</v>
+        <v>118.96</v>
       </c>
       <c r="K25" t="n">
-        <v>180.96</v>
+        <v>189.99</v>
       </c>
       <c r="L25" t="n">
-        <v>213.51</v>
+        <v>224.16</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>282.85</v>
+        <v>309.85</v>
       </c>
       <c r="K26" t="n">
-        <v>151.09</v>
+        <v>165.51</v>
       </c>
       <c r="L26" t="n">
-        <v>320.68</v>
+        <v>351.29</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>-212.81</v>
+        <v>-227.11</v>
       </c>
       <c r="K27" t="n">
-        <v>27.76</v>
+        <v>29.62</v>
       </c>
       <c r="L27" t="n">
-        <v>214.62</v>
+        <v>229.03</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-355.04</v>
+        <v>-382.12</v>
       </c>
       <c r="K28" t="n">
-        <v>-355.36</v>
+        <v>-382.47</v>
       </c>
       <c r="L28" t="n">
-        <v>502.33</v>
+        <v>540.65</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>-8.970000000000001</v>
+        <v>-8.59</v>
       </c>
       <c r="K29" t="n">
-        <v>96.04000000000001</v>
+        <v>91.98</v>
       </c>
       <c r="L29" t="n">
-        <v>96.45</v>
+        <v>92.38</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-154.51</v>
+        <v>-153.46</v>
       </c>
       <c r="K30" t="n">
-        <v>10.29</v>
+        <v>10.22</v>
       </c>
       <c r="L30" t="n">
-        <v>154.85</v>
+        <v>153.8</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>27</v>
       </c>
       <c r="J31" t="n">
-        <v>177.73</v>
+        <v>173.93</v>
       </c>
       <c r="K31" t="n">
-        <v>-55.57</v>
+        <v>-54.38</v>
       </c>
       <c r="L31" t="n">
-        <v>186.21</v>
+        <v>182.23</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>28</v>
       </c>
       <c r="J32" t="n">
-        <v>121.14</v>
+        <v>120.16</v>
       </c>
       <c r="K32" t="n">
-        <v>57.28</v>
+        <v>56.82</v>
       </c>
       <c r="L32" t="n">
-        <v>134</v>
+        <v>132.91</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>28</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.87</v>
+        <v>-1.86</v>
       </c>
       <c r="K33" t="n">
-        <v>127.44</v>
+        <v>126.85</v>
       </c>
       <c r="L33" t="n">
-        <v>127.46</v>
+        <v>126.86</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>291.06</v>
+        <v>294.01</v>
       </c>
       <c r="K34" t="n">
-        <v>-101.41</v>
+        <v>-102.44</v>
       </c>
       <c r="L34" t="n">
-        <v>308.22</v>
+        <v>311.34</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>-230.1</v>
+        <v>-240.39</v>
       </c>
       <c r="K35" t="n">
-        <v>302.09</v>
+        <v>315.59</v>
       </c>
       <c r="L35" t="n">
-        <v>379.74</v>
+        <v>396.72</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>18.29</v>
+        <v>18.96</v>
       </c>
       <c r="K36" t="n">
-        <v>-118.67</v>
+        <v>-122.99</v>
       </c>
       <c r="L36" t="n">
-        <v>120.07</v>
+        <v>124.44</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>-83.48</v>
+        <v>-87.62</v>
       </c>
       <c r="K37" t="n">
-        <v>-147.93</v>
+        <v>-155.26</v>
       </c>
       <c r="L37" t="n">
-        <v>169.86</v>
+        <v>178.28</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>239.54</v>
+        <v>258.76</v>
       </c>
       <c r="K38" t="n">
-        <v>202.37</v>
+        <v>218.61</v>
       </c>
       <c r="L38" t="n">
-        <v>313.58</v>
+        <v>338.75</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>26.99</v>
+        <v>28.88</v>
       </c>
       <c r="K39" t="n">
-        <v>-151.78</v>
+        <v>-162.4</v>
       </c>
       <c r="L39" t="n">
-        <v>154.16</v>
+        <v>164.95</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>195.03</v>
+        <v>205.5</v>
       </c>
       <c r="K40" t="n">
-        <v>51.87</v>
+        <v>54.65</v>
       </c>
       <c r="L40" t="n">
-        <v>201.81</v>
+        <v>212.64</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>-251.96</v>
+        <v>-272.27</v>
       </c>
       <c r="K41" t="n">
-        <v>-186.13</v>
+        <v>-201.13</v>
       </c>
       <c r="L41" t="n">
-        <v>313.25</v>
+        <v>338.5</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>22</v>
       </c>
       <c r="J42" t="n">
-        <v>400.96</v>
+        <v>438.71</v>
       </c>
       <c r="K42" t="n">
-        <v>-33.49</v>
+        <v>-36.64</v>
       </c>
       <c r="L42" t="n">
-        <v>402.36</v>
+        <v>440.24</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>143.52</v>
+        <v>158.2</v>
       </c>
       <c r="K43" t="n">
-        <v>-248.92</v>
+        <v>-274.39</v>
       </c>
       <c r="L43" t="n">
-        <v>287.33</v>
+        <v>316.73</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>110.48</v>
+        <v>110.21</v>
       </c>
       <c r="K44" t="n">
-        <v>-102.66</v>
+        <v>-102.4</v>
       </c>
       <c r="L44" t="n">
-        <v>150.82</v>
+        <v>150.44</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>105.68</v>
+        <v>105.05</v>
       </c>
       <c r="K45" t="n">
-        <v>49.41</v>
+        <v>49.11</v>
       </c>
       <c r="L45" t="n">
-        <v>116.66</v>
+        <v>115.96</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>216.54</v>
+        <v>211.88</v>
       </c>
       <c r="K46" t="n">
-        <v>92.14</v>
+        <v>90.16</v>
       </c>
       <c r="L46" t="n">
-        <v>235.33</v>
+        <v>230.27</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>-112.99</v>
+        <v>-113.02</v>
       </c>
       <c r="K47" t="n">
-        <v>40.15</v>
+        <v>40.16</v>
       </c>
       <c r="L47" t="n">
-        <v>119.91</v>
+        <v>119.95</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>13.13</v>
+        <v>13.21</v>
       </c>
       <c r="K48" t="n">
-        <v>247.28</v>
+        <v>248.8</v>
       </c>
       <c r="L48" t="n">
-        <v>247.63</v>
+        <v>249.15</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>62.86</v>
+        <v>62.16</v>
       </c>
       <c r="K49" t="n">
-        <v>-117.83</v>
+        <v>-116.52</v>
       </c>
       <c r="L49" t="n">
-        <v>133.55</v>
+        <v>132.06</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>-257.34</v>
+        <v>-271.23</v>
       </c>
       <c r="K50" t="n">
-        <v>-96.06999999999999</v>
+        <v>-101.25</v>
       </c>
       <c r="L50" t="n">
-        <v>274.69</v>
+        <v>289.52</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-158.05</v>
+        <v>-166.93</v>
       </c>
       <c r="K51" t="n">
-        <v>56.92</v>
+        <v>60.12</v>
       </c>
       <c r="L51" t="n">
-        <v>167.99</v>
+        <v>177.43</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>28</v>
       </c>
       <c r="J52" t="n">
-        <v>87.16</v>
+        <v>89.84</v>
       </c>
       <c r="K52" t="n">
-        <v>192.58</v>
+        <v>198.5</v>
       </c>
       <c r="L52" t="n">
-        <v>211.39</v>
+        <v>217.88</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>-483</v>
+        <v>-519.17</v>
       </c>
       <c r="K53" t="n">
-        <v>-288</v>
+        <v>-309.57</v>
       </c>
       <c r="L53" t="n">
-        <v>562.34</v>
+        <v>604.46</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>27</v>
       </c>
       <c r="J54" t="n">
-        <v>250.47</v>
+        <v>265.96</v>
       </c>
       <c r="K54" t="n">
-        <v>-144.14</v>
+        <v>-153.05</v>
       </c>
       <c r="L54" t="n">
-        <v>288.99</v>
+        <v>306.85</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>-95.34</v>
+        <v>-102.56</v>
       </c>
       <c r="K55" t="n">
-        <v>168.98</v>
+        <v>181.78</v>
       </c>
       <c r="L55" t="n">
-        <v>194.02</v>
+        <v>208.72</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>140.61</v>
+        <v>151.58</v>
       </c>
       <c r="K56" t="n">
-        <v>316.94</v>
+        <v>341.67</v>
       </c>
       <c r="L56" t="n">
-        <v>346.73</v>
+        <v>373.78</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>-309.65</v>
+        <v>-333.47</v>
       </c>
       <c r="K57" t="n">
-        <v>-46.99</v>
+        <v>-50.61</v>
       </c>
       <c r="L57" t="n">
-        <v>313.19</v>
+        <v>337.29</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>240.84</v>
+        <v>262.84</v>
       </c>
       <c r="K58" t="n">
-        <v>-303.63</v>
+        <v>-331.37</v>
       </c>
       <c r="L58" t="n">
-        <v>387.55</v>
+        <v>422.96</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>213.22</v>
+        <v>213.72</v>
       </c>
       <c r="K59" t="n">
-        <v>10.98</v>
+        <v>11.01</v>
       </c>
       <c r="L59" t="n">
-        <v>213.5</v>
+        <v>214</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>171.2</v>
+        <v>167.06</v>
       </c>
       <c r="K60" t="n">
-        <v>67.79000000000001</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="L60" t="n">
-        <v>184.13</v>
+        <v>179.68</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>168.45</v>
+        <v>168.3</v>
       </c>
       <c r="K61" t="n">
-        <v>107.47</v>
+        <v>107.38</v>
       </c>
       <c r="L61" t="n">
-        <v>199.82</v>
+        <v>199.64</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>114.79</v>
+        <v>113.52</v>
       </c>
       <c r="K62" t="n">
-        <v>-91.13</v>
+        <v>-90.13</v>
       </c>
       <c r="L62" t="n">
-        <v>146.56</v>
+        <v>144.95</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>-32.56</v>
+        <v>-32.07</v>
       </c>
       <c r="K63" t="n">
-        <v>97.73</v>
+        <v>96.25</v>
       </c>
       <c r="L63" t="n">
-        <v>103.01</v>
+        <v>101.46</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>232.8</v>
+        <v>233.12</v>
       </c>
       <c r="K64" t="n">
-        <v>-81</v>
+        <v>-81.11</v>
       </c>
       <c r="L64" t="n">
-        <v>246.49</v>
+        <v>246.83</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>-186.73</v>
+        <v>-190.79</v>
       </c>
       <c r="K65" t="n">
-        <v>-103.88</v>
+        <v>-106.14</v>
       </c>
       <c r="L65" t="n">
-        <v>213.68</v>
+        <v>218.33</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>230.35</v>
+        <v>238.03</v>
       </c>
       <c r="K66" t="n">
-        <v>-46.12</v>
+        <v>-47.66</v>
       </c>
       <c r="L66" t="n">
-        <v>234.92</v>
+        <v>242.76</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>-229.75</v>
+        <v>-235.38</v>
       </c>
       <c r="K67" t="n">
-        <v>-303.76</v>
+        <v>-311.2</v>
       </c>
       <c r="L67" t="n">
-        <v>380.87</v>
+        <v>390.19</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>404.73</v>
+        <v>441.28</v>
       </c>
       <c r="K68" t="n">
-        <v>-160.09</v>
+        <v>-174.55</v>
       </c>
       <c r="L68" t="n">
-        <v>435.24</v>
+        <v>474.55</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>-286.38</v>
+        <v>-305.18</v>
       </c>
       <c r="K69" t="n">
-        <v>105.97</v>
+        <v>112.93</v>
       </c>
       <c r="L69" t="n">
-        <v>305.36</v>
+        <v>325.4</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>191.48</v>
+        <v>207.39</v>
       </c>
       <c r="K70" t="n">
-        <v>-707.62</v>
+        <v>-766.41</v>
       </c>
       <c r="L70" t="n">
-        <v>733.0700000000001</v>
+        <v>793.97</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>241.09</v>
+        <v>266.56</v>
       </c>
       <c r="K71" t="n">
-        <v>273.93</v>
+        <v>302.87</v>
       </c>
       <c r="L71" t="n">
-        <v>364.92</v>
+        <v>403.47</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>442.22</v>
+        <v>483.96</v>
       </c>
       <c r="K72" t="n">
-        <v>296.01</v>
+        <v>323.95</v>
       </c>
       <c r="L72" t="n">
-        <v>532.14</v>
+        <v>582.38</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-328.13</v>
+        <v>-359.95</v>
       </c>
       <c r="K73" t="n">
-        <v>-81.65000000000001</v>
+        <v>-89.56</v>
       </c>
       <c r="L73" t="n">
-        <v>338.14</v>
+        <v>370.92</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>-109.68</v>
+        <v>-109.12</v>
       </c>
       <c r="K74" t="n">
-        <v>-176.87</v>
+        <v>-175.96</v>
       </c>
       <c r="L74" t="n">
-        <v>208.12</v>
+        <v>207.05</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>301.32</v>
+        <v>301.52</v>
       </c>
       <c r="K75" t="n">
-        <v>-171.25</v>
+        <v>-171.37</v>
       </c>
       <c r="L75" t="n">
-        <v>346.58</v>
+        <v>346.82</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>-85.53</v>
+        <v>-82.39</v>
       </c>
       <c r="K76" t="n">
-        <v>-63.89</v>
+        <v>-61.55</v>
       </c>
       <c r="L76" t="n">
-        <v>106.76</v>
+        <v>102.85</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-138.2</v>
+        <v>-139.52</v>
       </c>
       <c r="K77" t="n">
-        <v>-159.69</v>
+        <v>-161.21</v>
       </c>
       <c r="L77" t="n">
-        <v>211.19</v>
+        <v>213.2</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>28</v>
       </c>
       <c r="J78" t="n">
-        <v>162.27</v>
+        <v>158.85</v>
       </c>
       <c r="K78" t="n">
-        <v>-266.99</v>
+        <v>-261.36</v>
       </c>
       <c r="L78" t="n">
-        <v>312.44</v>
+        <v>305.85</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>251.36</v>
+        <v>248.54</v>
       </c>
       <c r="K79" t="n">
-        <v>-13.81</v>
+        <v>-13.66</v>
       </c>
       <c r="L79" t="n">
-        <v>251.74</v>
+        <v>248.91</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>301.45</v>
+        <v>317.94</v>
       </c>
       <c r="K80" t="n">
-        <v>38.55</v>
+        <v>40.65</v>
       </c>
       <c r="L80" t="n">
-        <v>303.9</v>
+        <v>320.53</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>106.07</v>
+        <v>111.51</v>
       </c>
       <c r="K81" t="n">
-        <v>-185.87</v>
+        <v>-195.42</v>
       </c>
       <c r="L81" t="n">
-        <v>214.01</v>
+        <v>224.99</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-264</v>
+        <v>-274.29</v>
       </c>
       <c r="K82" t="n">
-        <v>117.35</v>
+        <v>121.92</v>
       </c>
       <c r="L82" t="n">
-        <v>288.91</v>
+        <v>300.16</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>155.05</v>
+        <v>165.35</v>
       </c>
       <c r="K83" t="n">
-        <v>-376.26</v>
+        <v>-401.26</v>
       </c>
       <c r="L83" t="n">
-        <v>406.96</v>
+        <v>434</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>-39.58</v>
+        <v>-41.64</v>
       </c>
       <c r="K84" t="n">
-        <v>-212.91</v>
+        <v>-223.98</v>
       </c>
       <c r="L84" t="n">
-        <v>216.56</v>
+        <v>227.82</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>2.86</v>
+        <v>3.08</v>
       </c>
       <c r="K85" t="n">
-        <v>374.48</v>
+        <v>403.03</v>
       </c>
       <c r="L85" t="n">
-        <v>374.5</v>
+        <v>403.04</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>172.6</v>
+        <v>191.97</v>
       </c>
       <c r="K86" t="n">
-        <v>-257.02</v>
+        <v>-285.86</v>
       </c>
       <c r="L86" t="n">
-        <v>309.59</v>
+        <v>344.34</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>345.59</v>
+        <v>381.93</v>
       </c>
       <c r="K87" t="n">
-        <v>254.92</v>
+        <v>281.72</v>
       </c>
       <c r="L87" t="n">
-        <v>429.43</v>
+        <v>474.59</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>280.59</v>
+        <v>304.17</v>
       </c>
       <c r="K88" t="n">
-        <v>429.29</v>
+        <v>465.38</v>
       </c>
       <c r="L88" t="n">
-        <v>512.86</v>
+        <v>555.97</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-06.xlsx
+++ b/output/2024-07-06.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-127.12</v>
+        <v>-63.77</v>
       </c>
       <c r="K14" t="n">
-        <v>48.69</v>
+        <v>24.43</v>
       </c>
       <c r="L14" t="n">
-        <v>136.13</v>
+        <v>68.29000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>28</v>
       </c>
       <c r="J15" t="n">
-        <v>-124.4</v>
+        <v>-60.08</v>
       </c>
       <c r="K15" t="n">
-        <v>-35.29</v>
+        <v>-17.05</v>
       </c>
       <c r="L15" t="n">
-        <v>129.31</v>
+        <v>62.45</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>-53.18</v>
+        <v>-23.54</v>
       </c>
       <c r="K16" t="n">
-        <v>271.25</v>
+        <v>120.07</v>
       </c>
       <c r="L16" t="n">
-        <v>276.42</v>
+        <v>122.36</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>28</v>
       </c>
       <c r="J17" t="n">
-        <v>90.01000000000001</v>
+        <v>45.78</v>
       </c>
       <c r="K17" t="n">
-        <v>93.37</v>
+        <v>47.49</v>
       </c>
       <c r="L17" t="n">
-        <v>129.69</v>
+        <v>65.95999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>64.36</v>
+        <v>15.28</v>
       </c>
       <c r="K18" t="n">
-        <v>-46.9</v>
+        <v>-11.13</v>
       </c>
       <c r="L18" t="n">
-        <v>79.63</v>
+        <v>18.91</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-177.58</v>
+        <v>-93.92</v>
       </c>
       <c r="K19" t="n">
-        <v>63.21</v>
+        <v>33.43</v>
       </c>
       <c r="L19" t="n">
-        <v>188.5</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>209.55</v>
+        <v>105.74</v>
       </c>
       <c r="K20" t="n">
-        <v>243.91</v>
+        <v>123.08</v>
       </c>
       <c r="L20" t="n">
-        <v>321.56</v>
+        <v>162.26</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>28</v>
       </c>
       <c r="J21" t="n">
-        <v>39.73</v>
+        <v>21.06</v>
       </c>
       <c r="K21" t="n">
-        <v>-191.71</v>
+        <v>-101.63</v>
       </c>
       <c r="L21" t="n">
-        <v>195.79</v>
+        <v>103.79</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>144.01</v>
+        <v>73.56999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>-119.19</v>
+        <v>-60.89</v>
       </c>
       <c r="L22" t="n">
-        <v>186.94</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>-60.53</v>
+        <v>-33.46</v>
       </c>
       <c r="K23" t="n">
-        <v>364.47</v>
+        <v>201.45</v>
       </c>
       <c r="L23" t="n">
-        <v>369.47</v>
+        <v>204.2</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.54</v>
+        <v>-2.62</v>
       </c>
       <c r="K24" t="n">
-        <v>265.56</v>
+        <v>153.28</v>
       </c>
       <c r="L24" t="n">
-        <v>265.59</v>
+        <v>153.3</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>118.96</v>
+        <v>70.26000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>189.99</v>
+        <v>112.21</v>
       </c>
       <c r="L25" t="n">
-        <v>224.16</v>
+        <v>132.39</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>309.85</v>
+        <v>171.76</v>
       </c>
       <c r="K26" t="n">
-        <v>165.51</v>
+        <v>91.75</v>
       </c>
       <c r="L26" t="n">
-        <v>351.29</v>
+        <v>194.73</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>-227.11</v>
+        <v>-125.77</v>
       </c>
       <c r="K27" t="n">
-        <v>29.62</v>
+        <v>16.4</v>
       </c>
       <c r="L27" t="n">
-        <v>229.03</v>
+        <v>126.83</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-382.12</v>
+        <v>-213.32</v>
       </c>
       <c r="K28" t="n">
-        <v>-382.47</v>
+        <v>-213.52</v>
       </c>
       <c r="L28" t="n">
-        <v>540.65</v>
+        <v>301.82</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>-8.59</v>
+        <v>-4.56</v>
       </c>
       <c r="K29" t="n">
-        <v>91.98</v>
+        <v>48.82</v>
       </c>
       <c r="L29" t="n">
-        <v>92.38</v>
+        <v>49.03</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-153.46</v>
+        <v>-66.25</v>
       </c>
       <c r="K30" t="n">
-        <v>10.22</v>
+        <v>4.41</v>
       </c>
       <c r="L30" t="n">
-        <v>153.8</v>
+        <v>66.39</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>27</v>
       </c>
       <c r="J31" t="n">
-        <v>173.93</v>
+        <v>69.13</v>
       </c>
       <c r="K31" t="n">
-        <v>-54.38</v>
+        <v>-21.62</v>
       </c>
       <c r="L31" t="n">
-        <v>182.23</v>
+        <v>72.43000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>28</v>
       </c>
       <c r="J32" t="n">
-        <v>120.16</v>
+        <v>57.19</v>
       </c>
       <c r="K32" t="n">
-        <v>56.82</v>
+        <v>27.04</v>
       </c>
       <c r="L32" t="n">
-        <v>132.91</v>
+        <v>63.26</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>28</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.86</v>
+        <v>-0.98</v>
       </c>
       <c r="K33" t="n">
-        <v>126.85</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>126.86</v>
+        <v>66.79000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>294.01</v>
+        <v>121.92</v>
       </c>
       <c r="K34" t="n">
-        <v>-102.44</v>
+        <v>-42.48</v>
       </c>
       <c r="L34" t="n">
-        <v>311.34</v>
+        <v>129.11</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>-240.39</v>
+        <v>-116.4</v>
       </c>
       <c r="K35" t="n">
-        <v>315.59</v>
+        <v>152.82</v>
       </c>
       <c r="L35" t="n">
-        <v>396.72</v>
+        <v>192.1</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>18.96</v>
+        <v>5.04</v>
       </c>
       <c r="K36" t="n">
-        <v>-122.99</v>
+        <v>-32.67</v>
       </c>
       <c r="L36" t="n">
-        <v>124.44</v>
+        <v>33.06</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>-87.62</v>
+        <v>-44.45</v>
       </c>
       <c r="K37" t="n">
-        <v>-155.26</v>
+        <v>-78.77</v>
       </c>
       <c r="L37" t="n">
-        <v>178.28</v>
+        <v>90.45</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>258.76</v>
+        <v>134.78</v>
       </c>
       <c r="K38" t="n">
-        <v>218.61</v>
+        <v>113.86</v>
       </c>
       <c r="L38" t="n">
-        <v>338.75</v>
+        <v>176.44</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>28.88</v>
+        <v>15.1</v>
       </c>
       <c r="K39" t="n">
-        <v>-162.4</v>
+        <v>-84.93000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>164.95</v>
+        <v>86.26000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>205.5</v>
+        <v>116.7</v>
       </c>
       <c r="K40" t="n">
-        <v>54.65</v>
+        <v>31.04</v>
       </c>
       <c r="L40" t="n">
-        <v>212.64</v>
+        <v>120.76</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>-272.27</v>
+        <v>-144.7</v>
       </c>
       <c r="K41" t="n">
-        <v>-201.13</v>
+        <v>-106.89</v>
       </c>
       <c r="L41" t="n">
-        <v>338.5</v>
+        <v>179.9</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>22</v>
       </c>
       <c r="J42" t="n">
-        <v>438.71</v>
+        <v>238.09</v>
       </c>
       <c r="K42" t="n">
-        <v>-36.64</v>
+        <v>-19.89</v>
       </c>
       <c r="L42" t="n">
-        <v>440.24</v>
+        <v>238.92</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>158.2</v>
+        <v>84.28</v>
       </c>
       <c r="K43" t="n">
-        <v>-274.39</v>
+        <v>-146.18</v>
       </c>
       <c r="L43" t="n">
-        <v>316.73</v>
+        <v>168.74</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>110.21</v>
+        <v>48.12</v>
       </c>
       <c r="K44" t="n">
-        <v>-102.4</v>
+        <v>-44.72</v>
       </c>
       <c r="L44" t="n">
-        <v>150.44</v>
+        <v>65.69</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>105.05</v>
+        <v>48.34</v>
       </c>
       <c r="K45" t="n">
-        <v>49.11</v>
+        <v>22.6</v>
       </c>
       <c r="L45" t="n">
-        <v>115.96</v>
+        <v>53.36</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>211.88</v>
+        <v>94.73</v>
       </c>
       <c r="K46" t="n">
-        <v>90.16</v>
+        <v>40.31</v>
       </c>
       <c r="L46" t="n">
-        <v>230.27</v>
+        <v>102.95</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>-113.02</v>
+        <v>-54.59</v>
       </c>
       <c r="K47" t="n">
-        <v>40.16</v>
+        <v>19.4</v>
       </c>
       <c r="L47" t="n">
-        <v>119.95</v>
+        <v>57.94</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>13.21</v>
+        <v>5.88</v>
       </c>
       <c r="K48" t="n">
-        <v>248.8</v>
+        <v>110.68</v>
       </c>
       <c r="L48" t="n">
-        <v>249.15</v>
+        <v>110.83</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>62.16</v>
+        <v>27.91</v>
       </c>
       <c r="K49" t="n">
-        <v>-116.52</v>
+        <v>-52.33</v>
       </c>
       <c r="L49" t="n">
-        <v>132.06</v>
+        <v>59.31</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>-271.23</v>
+        <v>-135.02</v>
       </c>
       <c r="K50" t="n">
-        <v>-101.25</v>
+        <v>-50.41</v>
       </c>
       <c r="L50" t="n">
-        <v>289.52</v>
+        <v>144.13</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-166.93</v>
+        <v>-80.31999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>60.12</v>
+        <v>28.92</v>
       </c>
       <c r="L51" t="n">
-        <v>177.43</v>
+        <v>85.37</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>28</v>
       </c>
       <c r="J52" t="n">
-        <v>89.84</v>
+        <v>44.28</v>
       </c>
       <c r="K52" t="n">
-        <v>198.5</v>
+        <v>97.84</v>
       </c>
       <c r="L52" t="n">
-        <v>217.88</v>
+        <v>107.4</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>-519.17</v>
+        <v>-249.56</v>
       </c>
       <c r="K53" t="n">
-        <v>-309.57</v>
+        <v>-148.8</v>
       </c>
       <c r="L53" t="n">
-        <v>604.46</v>
+        <v>290.55</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>27</v>
       </c>
       <c r="J54" t="n">
-        <v>265.96</v>
+        <v>130.44</v>
       </c>
       <c r="K54" t="n">
-        <v>-153.05</v>
+        <v>-75.06</v>
       </c>
       <c r="L54" t="n">
-        <v>306.85</v>
+        <v>150.49</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>-102.56</v>
+        <v>-47.6</v>
       </c>
       <c r="K55" t="n">
-        <v>181.78</v>
+        <v>84.37</v>
       </c>
       <c r="L55" t="n">
-        <v>208.72</v>
+        <v>96.87</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>151.58</v>
+        <v>82.77</v>
       </c>
       <c r="K56" t="n">
-        <v>341.67</v>
+        <v>186.56</v>
       </c>
       <c r="L56" t="n">
-        <v>373.78</v>
+        <v>204.1</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>-333.47</v>
+        <v>-182.98</v>
       </c>
       <c r="K57" t="n">
-        <v>-50.61</v>
+        <v>-27.77</v>
       </c>
       <c r="L57" t="n">
-        <v>337.29</v>
+        <v>185.07</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>262.84</v>
+        <v>139.53</v>
       </c>
       <c r="K58" t="n">
-        <v>-331.37</v>
+        <v>-175.9</v>
       </c>
       <c r="L58" t="n">
-        <v>422.96</v>
+        <v>224.52</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>213.72</v>
+        <v>92.79000000000001</v>
       </c>
       <c r="K59" t="n">
-        <v>11.01</v>
+        <v>4.78</v>
       </c>
       <c r="L59" t="n">
-        <v>214</v>
+        <v>92.91</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>167.06</v>
+        <v>67.88</v>
       </c>
       <c r="K60" t="n">
-        <v>66.15000000000001</v>
+        <v>26.88</v>
       </c>
       <c r="L60" t="n">
-        <v>179.68</v>
+        <v>73.01000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>168.3</v>
+        <v>66.97</v>
       </c>
       <c r="K61" t="n">
-        <v>107.38</v>
+        <v>42.72</v>
       </c>
       <c r="L61" t="n">
-        <v>199.64</v>
+        <v>79.43000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>113.52</v>
+        <v>55.9</v>
       </c>
       <c r="K62" t="n">
-        <v>-90.13</v>
+        <v>-44.38</v>
       </c>
       <c r="L62" t="n">
-        <v>144.95</v>
+        <v>71.37</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>-32.07</v>
+        <v>-14.27</v>
       </c>
       <c r="K63" t="n">
-        <v>96.25</v>
+        <v>42.82</v>
       </c>
       <c r="L63" t="n">
-        <v>101.46</v>
+        <v>45.13</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>233.12</v>
+        <v>109.38</v>
       </c>
       <c r="K64" t="n">
-        <v>-81.11</v>
+        <v>-38.06</v>
       </c>
       <c r="L64" t="n">
-        <v>246.83</v>
+        <v>115.81</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>-190.79</v>
+        <v>-92.31</v>
       </c>
       <c r="K65" t="n">
-        <v>-106.14</v>
+        <v>-51.35</v>
       </c>
       <c r="L65" t="n">
-        <v>218.33</v>
+        <v>105.63</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>238.03</v>
+        <v>115.01</v>
       </c>
       <c r="K66" t="n">
-        <v>-47.66</v>
+        <v>-23.03</v>
       </c>
       <c r="L66" t="n">
-        <v>242.76</v>
+        <v>117.29</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>-235.38</v>
+        <v>-114.49</v>
       </c>
       <c r="K67" t="n">
-        <v>-311.2</v>
+        <v>-151.37</v>
       </c>
       <c r="L67" t="n">
-        <v>390.19</v>
+        <v>189.79</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>441.28</v>
+        <v>192.08</v>
       </c>
       <c r="K68" t="n">
-        <v>-174.55</v>
+        <v>-75.98</v>
       </c>
       <c r="L68" t="n">
-        <v>474.55</v>
+        <v>206.57</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>-305.18</v>
+        <v>-136.57</v>
       </c>
       <c r="K69" t="n">
-        <v>112.93</v>
+        <v>50.54</v>
       </c>
       <c r="L69" t="n">
-        <v>325.4</v>
+        <v>145.62</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>207.39</v>
+        <v>96.58</v>
       </c>
       <c r="K70" t="n">
-        <v>-766.41</v>
+        <v>-356.93</v>
       </c>
       <c r="L70" t="n">
-        <v>793.97</v>
+        <v>369.77</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>266.56</v>
+        <v>142.3</v>
       </c>
       <c r="K71" t="n">
-        <v>302.87</v>
+        <v>161.68</v>
       </c>
       <c r="L71" t="n">
-        <v>403.47</v>
+        <v>215.38</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>483.96</v>
+        <v>257.62</v>
       </c>
       <c r="K72" t="n">
-        <v>323.95</v>
+        <v>172.44</v>
       </c>
       <c r="L72" t="n">
-        <v>582.38</v>
+        <v>310.01</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-359.95</v>
+        <v>-194.81</v>
       </c>
       <c r="K73" t="n">
-        <v>-89.56</v>
+        <v>-48.47</v>
       </c>
       <c r="L73" t="n">
-        <v>370.92</v>
+        <v>200.75</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>-109.12</v>
+        <v>-48.3</v>
       </c>
       <c r="K74" t="n">
-        <v>-175.96</v>
+        <v>-77.89</v>
       </c>
       <c r="L74" t="n">
-        <v>207.05</v>
+        <v>91.65000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>301.52</v>
+        <v>124.85</v>
       </c>
       <c r="K75" t="n">
-        <v>-171.37</v>
+        <v>-70.95999999999999</v>
       </c>
       <c r="L75" t="n">
-        <v>346.82</v>
+        <v>143.6</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>-82.39</v>
+        <v>-40.74</v>
       </c>
       <c r="K76" t="n">
-        <v>-61.55</v>
+        <v>-30.43</v>
       </c>
       <c r="L76" t="n">
-        <v>102.85</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-139.52</v>
+        <v>-61.21</v>
       </c>
       <c r="K77" t="n">
-        <v>-161.21</v>
+        <v>-70.73</v>
       </c>
       <c r="L77" t="n">
-        <v>213.2</v>
+        <v>93.53</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>28</v>
       </c>
       <c r="J78" t="n">
-        <v>158.85</v>
+        <v>67.87</v>
       </c>
       <c r="K78" t="n">
-        <v>-261.36</v>
+        <v>-111.66</v>
       </c>
       <c r="L78" t="n">
-        <v>305.85</v>
+        <v>130.67</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>248.54</v>
+        <v>103.26</v>
       </c>
       <c r="K79" t="n">
-        <v>-13.66</v>
+        <v>-5.67</v>
       </c>
       <c r="L79" t="n">
-        <v>248.91</v>
+        <v>103.41</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>317.94</v>
+        <v>151.93</v>
       </c>
       <c r="K80" t="n">
-        <v>40.65</v>
+        <v>19.43</v>
       </c>
       <c r="L80" t="n">
-        <v>320.53</v>
+        <v>153.16</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>111.51</v>
+        <v>55.88</v>
       </c>
       <c r="K81" t="n">
-        <v>-195.42</v>
+        <v>-97.93000000000001</v>
       </c>
       <c r="L81" t="n">
-        <v>224.99</v>
+        <v>112.75</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-274.29</v>
+        <v>-131.64</v>
       </c>
       <c r="K82" t="n">
-        <v>121.92</v>
+        <v>58.52</v>
       </c>
       <c r="L82" t="n">
-        <v>300.16</v>
+        <v>144.06</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>165.35</v>
+        <v>72.26000000000001</v>
       </c>
       <c r="K83" t="n">
-        <v>-401.26</v>
+        <v>-175.35</v>
       </c>
       <c r="L83" t="n">
-        <v>434</v>
+        <v>189.66</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>-41.64</v>
+        <v>-18.63</v>
       </c>
       <c r="K84" t="n">
-        <v>-223.98</v>
+        <v>-100.23</v>
       </c>
       <c r="L84" t="n">
-        <v>227.82</v>
+        <v>101.95</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>3.08</v>
+        <v>1.4</v>
       </c>
       <c r="K85" t="n">
-        <v>403.03</v>
+        <v>183.63</v>
       </c>
       <c r="L85" t="n">
-        <v>403.04</v>
+        <v>183.64</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>191.97</v>
+        <v>101.86</v>
       </c>
       <c r="K86" t="n">
-        <v>-285.86</v>
+        <v>-151.69</v>
       </c>
       <c r="L86" t="n">
-        <v>344.34</v>
+        <v>182.71</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>381.93</v>
+        <v>202.93</v>
       </c>
       <c r="K87" t="n">
-        <v>281.72</v>
+        <v>149.69</v>
       </c>
       <c r="L87" t="n">
-        <v>474.59</v>
+        <v>252.17</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>304.17</v>
+        <v>166.41</v>
       </c>
       <c r="K88" t="n">
-        <v>465.38</v>
+        <v>254.6</v>
       </c>
       <c r="L88" t="n">
-        <v>555.97</v>
+        <v>304.16</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-06.xlsx
+++ b/output/2024-07-06.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-63.77</v>
+        <v>-63.07</v>
       </c>
       <c r="K14" t="n">
-        <v>24.43</v>
+        <v>24.16</v>
       </c>
       <c r="L14" t="n">
-        <v>68.29000000000001</v>
+        <v>67.54000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>28</v>
       </c>
       <c r="J15" t="n">
-        <v>-60.08</v>
+        <v>-58.97</v>
       </c>
       <c r="K15" t="n">
-        <v>-17.05</v>
+        <v>-16.73</v>
       </c>
       <c r="L15" t="n">
-        <v>62.45</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>-23.54</v>
+        <v>-21.64</v>
       </c>
       <c r="K16" t="n">
-        <v>120.07</v>
+        <v>110.37</v>
       </c>
       <c r="L16" t="n">
-        <v>122.36</v>
+        <v>112.47</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>28</v>
       </c>
       <c r="J17" t="n">
-        <v>45.78</v>
+        <v>45.65</v>
       </c>
       <c r="K17" t="n">
-        <v>47.49</v>
+        <v>47.36</v>
       </c>
       <c r="L17" t="n">
-        <v>65.95999999999999</v>
+        <v>65.78</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>15.28</v>
+        <v>14.62</v>
       </c>
       <c r="K18" t="n">
-        <v>-11.13</v>
+        <v>-10.65</v>
       </c>
       <c r="L18" t="n">
-        <v>18.91</v>
+        <v>18.08</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-93.92</v>
+        <v>-90.63</v>
       </c>
       <c r="K19" t="n">
-        <v>33.43</v>
+        <v>32.26</v>
       </c>
       <c r="L19" t="n">
-        <v>99.7</v>
+        <v>96.2</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>105.74</v>
+        <v>101.13</v>
       </c>
       <c r="K20" t="n">
-        <v>123.08</v>
+        <v>117.71</v>
       </c>
       <c r="L20" t="n">
-        <v>162.26</v>
+        <v>155.19</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>28</v>
       </c>
       <c r="J21" t="n">
-        <v>21.06</v>
+        <v>20.79</v>
       </c>
       <c r="K21" t="n">
-        <v>-101.63</v>
+        <v>-100.33</v>
       </c>
       <c r="L21" t="n">
-        <v>103.79</v>
+        <v>102.46</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>73.56999999999999</v>
+        <v>73.98</v>
       </c>
       <c r="K22" t="n">
-        <v>-60.89</v>
+        <v>-61.23</v>
       </c>
       <c r="L22" t="n">
-        <v>95.5</v>
+        <v>96.03</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>-33.46</v>
+        <v>-32.21</v>
       </c>
       <c r="K23" t="n">
-        <v>201.45</v>
+        <v>193.92</v>
       </c>
       <c r="L23" t="n">
-        <v>204.2</v>
+        <v>196.58</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.62</v>
+        <v>-2.6</v>
       </c>
       <c r="K24" t="n">
-        <v>153.28</v>
+        <v>152.19</v>
       </c>
       <c r="L24" t="n">
-        <v>153.3</v>
+        <v>152.21</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>70.26000000000001</v>
+        <v>70.11</v>
       </c>
       <c r="K25" t="n">
-        <v>112.21</v>
+        <v>111.97</v>
       </c>
       <c r="L25" t="n">
-        <v>132.39</v>
+        <v>132.11</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>171.76</v>
+        <v>177.08</v>
       </c>
       <c r="K26" t="n">
-        <v>91.75</v>
+        <v>94.59</v>
       </c>
       <c r="L26" t="n">
-        <v>194.73</v>
+        <v>200.76</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>-125.77</v>
+        <v>-136.72</v>
       </c>
       <c r="K27" t="n">
-        <v>16.4</v>
+        <v>17.83</v>
       </c>
       <c r="L27" t="n">
-        <v>126.83</v>
+        <v>137.88</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-213.32</v>
+        <v>-206.9</v>
       </c>
       <c r="K28" t="n">
-        <v>-213.52</v>
+        <v>-207.09</v>
       </c>
       <c r="L28" t="n">
-        <v>301.82</v>
+        <v>292.73</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>-4.56</v>
+        <v>-4.68</v>
       </c>
       <c r="K29" t="n">
-        <v>48.82</v>
+        <v>50.09</v>
       </c>
       <c r="L29" t="n">
-        <v>49.03</v>
+        <v>50.31</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-66.25</v>
+        <v>-64.81</v>
       </c>
       <c r="K30" t="n">
-        <v>4.41</v>
+        <v>4.32</v>
       </c>
       <c r="L30" t="n">
-        <v>66.39</v>
+        <v>64.95</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>27</v>
       </c>
       <c r="J31" t="n">
-        <v>69.13</v>
+        <v>65.02</v>
       </c>
       <c r="K31" t="n">
-        <v>-21.62</v>
+        <v>-20.33</v>
       </c>
       <c r="L31" t="n">
-        <v>72.43000000000001</v>
+        <v>68.12</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>28</v>
       </c>
       <c r="J32" t="n">
-        <v>57.19</v>
+        <v>57.22</v>
       </c>
       <c r="K32" t="n">
-        <v>27.04</v>
+        <v>27.06</v>
       </c>
       <c r="L32" t="n">
-        <v>63.26</v>
+        <v>63.29</v>
       </c>
     </row>
     <row r="33">
@@ -1441,10 +1441,10 @@
         <v>-0.98</v>
       </c>
       <c r="K33" t="n">
-        <v>66.79000000000001</v>
+        <v>66.91</v>
       </c>
       <c r="L33" t="n">
-        <v>66.79000000000001</v>
+        <v>66.91</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>121.92</v>
+        <v>111.96</v>
       </c>
       <c r="K34" t="n">
-        <v>-42.48</v>
+        <v>-39.01</v>
       </c>
       <c r="L34" t="n">
-        <v>129.11</v>
+        <v>118.56</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>-116.4</v>
+        <v>-93.26000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>152.82</v>
+        <v>122.43</v>
       </c>
       <c r="L35" t="n">
-        <v>192.1</v>
+        <v>153.91</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>5.04</v>
+        <v>4.87</v>
       </c>
       <c r="K36" t="n">
-        <v>-32.67</v>
+        <v>-31.6</v>
       </c>
       <c r="L36" t="n">
-        <v>33.06</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>-44.45</v>
+        <v>-45.52</v>
       </c>
       <c r="K37" t="n">
-        <v>-78.77</v>
+        <v>-80.66</v>
       </c>
       <c r="L37" t="n">
-        <v>90.45</v>
+        <v>92.62</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>134.78</v>
+        <v>133.49</v>
       </c>
       <c r="K38" t="n">
-        <v>113.86</v>
+        <v>112.78</v>
       </c>
       <c r="L38" t="n">
-        <v>176.44</v>
+        <v>174.75</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>15.1</v>
+        <v>16.56</v>
       </c>
       <c r="K39" t="n">
-        <v>-84.93000000000001</v>
+        <v>-93.11</v>
       </c>
       <c r="L39" t="n">
-        <v>86.26000000000001</v>
+        <v>94.56999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>116.7</v>
+        <v>119.19</v>
       </c>
       <c r="K40" t="n">
-        <v>31.04</v>
+        <v>31.7</v>
       </c>
       <c r="L40" t="n">
-        <v>120.76</v>
+        <v>123.33</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>-144.7</v>
+        <v>-163.14</v>
       </c>
       <c r="K41" t="n">
-        <v>-106.89</v>
+        <v>-120.51</v>
       </c>
       <c r="L41" t="n">
-        <v>179.9</v>
+        <v>202.83</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>22</v>
       </c>
       <c r="J42" t="n">
-        <v>238.09</v>
+        <v>247.15</v>
       </c>
       <c r="K42" t="n">
-        <v>-19.89</v>
+        <v>-20.64</v>
       </c>
       <c r="L42" t="n">
-        <v>238.92</v>
+        <v>248.01</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>84.28</v>
+        <v>96.17</v>
       </c>
       <c r="K43" t="n">
-        <v>-146.18</v>
+        <v>-166.8</v>
       </c>
       <c r="L43" t="n">
-        <v>168.74</v>
+        <v>192.54</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>48.12</v>
+        <v>47.43</v>
       </c>
       <c r="K44" t="n">
-        <v>-44.72</v>
+        <v>-44.07</v>
       </c>
       <c r="L44" t="n">
-        <v>65.69</v>
+        <v>64.73999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>48.34</v>
+        <v>49.26</v>
       </c>
       <c r="K45" t="n">
-        <v>22.6</v>
+        <v>23.03</v>
       </c>
       <c r="L45" t="n">
-        <v>53.36</v>
+        <v>54.38</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>94.73</v>
+        <v>88.51000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>40.31</v>
+        <v>37.66</v>
       </c>
       <c r="L46" t="n">
-        <v>102.95</v>
+        <v>96.19</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>-54.59</v>
+        <v>-56.13</v>
       </c>
       <c r="K47" t="n">
-        <v>19.4</v>
+        <v>19.94</v>
       </c>
       <c r="L47" t="n">
-        <v>57.94</v>
+        <v>59.57</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>5.88</v>
+        <v>5.54</v>
       </c>
       <c r="K48" t="n">
-        <v>110.68</v>
+        <v>104.43</v>
       </c>
       <c r="L48" t="n">
-        <v>110.83</v>
+        <v>104.58</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>27.91</v>
+        <v>28.39</v>
       </c>
       <c r="K49" t="n">
-        <v>-52.33</v>
+        <v>-53.23</v>
       </c>
       <c r="L49" t="n">
-        <v>59.31</v>
+        <v>60.33</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>-135.02</v>
+        <v>-131.47</v>
       </c>
       <c r="K50" t="n">
-        <v>-50.41</v>
+        <v>-49.08</v>
       </c>
       <c r="L50" t="n">
-        <v>144.13</v>
+        <v>140.33</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-80.31999999999999</v>
+        <v>-85.42</v>
       </c>
       <c r="K51" t="n">
-        <v>28.92</v>
+        <v>30.76</v>
       </c>
       <c r="L51" t="n">
-        <v>85.37</v>
+        <v>90.79000000000001</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>28</v>
       </c>
       <c r="J52" t="n">
-        <v>44.28</v>
+        <v>44.26</v>
       </c>
       <c r="K52" t="n">
-        <v>97.84</v>
+        <v>97.8</v>
       </c>
       <c r="L52" t="n">
-        <v>107.4</v>
+        <v>107.35</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>-249.56</v>
+        <v>-237.52</v>
       </c>
       <c r="K53" t="n">
-        <v>-148.8</v>
+        <v>-141.63</v>
       </c>
       <c r="L53" t="n">
-        <v>290.55</v>
+        <v>276.54</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>27</v>
       </c>
       <c r="J54" t="n">
-        <v>130.44</v>
+        <v>131.51</v>
       </c>
       <c r="K54" t="n">
-        <v>-75.06</v>
+        <v>-75.68000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>150.49</v>
+        <v>151.73</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>-47.6</v>
+        <v>-52.02</v>
       </c>
       <c r="K55" t="n">
-        <v>84.37</v>
+        <v>92.20999999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>96.87</v>
+        <v>105.87</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>82.77</v>
+        <v>86.39</v>
       </c>
       <c r="K56" t="n">
-        <v>186.56</v>
+        <v>194.73</v>
       </c>
       <c r="L56" t="n">
-        <v>204.1</v>
+        <v>213.04</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>-182.98</v>
+        <v>-192.17</v>
       </c>
       <c r="K57" t="n">
-        <v>-27.77</v>
+        <v>-29.16</v>
       </c>
       <c r="L57" t="n">
-        <v>185.07</v>
+        <v>194.37</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>139.53</v>
+        <v>154.9</v>
       </c>
       <c r="K58" t="n">
-        <v>-175.9</v>
+        <v>-195.28</v>
       </c>
       <c r="L58" t="n">
-        <v>224.52</v>
+        <v>249.26</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>92.79000000000001</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="K59" t="n">
-        <v>4.78</v>
+        <v>4.52</v>
       </c>
       <c r="L59" t="n">
-        <v>92.91</v>
+        <v>87.79000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>67.88</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="K60" t="n">
-        <v>26.88</v>
+        <v>25.52</v>
       </c>
       <c r="L60" t="n">
-        <v>73.01000000000001</v>
+        <v>69.33</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>66.97</v>
+        <v>62.47</v>
       </c>
       <c r="K61" t="n">
-        <v>42.72</v>
+        <v>39.86</v>
       </c>
       <c r="L61" t="n">
-        <v>79.43000000000001</v>
+        <v>74.09999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>55.9</v>
+        <v>55.31</v>
       </c>
       <c r="K62" t="n">
-        <v>-44.38</v>
+        <v>-43.91</v>
       </c>
       <c r="L62" t="n">
-        <v>71.37</v>
+        <v>70.63</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>-14.27</v>
+        <v>-15.06</v>
       </c>
       <c r="K63" t="n">
-        <v>42.82</v>
+        <v>45.21</v>
       </c>
       <c r="L63" t="n">
-        <v>45.13</v>
+        <v>47.65</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>109.38</v>
+        <v>103.1</v>
       </c>
       <c r="K64" t="n">
-        <v>-38.06</v>
+        <v>-35.87</v>
       </c>
       <c r="L64" t="n">
-        <v>115.81</v>
+        <v>109.16</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>-92.31</v>
+        <v>-92.65000000000001</v>
       </c>
       <c r="K65" t="n">
-        <v>-51.35</v>
+        <v>-51.54</v>
       </c>
       <c r="L65" t="n">
-        <v>105.63</v>
+        <v>106.02</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>115.01</v>
+        <v>114.07</v>
       </c>
       <c r="K66" t="n">
-        <v>-23.03</v>
+        <v>-22.84</v>
       </c>
       <c r="L66" t="n">
-        <v>117.29</v>
+        <v>116.33</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>-114.49</v>
+        <v>-107.78</v>
       </c>
       <c r="K67" t="n">
-        <v>-151.37</v>
+        <v>-142.51</v>
       </c>
       <c r="L67" t="n">
-        <v>189.79</v>
+        <v>178.68</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>192.08</v>
+        <v>199.35</v>
       </c>
       <c r="K68" t="n">
-        <v>-75.98</v>
+        <v>-78.86</v>
       </c>
       <c r="L68" t="n">
-        <v>206.57</v>
+        <v>214.38</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>-136.57</v>
+        <v>-139.69</v>
       </c>
       <c r="K69" t="n">
-        <v>50.54</v>
+        <v>51.69</v>
       </c>
       <c r="L69" t="n">
-        <v>145.62</v>
+        <v>148.95</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>96.58</v>
+        <v>90.75</v>
       </c>
       <c r="K70" t="n">
-        <v>-356.93</v>
+        <v>-335.37</v>
       </c>
       <c r="L70" t="n">
-        <v>369.77</v>
+        <v>347.43</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>142.3</v>
+        <v>168</v>
       </c>
       <c r="K71" t="n">
-        <v>161.68</v>
+        <v>190.89</v>
       </c>
       <c r="L71" t="n">
-        <v>215.38</v>
+        <v>254.29</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>257.62</v>
+        <v>272.12</v>
       </c>
       <c r="K72" t="n">
-        <v>172.44</v>
+        <v>182.15</v>
       </c>
       <c r="L72" t="n">
-        <v>310.01</v>
+        <v>327.46</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-194.81</v>
+        <v>-206.89</v>
       </c>
       <c r="K73" t="n">
-        <v>-48.47</v>
+        <v>-51.48</v>
       </c>
       <c r="L73" t="n">
-        <v>200.75</v>
+        <v>213.2</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>-48.3</v>
+        <v>-45.58</v>
       </c>
       <c r="K74" t="n">
-        <v>-77.89</v>
+        <v>-73.51000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>91.65000000000001</v>
+        <v>86.48999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>124.85</v>
+        <v>112.63</v>
       </c>
       <c r="K75" t="n">
-        <v>-70.95999999999999</v>
+        <v>-64.01000000000001</v>
       </c>
       <c r="L75" t="n">
-        <v>143.6</v>
+        <v>129.55</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>-40.74</v>
+        <v>-41.18</v>
       </c>
       <c r="K76" t="n">
-        <v>-30.43</v>
+        <v>-30.77</v>
       </c>
       <c r="L76" t="n">
-        <v>50.85</v>
+        <v>51.41</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-61.21</v>
+        <v>-58.48</v>
       </c>
       <c r="K77" t="n">
-        <v>-70.73</v>
+        <v>-67.56999999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>93.53</v>
+        <v>89.36</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>28</v>
       </c>
       <c r="J78" t="n">
-        <v>67.87</v>
+        <v>62.02</v>
       </c>
       <c r="K78" t="n">
-        <v>-111.66</v>
+        <v>-102.04</v>
       </c>
       <c r="L78" t="n">
-        <v>130.67</v>
+        <v>119.41</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>103.26</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="K79" t="n">
-        <v>-5.67</v>
+        <v>-5.25</v>
       </c>
       <c r="L79" t="n">
-        <v>103.41</v>
+        <v>95.65000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>151.93</v>
+        <v>147.06</v>
       </c>
       <c r="K80" t="n">
-        <v>19.43</v>
+        <v>18.8</v>
       </c>
       <c r="L80" t="n">
-        <v>153.16</v>
+        <v>148.26</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>55.88</v>
+        <v>55.53</v>
       </c>
       <c r="K81" t="n">
-        <v>-97.93000000000001</v>
+        <v>-97.31</v>
       </c>
       <c r="L81" t="n">
-        <v>112.75</v>
+        <v>112.04</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-131.64</v>
+        <v>-127.74</v>
       </c>
       <c r="K82" t="n">
-        <v>58.52</v>
+        <v>56.78</v>
       </c>
       <c r="L82" t="n">
-        <v>144.06</v>
+        <v>139.79</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>72.26000000000001</v>
+        <v>75.02</v>
       </c>
       <c r="K83" t="n">
-        <v>-175.35</v>
+        <v>-182.06</v>
       </c>
       <c r="L83" t="n">
-        <v>189.66</v>
+        <v>196.91</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>-18.63</v>
+        <v>-19.96</v>
       </c>
       <c r="K84" t="n">
-        <v>-100.23</v>
+        <v>-107.36</v>
       </c>
       <c r="L84" t="n">
-        <v>101.95</v>
+        <v>109.2</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="K85" t="n">
-        <v>183.63</v>
+        <v>198.78</v>
       </c>
       <c r="L85" t="n">
-        <v>183.64</v>
+        <v>198.79</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>101.86</v>
+        <v>116.78</v>
       </c>
       <c r="K86" t="n">
-        <v>-151.69</v>
+        <v>-173.89</v>
       </c>
       <c r="L86" t="n">
-        <v>182.71</v>
+        <v>209.46</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>202.93</v>
+        <v>231.07</v>
       </c>
       <c r="K87" t="n">
-        <v>149.69</v>
+        <v>170.45</v>
       </c>
       <c r="L87" t="n">
-        <v>252.17</v>
+        <v>287.14</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>166.41</v>
+        <v>165.52</v>
       </c>
       <c r="K88" t="n">
-        <v>254.6</v>
+        <v>253.24</v>
       </c>
       <c r="L88" t="n">
-        <v>304.16</v>
+        <v>302.53</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-06.xlsx
+++ b/output/2024-07-06.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-63.07</v>
+        <v>-62.96</v>
       </c>
       <c r="K14" t="n">
-        <v>24.16</v>
+        <v>24.11</v>
       </c>
       <c r="L14" t="n">
-        <v>67.54000000000001</v>
+        <v>67.42</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>28</v>
       </c>
       <c r="J15" t="n">
-        <v>-58.97</v>
+        <v>-58.67</v>
       </c>
       <c r="K15" t="n">
-        <v>-16.73</v>
+        <v>-16.64</v>
       </c>
       <c r="L15" t="n">
-        <v>61.3</v>
+        <v>60.98</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>-21.64</v>
+        <v>-20.15</v>
       </c>
       <c r="K16" t="n">
-        <v>110.37</v>
+        <v>102.78</v>
       </c>
       <c r="L16" t="n">
-        <v>112.47</v>
+        <v>104.74</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>28</v>
       </c>
       <c r="J17" t="n">
-        <v>45.65</v>
+        <v>45.94</v>
       </c>
       <c r="K17" t="n">
-        <v>47.36</v>
+        <v>47.66</v>
       </c>
       <c r="L17" t="n">
-        <v>65.78</v>
+        <v>66.19</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>14.62</v>
+        <v>15.8</v>
       </c>
       <c r="K18" t="n">
-        <v>-10.65</v>
+        <v>-11.51</v>
       </c>
       <c r="L18" t="n">
-        <v>18.08</v>
+        <v>19.54</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-90.63</v>
+        <v>-87.17</v>
       </c>
       <c r="K19" t="n">
-        <v>32.26</v>
+        <v>31.03</v>
       </c>
       <c r="L19" t="n">
-        <v>96.2</v>
+        <v>92.53</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>101.13</v>
+        <v>96.31999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>117.71</v>
+        <v>112.12</v>
       </c>
       <c r="L20" t="n">
-        <v>155.19</v>
+        <v>147.81</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>28</v>
       </c>
       <c r="J21" t="n">
-        <v>20.79</v>
+        <v>20.48</v>
       </c>
       <c r="K21" t="n">
-        <v>-100.33</v>
+        <v>-98.84</v>
       </c>
       <c r="L21" t="n">
-        <v>102.46</v>
+        <v>100.94</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>73.98</v>
+        <v>74.58</v>
       </c>
       <c r="K22" t="n">
-        <v>-61.23</v>
+        <v>-61.72</v>
       </c>
       <c r="L22" t="n">
-        <v>96.03</v>
+        <v>96.81</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>-32.21</v>
+        <v>-30.72</v>
       </c>
       <c r="K23" t="n">
-        <v>193.92</v>
+        <v>184.98</v>
       </c>
       <c r="L23" t="n">
-        <v>196.58</v>
+        <v>187.52</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.6</v>
+        <v>-2.58</v>
       </c>
       <c r="K24" t="n">
-        <v>152.19</v>
+        <v>150.93</v>
       </c>
       <c r="L24" t="n">
-        <v>152.21</v>
+        <v>150.95</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>70.11</v>
+        <v>69.94</v>
       </c>
       <c r="K25" t="n">
-        <v>111.97</v>
+        <v>111.71</v>
       </c>
       <c r="L25" t="n">
-        <v>132.11</v>
+        <v>131.8</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>177.08</v>
+        <v>179.08</v>
       </c>
       <c r="K26" t="n">
-        <v>94.59</v>
+        <v>95.66</v>
       </c>
       <c r="L26" t="n">
-        <v>200.76</v>
+        <v>203.03</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>-136.72</v>
+        <v>-146.16</v>
       </c>
       <c r="K27" t="n">
-        <v>17.83</v>
+        <v>19.06</v>
       </c>
       <c r="L27" t="n">
-        <v>137.88</v>
+        <v>147.4</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-206.9</v>
+        <v>-196.05</v>
       </c>
       <c r="K28" t="n">
-        <v>-207.09</v>
+        <v>-196.23</v>
       </c>
       <c r="L28" t="n">
-        <v>292.73</v>
+        <v>277.39</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>-4.68</v>
+        <v>-4.83</v>
       </c>
       <c r="K29" t="n">
-        <v>50.09</v>
+        <v>51.72</v>
       </c>
       <c r="L29" t="n">
-        <v>50.31</v>
+        <v>51.95</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-64.81</v>
+        <v>-65.33</v>
       </c>
       <c r="K30" t="n">
-        <v>4.32</v>
+        <v>4.35</v>
       </c>
       <c r="L30" t="n">
-        <v>64.95</v>
+        <v>65.47</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>27</v>
       </c>
       <c r="J31" t="n">
-        <v>65.02</v>
+        <v>64.17</v>
       </c>
       <c r="K31" t="n">
-        <v>-20.33</v>
+        <v>-20.07</v>
       </c>
       <c r="L31" t="n">
-        <v>68.12</v>
+        <v>67.23999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>28</v>
       </c>
       <c r="J32" t="n">
-        <v>57.22</v>
+        <v>58.4</v>
       </c>
       <c r="K32" t="n">
-        <v>27.06</v>
+        <v>27.62</v>
       </c>
       <c r="L32" t="n">
-        <v>63.29</v>
+        <v>64.59999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>28</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.98</v>
+        <v>-0.99</v>
       </c>
       <c r="K33" t="n">
-        <v>66.91</v>
+        <v>67.3</v>
       </c>
       <c r="L33" t="n">
-        <v>66.91</v>
+        <v>67.31</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>111.96</v>
+        <v>106.44</v>
       </c>
       <c r="K34" t="n">
-        <v>-39.01</v>
+        <v>-37.08</v>
       </c>
       <c r="L34" t="n">
-        <v>118.56</v>
+        <v>112.71</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>-93.26000000000001</v>
+        <v>-90.22</v>
       </c>
       <c r="K35" t="n">
-        <v>122.43</v>
+        <v>118.45</v>
       </c>
       <c r="L35" t="n">
-        <v>153.91</v>
+        <v>148.9</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>4.87</v>
+        <v>5.28</v>
       </c>
       <c r="K36" t="n">
-        <v>-31.6</v>
+        <v>-34.24</v>
       </c>
       <c r="L36" t="n">
-        <v>31.97</v>
+        <v>34.65</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>-45.52</v>
+        <v>-46.88</v>
       </c>
       <c r="K37" t="n">
-        <v>-80.66</v>
+        <v>-83.06999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>92.62</v>
+        <v>95.39</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>133.49</v>
+        <v>131.49</v>
       </c>
       <c r="K38" t="n">
-        <v>112.78</v>
+        <v>111.08</v>
       </c>
       <c r="L38" t="n">
-        <v>174.75</v>
+        <v>172.13</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>16.56</v>
+        <v>18.16</v>
       </c>
       <c r="K39" t="n">
-        <v>-93.11</v>
+        <v>-102.14</v>
       </c>
       <c r="L39" t="n">
-        <v>94.56999999999999</v>
+        <v>103.74</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>119.19</v>
+        <v>121.95</v>
       </c>
       <c r="K40" t="n">
-        <v>31.7</v>
+        <v>32.43</v>
       </c>
       <c r="L40" t="n">
-        <v>123.33</v>
+        <v>126.19</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>-163.14</v>
+        <v>-169.7</v>
       </c>
       <c r="K41" t="n">
-        <v>-120.51</v>
+        <v>-125.36</v>
       </c>
       <c r="L41" t="n">
-        <v>202.83</v>
+        <v>210.98</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>22</v>
       </c>
       <c r="J42" t="n">
-        <v>247.15</v>
+        <v>246.45</v>
       </c>
       <c r="K42" t="n">
-        <v>-20.64</v>
+        <v>-20.58</v>
       </c>
       <c r="L42" t="n">
-        <v>248.01</v>
+        <v>247.31</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>96.17</v>
+        <v>102.28</v>
       </c>
       <c r="K43" t="n">
-        <v>-166.8</v>
+        <v>-177.4</v>
       </c>
       <c r="L43" t="n">
-        <v>192.54</v>
+        <v>204.78</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>47.43</v>
+        <v>48.12</v>
       </c>
       <c r="K44" t="n">
-        <v>-44.07</v>
+        <v>-44.71</v>
       </c>
       <c r="L44" t="n">
-        <v>64.73999999999999</v>
+        <v>65.69</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>49.26</v>
+        <v>51.41</v>
       </c>
       <c r="K45" t="n">
-        <v>23.03</v>
+        <v>24.04</v>
       </c>
       <c r="L45" t="n">
-        <v>54.38</v>
+        <v>56.76</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>88.51000000000001</v>
+        <v>84.01000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>37.66</v>
+        <v>35.75</v>
       </c>
       <c r="L46" t="n">
-        <v>96.19</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>-56.13</v>
+        <v>-58.84</v>
       </c>
       <c r="K47" t="n">
-        <v>19.94</v>
+        <v>20.91</v>
       </c>
       <c r="L47" t="n">
-        <v>59.57</v>
+        <v>62.44</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>5.54</v>
+        <v>5.36</v>
       </c>
       <c r="K48" t="n">
-        <v>104.43</v>
+        <v>100.87</v>
       </c>
       <c r="L48" t="n">
-        <v>104.58</v>
+        <v>101.01</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>28.39</v>
+        <v>29.79</v>
       </c>
       <c r="K49" t="n">
-        <v>-53.23</v>
+        <v>-55.84</v>
       </c>
       <c r="L49" t="n">
-        <v>60.33</v>
+        <v>63.29</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>-131.47</v>
+        <v>-128.35</v>
       </c>
       <c r="K50" t="n">
-        <v>-49.08</v>
+        <v>-47.92</v>
       </c>
       <c r="L50" t="n">
-        <v>140.33</v>
+        <v>137.01</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-85.42</v>
+        <v>-92.36</v>
       </c>
       <c r="K51" t="n">
-        <v>30.76</v>
+        <v>33.26</v>
       </c>
       <c r="L51" t="n">
-        <v>90.79000000000001</v>
+        <v>98.17</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>28</v>
       </c>
       <c r="J52" t="n">
-        <v>44.26</v>
+        <v>44.64</v>
       </c>
       <c r="K52" t="n">
-        <v>97.8</v>
+        <v>98.64</v>
       </c>
       <c r="L52" t="n">
-        <v>107.35</v>
+        <v>108.27</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>-237.52</v>
+        <v>-221.92</v>
       </c>
       <c r="K53" t="n">
-        <v>-141.63</v>
+        <v>-132.33</v>
       </c>
       <c r="L53" t="n">
-        <v>276.54</v>
+        <v>258.38</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>27</v>
       </c>
       <c r="J54" t="n">
-        <v>131.51</v>
+        <v>131.89</v>
       </c>
       <c r="K54" t="n">
-        <v>-75.68000000000001</v>
+        <v>-75.90000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>151.73</v>
+        <v>152.17</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>-52.02</v>
+        <v>-56.67</v>
       </c>
       <c r="K55" t="n">
-        <v>92.20999999999999</v>
+        <v>100.43</v>
       </c>
       <c r="L55" t="n">
-        <v>105.87</v>
+        <v>115.32</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>86.39</v>
+        <v>87.25</v>
       </c>
       <c r="K56" t="n">
-        <v>194.73</v>
+        <v>196.66</v>
       </c>
       <c r="L56" t="n">
-        <v>213.04</v>
+        <v>215.15</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>-192.17</v>
+        <v>-196.37</v>
       </c>
       <c r="K57" t="n">
-        <v>-29.16</v>
+        <v>-29.8</v>
       </c>
       <c r="L57" t="n">
-        <v>194.37</v>
+        <v>198.62</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>154.9</v>
+        <v>157.63</v>
       </c>
       <c r="K58" t="n">
-        <v>-195.28</v>
+        <v>-198.73</v>
       </c>
       <c r="L58" t="n">
-        <v>249.26</v>
+        <v>253.66</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>87.68000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="K59" t="n">
-        <v>4.52</v>
+        <v>4.37</v>
       </c>
       <c r="L59" t="n">
-        <v>87.79000000000001</v>
+        <v>84.92</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>64.45999999999999</v>
+        <v>63.43</v>
       </c>
       <c r="K60" t="n">
-        <v>25.52</v>
+        <v>25.12</v>
       </c>
       <c r="L60" t="n">
-        <v>69.33</v>
+        <v>68.23</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>62.47</v>
+        <v>61.69</v>
       </c>
       <c r="K61" t="n">
-        <v>39.86</v>
+        <v>39.36</v>
       </c>
       <c r="L61" t="n">
-        <v>74.09999999999999</v>
+        <v>73.17</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>55.31</v>
+        <v>55.46</v>
       </c>
       <c r="K62" t="n">
-        <v>-43.91</v>
+        <v>-44.03</v>
       </c>
       <c r="L62" t="n">
-        <v>70.63</v>
+        <v>70.81</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>-15.06</v>
+        <v>-16.42</v>
       </c>
       <c r="K63" t="n">
-        <v>45.21</v>
+        <v>49.29</v>
       </c>
       <c r="L63" t="n">
-        <v>47.65</v>
+        <v>51.95</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>103.1</v>
+        <v>98.42</v>
       </c>
       <c r="K64" t="n">
-        <v>-35.87</v>
+        <v>-34.24</v>
       </c>
       <c r="L64" t="n">
-        <v>109.16</v>
+        <v>104.21</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>-92.65000000000001</v>
+        <v>-94.23</v>
       </c>
       <c r="K65" t="n">
-        <v>-51.54</v>
+        <v>-52.42</v>
       </c>
       <c r="L65" t="n">
-        <v>106.02</v>
+        <v>107.83</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>114.07</v>
+        <v>114.5</v>
       </c>
       <c r="K66" t="n">
-        <v>-22.84</v>
+        <v>-22.92</v>
       </c>
       <c r="L66" t="n">
-        <v>116.33</v>
+        <v>116.77</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>-107.78</v>
+        <v>-101.49</v>
       </c>
       <c r="K67" t="n">
-        <v>-142.51</v>
+        <v>-134.18</v>
       </c>
       <c r="L67" t="n">
-        <v>178.68</v>
+        <v>168.24</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>199.35</v>
+        <v>195.78</v>
       </c>
       <c r="K68" t="n">
-        <v>-78.86</v>
+        <v>-77.44</v>
       </c>
       <c r="L68" t="n">
-        <v>214.38</v>
+        <v>210.54</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>-139.69</v>
+        <v>-141.28</v>
       </c>
       <c r="K69" t="n">
-        <v>51.69</v>
+        <v>52.28</v>
       </c>
       <c r="L69" t="n">
-        <v>148.95</v>
+        <v>150.64</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>90.75</v>
+        <v>83.23</v>
       </c>
       <c r="K70" t="n">
-        <v>-335.37</v>
+        <v>-307.57</v>
       </c>
       <c r="L70" t="n">
-        <v>347.43</v>
+        <v>318.63</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>168</v>
+        <v>175.9</v>
       </c>
       <c r="K71" t="n">
-        <v>190.89</v>
+        <v>199.86</v>
       </c>
       <c r="L71" t="n">
-        <v>254.29</v>
+        <v>266.24</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>272.12</v>
+        <v>264.39</v>
       </c>
       <c r="K72" t="n">
-        <v>182.15</v>
+        <v>176.97</v>
       </c>
       <c r="L72" t="n">
-        <v>327.46</v>
+        <v>318.15</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-206.89</v>
+        <v>-211.12</v>
       </c>
       <c r="K73" t="n">
-        <v>-51.48</v>
+        <v>-52.53</v>
       </c>
       <c r="L73" t="n">
-        <v>213.2</v>
+        <v>217.56</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>-45.58</v>
+        <v>-43.88</v>
       </c>
       <c r="K74" t="n">
-        <v>-73.51000000000001</v>
+        <v>-70.75</v>
       </c>
       <c r="L74" t="n">
-        <v>86.48999999999999</v>
+        <v>83.25</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>112.63</v>
+        <v>103.64</v>
       </c>
       <c r="K75" t="n">
-        <v>-64.01000000000001</v>
+        <v>-58.9</v>
       </c>
       <c r="L75" t="n">
-        <v>129.55</v>
+        <v>119.21</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>-41.18</v>
+        <v>-42.22</v>
       </c>
       <c r="K76" t="n">
-        <v>-30.77</v>
+        <v>-31.54</v>
       </c>
       <c r="L76" t="n">
-        <v>51.41</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-58.48</v>
+        <v>-57.49</v>
       </c>
       <c r="K77" t="n">
-        <v>-67.56999999999999</v>
+        <v>-66.43000000000001</v>
       </c>
       <c r="L77" t="n">
-        <v>89.36</v>
+        <v>87.84999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>28</v>
       </c>
       <c r="J78" t="n">
-        <v>62.02</v>
+        <v>58.06</v>
       </c>
       <c r="K78" t="n">
-        <v>-102.04</v>
+        <v>-95.52</v>
       </c>
       <c r="L78" t="n">
-        <v>119.41</v>
+        <v>111.78</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>95.51000000000001</v>
+        <v>92.44</v>
       </c>
       <c r="K79" t="n">
-        <v>-5.25</v>
+        <v>-5.08</v>
       </c>
       <c r="L79" t="n">
-        <v>95.65000000000001</v>
+        <v>92.58</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>147.06</v>
+        <v>145.22</v>
       </c>
       <c r="K80" t="n">
-        <v>18.8</v>
+        <v>18.57</v>
       </c>
       <c r="L80" t="n">
-        <v>148.26</v>
+        <v>146.41</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>55.53</v>
+        <v>55.44</v>
       </c>
       <c r="K81" t="n">
-        <v>-97.31</v>
+        <v>-97.15000000000001</v>
       </c>
       <c r="L81" t="n">
-        <v>112.04</v>
+        <v>111.86</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-127.74</v>
+        <v>-125.2</v>
       </c>
       <c r="K82" t="n">
-        <v>56.78</v>
+        <v>55.65</v>
       </c>
       <c r="L82" t="n">
-        <v>139.79</v>
+        <v>137.01</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>75.02</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="K83" t="n">
-        <v>-182.06</v>
+        <v>-178.6</v>
       </c>
       <c r="L83" t="n">
-        <v>196.91</v>
+        <v>193.17</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>-19.96</v>
+        <v>-21.21</v>
       </c>
       <c r="K84" t="n">
-        <v>-107.36</v>
+        <v>-114.1</v>
       </c>
       <c r="L84" t="n">
-        <v>109.2</v>
+        <v>116.06</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="K85" t="n">
-        <v>198.78</v>
+        <v>201.57</v>
       </c>
       <c r="L85" t="n">
-        <v>198.79</v>
+        <v>201.58</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>116.78</v>
+        <v>122.89</v>
       </c>
       <c r="K86" t="n">
-        <v>-173.89</v>
+        <v>-182.99</v>
       </c>
       <c r="L86" t="n">
-        <v>209.46</v>
+        <v>220.42</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>231.07</v>
+        <v>233.94</v>
       </c>
       <c r="K87" t="n">
-        <v>170.45</v>
+        <v>172.57</v>
       </c>
       <c r="L87" t="n">
-        <v>287.14</v>
+        <v>290.71</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>165.52</v>
+        <v>158.17</v>
       </c>
       <c r="K88" t="n">
-        <v>253.24</v>
+        <v>242</v>
       </c>
       <c r="L88" t="n">
-        <v>302.53</v>
+        <v>289.1</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-06.xlsx
+++ b/output/2024-07-06.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.57</v>
+        <v>3.32</v>
       </c>
       <c r="F14" t="n">
-        <v>10.68</v>
+        <v>7.89</v>
       </c>
       <c r="G14" t="n">
-        <v>287.1</v>
+        <v>295.8</v>
       </c>
       <c r="H14" t="n">
         <v>44.4</v>
       </c>
       <c r="I14" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>-62.96</v>
+        <v>-25.78</v>
       </c>
       <c r="K14" t="n">
-        <v>24.11</v>
+        <v>-76.79000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>67.42</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:41:11</t>
+          <t>04:40:14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.73</v>
+        <v>4.05</v>
       </c>
       <c r="F15" t="n">
-        <v>11.23</v>
+        <v>12.54</v>
       </c>
       <c r="G15" t="n">
-        <v>283.8</v>
+        <v>286.8</v>
       </c>
       <c r="H15" t="n">
-        <v>44</v>
+        <v>48.5</v>
       </c>
       <c r="I15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J15" t="n">
-        <v>-58.67</v>
+        <v>14.28</v>
       </c>
       <c r="K15" t="n">
-        <v>-16.64</v>
+        <v>61.61</v>
       </c>
       <c r="L15" t="n">
-        <v>60.98</v>
+        <v>63.25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:43:16</t>
+          <t>04:43:04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>4.14</v>
+        <v>3.69</v>
       </c>
       <c r="F16" t="n">
-        <v>10.12</v>
+        <v>10.07</v>
       </c>
       <c r="G16" t="n">
-        <v>275.9</v>
+        <v>280.7</v>
       </c>
       <c r="H16" t="n">
-        <v>39.4</v>
+        <v>42.5</v>
       </c>
       <c r="I16" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>-20.15</v>
+        <v>-22.15</v>
       </c>
       <c r="K16" t="n">
-        <v>102.78</v>
+        <v>33.18</v>
       </c>
       <c r="L16" t="n">
-        <v>104.74</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:47:23</t>
+          <t>04:47:11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.52</v>
+        <v>3.13</v>
       </c>
       <c r="F17" t="n">
-        <v>11.21</v>
+        <v>7.34</v>
       </c>
       <c r="G17" t="n">
-        <v>282.7</v>
+        <v>278.3</v>
       </c>
       <c r="H17" t="n">
-        <v>36</v>
+        <v>38.8</v>
       </c>
       <c r="I17" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>45.94</v>
+        <v>10.25</v>
       </c>
       <c r="K17" t="n">
-        <v>47.66</v>
+        <v>75.23999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>66.19</v>
+        <v>75.93000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:48:34</t>
+          <t>04:49:19</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.99</v>
+        <v>3.75</v>
       </c>
       <c r="F18" t="n">
-        <v>10.97</v>
+        <v>10.03</v>
       </c>
       <c r="G18" t="n">
-        <v>280.2</v>
+        <v>278.1</v>
       </c>
       <c r="H18" t="n">
-        <v>35.4</v>
+        <v>37.5</v>
       </c>
       <c r="I18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>15.8</v>
+        <v>-1.44</v>
       </c>
       <c r="K18" t="n">
-        <v>-11.51</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>19.54</v>
+        <v>77.84</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:50:22</t>
+          <t>04:50:36</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.34</v>
+        <v>4.12</v>
       </c>
       <c r="F19" t="n">
-        <v>11.31</v>
+        <v>12.54</v>
       </c>
       <c r="G19" t="n">
-        <v>282.6</v>
+        <v>266.3</v>
       </c>
       <c r="H19" t="n">
-        <v>47.8</v>
+        <v>35.3</v>
       </c>
       <c r="I19" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J19" t="n">
-        <v>-87.17</v>
+        <v>-65.37</v>
       </c>
       <c r="K19" t="n">
-        <v>31.03</v>
+        <v>-40.73</v>
       </c>
       <c r="L19" t="n">
-        <v>92.53</v>
+        <v>77.02</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:56:34</t>
+          <t>04:54:27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.59</v>
+        <v>3.73</v>
       </c>
       <c r="F20" t="n">
-        <v>11.33</v>
+        <v>6.67</v>
       </c>
       <c r="G20" t="n">
-        <v>281.4</v>
+        <v>280.8</v>
       </c>
       <c r="H20" t="n">
-        <v>35.9</v>
+        <v>35.1</v>
       </c>
       <c r="I20" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>96.31999999999999</v>
+        <v>-30.47</v>
       </c>
       <c r="K20" t="n">
-        <v>112.12</v>
+        <v>-90.93000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>147.81</v>
+        <v>95.90000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:58:04</t>
+          <t>04:55:16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.11</v>
+        <v>3.06</v>
       </c>
       <c r="F21" t="n">
-        <v>10.7</v>
+        <v>6.23</v>
       </c>
       <c r="G21" t="n">
-        <v>275.3</v>
+        <v>269.3</v>
       </c>
       <c r="H21" t="n">
-        <v>42.6</v>
+        <v>33.2</v>
       </c>
       <c r="I21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>20.48</v>
+        <v>-33.19</v>
       </c>
       <c r="K21" t="n">
-        <v>-98.84</v>
+        <v>-94.09999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>100.94</v>
+        <v>99.78</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:00:35</t>
+          <t>04:57:30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.39</v>
+        <v>4.71</v>
       </c>
       <c r="F22" t="n">
-        <v>10.58</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>280.6</v>
+        <v>282.2</v>
       </c>
       <c r="H22" t="n">
-        <v>44.9</v>
+        <v>40.7</v>
       </c>
       <c r="I22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>74.58</v>
+        <v>-24.23</v>
       </c>
       <c r="K22" t="n">
-        <v>-61.72</v>
+        <v>107.04</v>
       </c>
       <c r="L22" t="n">
-        <v>96.81</v>
+        <v>109.75</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:05:54</t>
+          <t>05:02:35</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.45</v>
+        <v>3.87</v>
       </c>
       <c r="F23" t="n">
-        <v>10.42</v>
+        <v>5.99</v>
       </c>
       <c r="G23" t="n">
-        <v>278.9</v>
+        <v>288.1</v>
       </c>
       <c r="H23" t="n">
-        <v>36.3</v>
+        <v>46</v>
       </c>
       <c r="I23" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-30.72</v>
+        <v>80.61</v>
       </c>
       <c r="K23" t="n">
-        <v>184.98</v>
+        <v>-169.38</v>
       </c>
       <c r="L23" t="n">
-        <v>187.52</v>
+        <v>187.59</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:07:09</t>
+          <t>05:04:51</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.26</v>
+        <v>4.12</v>
       </c>
       <c r="F24" t="n">
-        <v>10.94</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>272.6</v>
+        <v>282.4</v>
       </c>
       <c r="H24" t="n">
-        <v>40.8</v>
+        <v>50.6</v>
       </c>
       <c r="I24" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.58</v>
+        <v>-2.12</v>
       </c>
       <c r="K24" t="n">
-        <v>150.93</v>
+        <v>-142.91</v>
       </c>
       <c r="L24" t="n">
-        <v>150.95</v>
+        <v>142.92</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:09:21</t>
+          <t>05:06:40</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.1</v>
+        <v>4.26</v>
       </c>
       <c r="F25" t="n">
-        <v>11.39</v>
+        <v>9.4</v>
       </c>
       <c r="G25" t="n">
-        <v>285.1</v>
+        <v>274.2</v>
       </c>
       <c r="H25" t="n">
-        <v>43.7</v>
+        <v>43.9</v>
       </c>
       <c r="I25" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J25" t="n">
-        <v>69.94</v>
+        <v>39.59</v>
       </c>
       <c r="K25" t="n">
-        <v>111.71</v>
+        <v>-112.38</v>
       </c>
       <c r="L25" t="n">
-        <v>131.8</v>
+        <v>119.15</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:13:25</t>
+          <t>05:10:58</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="F26" t="n">
-        <v>11.05</v>
+        <v>7.47</v>
       </c>
       <c r="G26" t="n">
-        <v>263.3</v>
+        <v>282.7</v>
       </c>
       <c r="H26" t="n">
-        <v>40.9</v>
+        <v>31.2</v>
       </c>
       <c r="I26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>179.08</v>
+        <v>-186.54</v>
       </c>
       <c r="K26" t="n">
-        <v>95.66</v>
+        <v>-227.05</v>
       </c>
       <c r="L26" t="n">
-        <v>203.03</v>
+        <v>293.86</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:14:42</t>
+          <t>05:12:43</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.67</v>
+        <v>3.3</v>
       </c>
       <c r="F27" t="n">
-        <v>11.11</v>
+        <v>7.68</v>
       </c>
       <c r="G27" t="n">
-        <v>279.6</v>
+        <v>275.6</v>
       </c>
       <c r="H27" t="n">
-        <v>36.8</v>
+        <v>34.8</v>
       </c>
       <c r="I27" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>-146.16</v>
+        <v>-93.56999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>19.06</v>
+        <v>179.11</v>
       </c>
       <c r="L27" t="n">
-        <v>147.4</v>
+        <v>202.08</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:16:50</t>
+          <t>05:15:06</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.52</v>
+        <v>4.22</v>
       </c>
       <c r="F28" t="n">
-        <v>10.5</v>
+        <v>7.42</v>
       </c>
       <c r="G28" t="n">
-        <v>264.9</v>
+        <v>280</v>
       </c>
       <c r="H28" t="n">
-        <v>41.1</v>
+        <v>37.1</v>
       </c>
       <c r="I28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J28" t="n">
-        <v>-196.05</v>
+        <v>-239.27</v>
       </c>
       <c r="K28" t="n">
-        <v>-196.23</v>
+        <v>22.99</v>
       </c>
       <c r="L28" t="n">
-        <v>277.39</v>
+        <v>240.37</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:27:19</t>
+          <t>05:24:30</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.35</v>
+        <v>4.77</v>
       </c>
       <c r="F29" t="n">
-        <v>10.64</v>
+        <v>11.69</v>
       </c>
       <c r="G29" t="n">
-        <v>270.3</v>
+        <v>287.8</v>
       </c>
       <c r="H29" t="n">
-        <v>39.1</v>
+        <v>45.1</v>
       </c>
       <c r="I29" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>-4.83</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>51.72</v>
+        <v>-24.61</v>
       </c>
       <c r="L29" t="n">
-        <v>51.95</v>
+        <v>82.17</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:29:38</t>
+          <t>05:25:50</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>4.27</v>
+        <v>3.82</v>
       </c>
       <c r="F30" t="n">
-        <v>10.86</v>
+        <v>10.35</v>
       </c>
       <c r="G30" t="n">
-        <v>274.7</v>
+        <v>284.4</v>
       </c>
       <c r="H30" t="n">
-        <v>32.7</v>
+        <v>31.2</v>
       </c>
       <c r="I30" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>-65.33</v>
+        <v>56.45</v>
       </c>
       <c r="K30" t="n">
-        <v>4.35</v>
+        <v>27.9</v>
       </c>
       <c r="L30" t="n">
-        <v>65.47</v>
+        <v>62.97</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:31:55</t>
+          <t>05:26:34</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4.79</v>
+        <v>3.32</v>
       </c>
       <c r="F31" t="n">
-        <v>11.25</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>290.7</v>
+        <v>292.8</v>
       </c>
       <c r="H31" t="n">
-        <v>34.9</v>
+        <v>42.4</v>
       </c>
       <c r="I31" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>64.17</v>
+        <v>-1.01</v>
       </c>
       <c r="K31" t="n">
-        <v>-20.07</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>67.23999999999999</v>
+        <v>71.58</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:36:51</t>
+          <t>05:30:56</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.86</v>
+        <v>4.73</v>
       </c>
       <c r="F32" t="n">
-        <v>11.08</v>
+        <v>11.96</v>
       </c>
       <c r="G32" t="n">
-        <v>263</v>
+        <v>282.8</v>
       </c>
       <c r="H32" t="n">
-        <v>42.6</v>
+        <v>41.8</v>
       </c>
       <c r="I32" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>58.4</v>
+        <v>113.04</v>
       </c>
       <c r="K32" t="n">
-        <v>27.62</v>
+        <v>-39.86</v>
       </c>
       <c r="L32" t="n">
-        <v>64.59999999999999</v>
+        <v>119.86</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:38:30</t>
+          <t>05:33:06</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.36</v>
+        <v>4.35</v>
       </c>
       <c r="F33" t="n">
-        <v>11.5</v>
+        <v>8.43</v>
       </c>
       <c r="G33" t="n">
         <v>285.4</v>
       </c>
       <c r="H33" t="n">
-        <v>41.6</v>
+        <v>37.9</v>
       </c>
       <c r="I33" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.99</v>
+        <v>-62.69</v>
       </c>
       <c r="K33" t="n">
-        <v>67.3</v>
+        <v>83.45</v>
       </c>
       <c r="L33" t="n">
-        <v>67.31</v>
+        <v>104.38</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:40:15</t>
+          <t>05:33:43</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.76</v>
+        <v>4.33</v>
       </c>
       <c r="F34" t="n">
-        <v>11</v>
+        <v>11.04</v>
       </c>
       <c r="G34" t="n">
-        <v>284.3</v>
+        <v>286.4</v>
       </c>
       <c r="H34" t="n">
-        <v>40.9</v>
+        <v>40</v>
       </c>
       <c r="I34" t="n">
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>106.44</v>
+        <v>4.51</v>
       </c>
       <c r="K34" t="n">
-        <v>-37.08</v>
+        <v>-24.96</v>
       </c>
       <c r="L34" t="n">
-        <v>112.71</v>
+        <v>25.37</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:45:45</t>
+          <t>05:38:38</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>4.4</v>
+        <v>3.46</v>
       </c>
       <c r="F35" t="n">
-        <v>11.13</v>
+        <v>7.87</v>
       </c>
       <c r="G35" t="n">
-        <v>276.4</v>
+        <v>291</v>
       </c>
       <c r="H35" t="n">
-        <v>39.3</v>
+        <v>41.6</v>
       </c>
       <c r="I35" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J35" t="n">
-        <v>-90.22</v>
+        <v>-61.1</v>
       </c>
       <c r="K35" t="n">
-        <v>118.45</v>
+        <v>-78.61</v>
       </c>
       <c r="L35" t="n">
-        <v>148.9</v>
+        <v>99.56</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:46:41</t>
+          <t>05:40:42</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>4.38</v>
+        <v>3.69</v>
       </c>
       <c r="F36" t="n">
-        <v>11.18</v>
+        <v>8.83</v>
       </c>
       <c r="G36" t="n">
-        <v>280.5</v>
+        <v>283.4</v>
       </c>
       <c r="H36" t="n">
-        <v>41</v>
+        <v>42.4</v>
       </c>
       <c r="I36" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>5.28</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>-34.24</v>
+        <v>90.48</v>
       </c>
       <c r="L36" t="n">
-        <v>34.65</v>
+        <v>132.94</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:48:20</t>
+          <t>05:42:55</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="F37" t="n">
-        <v>11.41</v>
+        <v>9.6</v>
       </c>
       <c r="G37" t="n">
-        <v>283.7</v>
+        <v>280.6</v>
       </c>
       <c r="H37" t="n">
-        <v>39.1</v>
+        <v>41.5</v>
       </c>
       <c r="I37" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>-46.88</v>
+        <v>-10</v>
       </c>
       <c r="K37" t="n">
-        <v>-83.06999999999999</v>
+        <v>-85.31</v>
       </c>
       <c r="L37" t="n">
-        <v>95.39</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:52:25</t>
+          <t>05:46:27</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.73</v>
+        <v>3.29</v>
       </c>
       <c r="F38" t="n">
-        <v>11.03</v>
+        <v>7.59</v>
       </c>
       <c r="G38" t="n">
-        <v>285.5</v>
+        <v>284.7</v>
       </c>
       <c r="H38" t="n">
-        <v>39.3</v>
+        <v>43.2</v>
       </c>
       <c r="I38" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>131.49</v>
+        <v>126.04</v>
       </c>
       <c r="K38" t="n">
-        <v>111.08</v>
+        <v>53.22</v>
       </c>
       <c r="L38" t="n">
-        <v>172.13</v>
+        <v>136.81</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:54:27</t>
+          <t>05:48:18</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.71</v>
+        <v>4.53</v>
       </c>
       <c r="F39" t="n">
-        <v>10.89</v>
+        <v>10.16</v>
       </c>
       <c r="G39" t="n">
-        <v>283.7</v>
+        <v>286.6</v>
       </c>
       <c r="H39" t="n">
-        <v>39.5</v>
+        <v>35.2</v>
       </c>
       <c r="I39" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>18.16</v>
+        <v>-134.6</v>
       </c>
       <c r="K39" t="n">
-        <v>-102.14</v>
+        <v>-63.51</v>
       </c>
       <c r="L39" t="n">
-        <v>103.74</v>
+        <v>148.84</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:55:57</t>
+          <t>05:49:21</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.33</v>
+        <v>4.03</v>
       </c>
       <c r="F40" t="n">
-        <v>11.09</v>
+        <v>6.56</v>
       </c>
       <c r="G40" t="n">
-        <v>287</v>
+        <v>263.9</v>
       </c>
       <c r="H40" t="n">
-        <v>38.6</v>
+        <v>41.9</v>
       </c>
       <c r="I40" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>121.95</v>
+        <v>156.45</v>
       </c>
       <c r="K40" t="n">
-        <v>32.43</v>
+        <v>-27.86</v>
       </c>
       <c r="L40" t="n">
-        <v>126.19</v>
+        <v>158.91</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:59:50</t>
+          <t>05:55:04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>4.57</v>
+        <v>4.48</v>
       </c>
       <c r="F41" t="n">
-        <v>11.19</v>
+        <v>12.54</v>
       </c>
       <c r="G41" t="n">
-        <v>270.9</v>
+        <v>280.2</v>
       </c>
       <c r="H41" t="n">
-        <v>38.8</v>
+        <v>30.6</v>
       </c>
       <c r="I41" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>-169.7</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>-125.36</v>
+        <v>-202.78</v>
       </c>
       <c r="L41" t="n">
-        <v>210.98</v>
+        <v>212.78</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:01:39</t>
+          <t>05:57:30</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.08</v>
+        <v>4.15</v>
       </c>
       <c r="F42" t="n">
-        <v>10.05</v>
+        <v>10.24</v>
       </c>
       <c r="G42" t="n">
-        <v>284.5</v>
+        <v>276.7</v>
       </c>
       <c r="H42" t="n">
-        <v>31.1</v>
+        <v>50.6</v>
       </c>
       <c r="I42" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>246.45</v>
+        <v>109.44</v>
       </c>
       <c r="K42" t="n">
-        <v>-20.58</v>
+        <v>-196.02</v>
       </c>
       <c r="L42" t="n">
-        <v>247.31</v>
+        <v>224.5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:03:16</t>
+          <t>05:58:54</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.51</v>
+        <v>3.9</v>
       </c>
       <c r="F43" t="n">
-        <v>10.87</v>
+        <v>7.93</v>
       </c>
       <c r="G43" t="n">
-        <v>261.9</v>
+        <v>283.5</v>
       </c>
       <c r="H43" t="n">
-        <v>38.3</v>
+        <v>40.7</v>
       </c>
       <c r="I43" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>102.28</v>
+        <v>106.66</v>
       </c>
       <c r="K43" t="n">
-        <v>-177.4</v>
+        <v>152.04</v>
       </c>
       <c r="L43" t="n">
-        <v>204.78</v>
+        <v>185.72</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:13:59</t>
+          <t>06:08:03</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>4.21</v>
+        <v>4.06</v>
       </c>
       <c r="F44" t="n">
-        <v>10.69</v>
+        <v>9.58</v>
       </c>
       <c r="G44" t="n">
-        <v>301.8</v>
+        <v>278.9</v>
       </c>
       <c r="H44" t="n">
-        <v>39.8</v>
+        <v>37.7</v>
       </c>
       <c r="I44" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J44" t="n">
-        <v>48.12</v>
+        <v>83.31</v>
       </c>
       <c r="K44" t="n">
-        <v>-44.71</v>
+        <v>36</v>
       </c>
       <c r="L44" t="n">
-        <v>65.69</v>
+        <v>90.75</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:15:15</t>
+          <t>06:10:25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="F45" t="n">
-        <v>11.04</v>
+        <v>8.77</v>
       </c>
       <c r="G45" t="n">
-        <v>282</v>
+        <v>265</v>
       </c>
       <c r="H45" t="n">
-        <v>44.2</v>
+        <v>43.7</v>
       </c>
       <c r="I45" t="n">
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>51.41</v>
+        <v>-55.88</v>
       </c>
       <c r="K45" t="n">
-        <v>24.04</v>
+        <v>18.06</v>
       </c>
       <c r="L45" t="n">
-        <v>56.76</v>
+        <v>58.72</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:17:06</t>
+          <t>06:11:38</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>4.09</v>
+        <v>4.22</v>
       </c>
       <c r="F46" t="n">
-        <v>10.8</v>
+        <v>10.44</v>
       </c>
       <c r="G46" t="n">
-        <v>276.1</v>
+        <v>283.2</v>
       </c>
       <c r="H46" t="n">
-        <v>38.5</v>
+        <v>44.4</v>
       </c>
       <c r="I46" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>84.01000000000001</v>
+        <v>4.46</v>
       </c>
       <c r="K46" t="n">
-        <v>35.75</v>
+        <v>86.8</v>
       </c>
       <c r="L46" t="n">
-        <v>91.3</v>
+        <v>86.91</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:20:38</t>
+          <t>06:15:10</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.78</v>
+        <v>4.16</v>
       </c>
       <c r="F47" t="n">
-        <v>10.11</v>
+        <v>7.55</v>
       </c>
       <c r="G47" t="n">
-        <v>288</v>
+        <v>279.9</v>
       </c>
       <c r="H47" t="n">
-        <v>40.2</v>
+        <v>38.2</v>
       </c>
       <c r="I47" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J47" t="n">
-        <v>-58.84</v>
+        <v>28.84</v>
       </c>
       <c r="K47" t="n">
-        <v>20.91</v>
+        <v>-63.84</v>
       </c>
       <c r="L47" t="n">
-        <v>62.44</v>
+        <v>70.05</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:22:57</t>
+          <t>06:16:17</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.26</v>
+        <v>3.79</v>
       </c>
       <c r="F48" t="n">
-        <v>11.02</v>
+        <v>11.69</v>
       </c>
       <c r="G48" t="n">
-        <v>289.3</v>
+        <v>282.7</v>
       </c>
       <c r="H48" t="n">
-        <v>39.6</v>
+        <v>35.7</v>
       </c>
       <c r="I48" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>5.36</v>
+        <v>-92.16</v>
       </c>
       <c r="K48" t="n">
-        <v>100.87</v>
+        <v>-33.41</v>
       </c>
       <c r="L48" t="n">
-        <v>101.01</v>
+        <v>98.03</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:25:24</t>
+          <t>06:17:35</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4.2</v>
+        <v>4.51</v>
       </c>
       <c r="F49" t="n">
-        <v>10.86</v>
+        <v>10.14</v>
       </c>
       <c r="G49" t="n">
-        <v>277.1</v>
+        <v>274.5</v>
       </c>
       <c r="H49" t="n">
-        <v>34.4</v>
+        <v>40.2</v>
       </c>
       <c r="I49" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>29.79</v>
+        <v>-60.95</v>
       </c>
       <c r="K49" t="n">
-        <v>-55.84</v>
+        <v>19.76</v>
       </c>
       <c r="L49" t="n">
-        <v>63.29</v>
+        <v>64.06999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:29:57</t>
+          <t>06:21:44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.83</v>
+        <v>3.99</v>
       </c>
       <c r="F50" t="n">
-        <v>11</v>
+        <v>12.02</v>
       </c>
       <c r="G50" t="n">
-        <v>271.9</v>
+        <v>274.7</v>
       </c>
       <c r="H50" t="n">
-        <v>45.6</v>
+        <v>46.8</v>
       </c>
       <c r="I50" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>-128.35</v>
+        <v>35.59</v>
       </c>
       <c r="K50" t="n">
-        <v>-47.92</v>
+        <v>116.08</v>
       </c>
       <c r="L50" t="n">
-        <v>137.01</v>
+        <v>121.41</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:31:13</t>
+          <t>06:23:09</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.55</v>
+        <v>4.1</v>
       </c>
       <c r="F51" t="n">
-        <v>10.59</v>
+        <v>11.85</v>
       </c>
       <c r="G51" t="n">
-        <v>281.1</v>
+        <v>282.4</v>
       </c>
       <c r="H51" t="n">
-        <v>40.2</v>
+        <v>46.4</v>
       </c>
       <c r="I51" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>-92.36</v>
+        <v>-182.44</v>
       </c>
       <c r="K51" t="n">
-        <v>33.26</v>
+        <v>-104.97</v>
       </c>
       <c r="L51" t="n">
-        <v>98.17</v>
+        <v>210.48</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:32:21</t>
+          <t>06:25:28</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="F52" t="n">
-        <v>10.6</v>
+        <v>11.42</v>
       </c>
       <c r="G52" t="n">
-        <v>294.1</v>
+        <v>276.8</v>
       </c>
       <c r="H52" t="n">
-        <v>45</v>
+        <v>34.9</v>
       </c>
       <c r="I52" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>44.64</v>
+        <v>110.04</v>
       </c>
       <c r="K52" t="n">
-        <v>98.64</v>
+        <v>-66.36</v>
       </c>
       <c r="L52" t="n">
-        <v>108.27</v>
+        <v>128.5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:37:06</t>
+          <t>06:29:25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.15</v>
+        <v>4.31</v>
       </c>
       <c r="F53" t="n">
-        <v>10.98</v>
+        <v>12.37</v>
       </c>
       <c r="G53" t="n">
-        <v>293.3</v>
+        <v>267.2</v>
       </c>
       <c r="H53" t="n">
-        <v>43.9</v>
+        <v>40</v>
       </c>
       <c r="I53" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>-221.92</v>
+        <v>-113.34</v>
       </c>
       <c r="K53" t="n">
-        <v>-132.33</v>
+        <v>72</v>
       </c>
       <c r="L53" t="n">
-        <v>258.38</v>
+        <v>134.27</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:38:06</t>
+          <t>06:31:24</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.04</v>
+        <v>3.9</v>
       </c>
       <c r="F54" t="n">
-        <v>10.7</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="G54" t="n">
-        <v>270.3</v>
+        <v>277.1</v>
       </c>
       <c r="H54" t="n">
-        <v>43.4</v>
+        <v>36.4</v>
       </c>
       <c r="I54" t="n">
         <v>27</v>
       </c>
       <c r="J54" t="n">
-        <v>131.89</v>
+        <v>36.18</v>
       </c>
       <c r="K54" t="n">
-        <v>-75.90000000000001</v>
+        <v>148.53</v>
       </c>
       <c r="L54" t="n">
-        <v>152.17</v>
+        <v>152.87</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:40:03</t>
+          <t>06:32:50</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.35</v>
+        <v>3.8</v>
       </c>
       <c r="F55" t="n">
-        <v>10.22</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="G55" t="n">
-        <v>280.5</v>
+        <v>276.9</v>
       </c>
       <c r="H55" t="n">
-        <v>43.5</v>
+        <v>39.4</v>
       </c>
       <c r="I55" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>-56.67</v>
+        <v>-169.69</v>
       </c>
       <c r="K55" t="n">
-        <v>100.43</v>
+        <v>-18.9</v>
       </c>
       <c r="L55" t="n">
-        <v>115.32</v>
+        <v>170.74</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:45:04</t>
+          <t>06:36:33</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.95</v>
+        <v>4.56</v>
       </c>
       <c r="F56" t="n">
-        <v>10.72</v>
+        <v>12.19</v>
       </c>
       <c r="G56" t="n">
-        <v>273.4</v>
+        <v>279.3</v>
       </c>
       <c r="H56" t="n">
-        <v>40.2</v>
+        <v>45.6</v>
       </c>
       <c r="I56" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>87.25</v>
+        <v>141.82</v>
       </c>
       <c r="K56" t="n">
-        <v>196.66</v>
+        <v>-246.3</v>
       </c>
       <c r="L56" t="n">
-        <v>215.15</v>
+        <v>284.21</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:46:18</t>
+          <t>06:37:30</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.85</v>
+        <v>4.17</v>
       </c>
       <c r="F57" t="n">
-        <v>10.7</v>
+        <v>7.77</v>
       </c>
       <c r="G57" t="n">
-        <v>279.4</v>
+        <v>270.7</v>
       </c>
       <c r="H57" t="n">
-        <v>40.8</v>
+        <v>38.6</v>
       </c>
       <c r="I57" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>-196.37</v>
+        <v>114.36</v>
       </c>
       <c r="K57" t="n">
-        <v>-29.8</v>
+        <v>297.33</v>
       </c>
       <c r="L57" t="n">
-        <v>198.62</v>
+        <v>318.57</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:48:27</t>
+          <t>06:39:25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.6</v>
+        <v>4.22</v>
       </c>
       <c r="F58" t="n">
-        <v>10.83</v>
+        <v>11.42</v>
       </c>
       <c r="G58" t="n">
-        <v>291.8</v>
+        <v>265.4</v>
       </c>
       <c r="H58" t="n">
-        <v>41.5</v>
+        <v>38.6</v>
       </c>
       <c r="I58" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>157.63</v>
+        <v>-226.52</v>
       </c>
       <c r="K58" t="n">
-        <v>-198.73</v>
+        <v>211.32</v>
       </c>
       <c r="L58" t="n">
-        <v>253.66</v>
+        <v>309.78</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:58:02</t>
+          <t>06:50:15</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.24</v>
+        <v>4.41</v>
       </c>
       <c r="F59" t="n">
-        <v>10.9</v>
+        <v>11.83</v>
       </c>
       <c r="G59" t="n">
-        <v>270.7</v>
+        <v>276.7</v>
       </c>
       <c r="H59" t="n">
-        <v>39.5</v>
+        <v>46.2</v>
       </c>
       <c r="I59" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>84.8</v>
+        <v>6.42</v>
       </c>
       <c r="K59" t="n">
-        <v>4.37</v>
+        <v>-23.25</v>
       </c>
       <c r="L59" t="n">
-        <v>84.92</v>
+        <v>24.12</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:59:48</t>
+          <t>06:51:56</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.61</v>
+        <v>4.65</v>
       </c>
       <c r="F60" t="n">
-        <v>11.55</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="G60" t="n">
-        <v>265.4</v>
+        <v>279.4</v>
       </c>
       <c r="H60" t="n">
-        <v>38.6</v>
+        <v>41.9</v>
       </c>
       <c r="I60" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>63.43</v>
+        <v>10.72</v>
       </c>
       <c r="K60" t="n">
-        <v>25.12</v>
+        <v>68.19</v>
       </c>
       <c r="L60" t="n">
-        <v>68.23</v>
+        <v>69.02</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:01:47</t>
+          <t>06:54:02</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.83</v>
+        <v>4.58</v>
       </c>
       <c r="F61" t="n">
-        <v>10.94</v>
+        <v>11.72</v>
       </c>
       <c r="G61" t="n">
-        <v>275.1</v>
+        <v>279.9</v>
       </c>
       <c r="H61" t="n">
-        <v>38</v>
+        <v>33.4</v>
       </c>
       <c r="I61" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>61.69</v>
+        <v>-88.36</v>
       </c>
       <c r="K61" t="n">
-        <v>39.36</v>
+        <v>-0.7</v>
       </c>
       <c r="L61" t="n">
-        <v>73.17</v>
+        <v>88.36</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:05:41</t>
+          <t>06:58:56</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.68</v>
+        <v>4.23</v>
       </c>
       <c r="F62" t="n">
-        <v>11</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="G62" t="n">
-        <v>281.1</v>
+        <v>269.8</v>
       </c>
       <c r="H62" t="n">
-        <v>39.4</v>
+        <v>34.4</v>
       </c>
       <c r="I62" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>55.46</v>
+        <v>-76.69</v>
       </c>
       <c r="K62" t="n">
-        <v>-44.03</v>
+        <v>-35.23</v>
       </c>
       <c r="L62" t="n">
-        <v>70.81</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:06:55</t>
+          <t>06:59:42</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.26</v>
+        <v>4.99</v>
       </c>
       <c r="F63" t="n">
-        <v>10.22</v>
+        <v>12.54</v>
       </c>
       <c r="G63" t="n">
-        <v>295.6</v>
+        <v>270.1</v>
       </c>
       <c r="H63" t="n">
-        <v>39.7</v>
+        <v>44.2</v>
       </c>
       <c r="I63" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-16.42</v>
+        <v>10.35</v>
       </c>
       <c r="K63" t="n">
-        <v>49.29</v>
+        <v>112.43</v>
       </c>
       <c r="L63" t="n">
-        <v>51.95</v>
+        <v>112.9</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:07:52</t>
+          <t>07:00:57</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.94</v>
+        <v>3.99</v>
       </c>
       <c r="F64" t="n">
-        <v>10.51</v>
+        <v>10.98</v>
       </c>
       <c r="G64" t="n">
-        <v>291.4</v>
+        <v>286.2</v>
       </c>
       <c r="H64" t="n">
-        <v>34.6</v>
+        <v>42.6</v>
       </c>
       <c r="I64" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>98.42</v>
+        <v>-66.39</v>
       </c>
       <c r="K64" t="n">
-        <v>-34.24</v>
+        <v>25.73</v>
       </c>
       <c r="L64" t="n">
-        <v>104.21</v>
+        <v>71.2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:13:00</t>
+          <t>07:05:47</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.42</v>
+        <v>4.71</v>
       </c>
       <c r="F65" t="n">
-        <v>11.02</v>
+        <v>12.19</v>
       </c>
       <c r="G65" t="n">
-        <v>275.1</v>
+        <v>282</v>
       </c>
       <c r="H65" t="n">
-        <v>34.8</v>
+        <v>47.6</v>
       </c>
       <c r="I65" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-94.23</v>
+        <v>-93.97</v>
       </c>
       <c r="K65" t="n">
-        <v>-52.42</v>
+        <v>53.92</v>
       </c>
       <c r="L65" t="n">
-        <v>107.83</v>
+        <v>108.34</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:14:35</t>
+          <t>07:07:00</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.45</v>
+        <v>3.75</v>
       </c>
       <c r="F66" t="n">
-        <v>10.69</v>
+        <v>11.67</v>
       </c>
       <c r="G66" t="n">
-        <v>274</v>
+        <v>282.5</v>
       </c>
       <c r="H66" t="n">
-        <v>42.8</v>
+        <v>40.4</v>
       </c>
       <c r="I66" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>114.5</v>
+        <v>-108.78</v>
       </c>
       <c r="K66" t="n">
-        <v>-22.92</v>
+        <v>107.22</v>
       </c>
       <c r="L66" t="n">
-        <v>116.77</v>
+        <v>152.74</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:16:09</t>
+          <t>07:09:06</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.3</v>
+        <v>4.89</v>
       </c>
       <c r="F67" t="n">
-        <v>10.91</v>
+        <v>12.54</v>
       </c>
       <c r="G67" t="n">
-        <v>289.4</v>
+        <v>295.6</v>
       </c>
       <c r="H67" t="n">
-        <v>40.7</v>
+        <v>39.6</v>
       </c>
       <c r="I67" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J67" t="n">
-        <v>-101.49</v>
+        <v>131.46</v>
       </c>
       <c r="K67" t="n">
-        <v>-134.18</v>
+        <v>69.36</v>
       </c>
       <c r="L67" t="n">
-        <v>168.24</v>
+        <v>148.63</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:21:56</t>
+          <t>07:15:26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.76</v>
+        <v>4.3</v>
       </c>
       <c r="F68" t="n">
-        <v>10.54</v>
+        <v>11.66</v>
       </c>
       <c r="G68" t="n">
-        <v>270.8</v>
+        <v>291.8</v>
       </c>
       <c r="H68" t="n">
-        <v>40.9</v>
+        <v>39.7</v>
       </c>
       <c r="I68" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J68" t="n">
-        <v>195.78</v>
+        <v>69.7</v>
       </c>
       <c r="K68" t="n">
-        <v>-77.44</v>
+        <v>-313.8</v>
       </c>
       <c r="L68" t="n">
-        <v>210.54</v>
+        <v>321.45</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:24:11</t>
+          <t>07:17:35</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.57</v>
+        <v>5.04</v>
       </c>
       <c r="F69" t="n">
-        <v>11.4</v>
+        <v>12.54</v>
       </c>
       <c r="G69" t="n">
-        <v>277.2</v>
+        <v>278.7</v>
       </c>
       <c r="H69" t="n">
-        <v>47.5</v>
+        <v>42.8</v>
       </c>
       <c r="I69" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J69" t="n">
-        <v>-141.28</v>
+        <v>99.31999999999999</v>
       </c>
       <c r="K69" t="n">
-        <v>52.28</v>
+        <v>156.16</v>
       </c>
       <c r="L69" t="n">
-        <v>150.64</v>
+        <v>185.07</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:26:41</t>
+          <t>07:19:42</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.33</v>
+        <v>4.49</v>
       </c>
       <c r="F70" t="n">
-        <v>11.45</v>
+        <v>12.54</v>
       </c>
       <c r="G70" t="n">
-        <v>280</v>
+        <v>288.7</v>
       </c>
       <c r="H70" t="n">
-        <v>41.3</v>
+        <v>39.6</v>
       </c>
       <c r="I70" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>83.23</v>
+        <v>180.05</v>
       </c>
       <c r="K70" t="n">
-        <v>-307.57</v>
+        <v>143.52</v>
       </c>
       <c r="L70" t="n">
-        <v>318.63</v>
+        <v>230.25</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:30:28</t>
+          <t>07:22:45</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>5.08</v>
+        <v>4.11</v>
       </c>
       <c r="F71" t="n">
-        <v>10.79</v>
+        <v>7.5</v>
       </c>
       <c r="G71" t="n">
-        <v>286.2</v>
+        <v>295.9</v>
       </c>
       <c r="H71" t="n">
-        <v>41.1</v>
+        <v>37.3</v>
       </c>
       <c r="I71" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>175.9</v>
+        <v>-247.59</v>
       </c>
       <c r="K71" t="n">
-        <v>199.86</v>
+        <v>-19.7</v>
       </c>
       <c r="L71" t="n">
-        <v>266.24</v>
+        <v>248.38</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:32:41</t>
+          <t>07:24:08</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.53</v>
+        <v>4.08</v>
       </c>
       <c r="F72" t="n">
-        <v>11.3</v>
+        <v>10.17</v>
       </c>
       <c r="G72" t="n">
-        <v>279.9</v>
+        <v>283</v>
       </c>
       <c r="H72" t="n">
-        <v>44.2</v>
+        <v>37.1</v>
       </c>
       <c r="I72" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J72" t="n">
-        <v>264.39</v>
+        <v>-215.04</v>
       </c>
       <c r="K72" t="n">
-        <v>176.97</v>
+        <v>-243.31</v>
       </c>
       <c r="L72" t="n">
-        <v>318.15</v>
+        <v>324.72</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:34:03</t>
+          <t>07:26:05</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.14</v>
+        <v>4.45</v>
       </c>
       <c r="F73" t="n">
-        <v>11.65</v>
+        <v>12.54</v>
       </c>
       <c r="G73" t="n">
-        <v>275.2</v>
+        <v>288.8</v>
       </c>
       <c r="H73" t="n">
-        <v>42.6</v>
+        <v>46.4</v>
       </c>
       <c r="I73" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>-211.12</v>
+        <v>416.32</v>
       </c>
       <c r="K73" t="n">
-        <v>-52.53</v>
+        <v>-249.18</v>
       </c>
       <c r="L73" t="n">
-        <v>217.56</v>
+        <v>485.2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:42:41</t>
+          <t>07:37:17</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.14</v>
+        <v>3.61</v>
       </c>
       <c r="F74" t="n">
-        <v>11.01</v>
+        <v>10.29</v>
       </c>
       <c r="G74" t="n">
-        <v>274.8</v>
+        <v>286.4</v>
       </c>
       <c r="H74" t="n">
-        <v>38.8</v>
+        <v>39.8</v>
       </c>
       <c r="I74" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J74" t="n">
-        <v>-43.88</v>
+        <v>-48.19</v>
       </c>
       <c r="K74" t="n">
-        <v>-70.75</v>
+        <v>-34.57</v>
       </c>
       <c r="L74" t="n">
-        <v>83.25</v>
+        <v>59.31</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:44:38</t>
+          <t>07:38:32</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.5</v>
+        <v>4.31</v>
       </c>
       <c r="F75" t="n">
-        <v>11.3</v>
+        <v>10.61</v>
       </c>
       <c r="G75" t="n">
-        <v>293.4</v>
+        <v>279.2</v>
       </c>
       <c r="H75" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="I75" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>103.64</v>
+        <v>-47.19</v>
       </c>
       <c r="K75" t="n">
-        <v>-58.9</v>
+        <v>-54.61</v>
       </c>
       <c r="L75" t="n">
-        <v>119.21</v>
+        <v>72.17</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:46:47</t>
+          <t>07:40:17</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.63</v>
+        <v>4.49</v>
       </c>
       <c r="F76" t="n">
-        <v>11.18</v>
+        <v>10.51</v>
       </c>
       <c r="G76" t="n">
-        <v>280.2</v>
+        <v>296.2</v>
       </c>
       <c r="H76" t="n">
-        <v>42.1</v>
+        <v>45.5</v>
       </c>
       <c r="I76" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>-42.22</v>
+        <v>51.82</v>
       </c>
       <c r="K76" t="n">
-        <v>-31.54</v>
+        <v>-85.06999999999999</v>
       </c>
       <c r="L76" t="n">
-        <v>52.7</v>
+        <v>99.61</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:51:59</t>
+          <t>07:45:33</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.35</v>
+        <v>4.77</v>
       </c>
       <c r="F77" t="n">
-        <v>10.82</v>
+        <v>12.54</v>
       </c>
       <c r="G77" t="n">
-        <v>285.4</v>
+        <v>274.3</v>
       </c>
       <c r="H77" t="n">
-        <v>38.9</v>
+        <v>39.8</v>
       </c>
       <c r="I77" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>-57.49</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>-66.43000000000001</v>
+        <v>-5.4</v>
       </c>
       <c r="L77" t="n">
-        <v>87.84999999999999</v>
+        <v>93.56</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:53:19</t>
+          <t>07:47:28</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.53</v>
+        <v>5.14</v>
       </c>
       <c r="F78" t="n">
-        <v>11.67</v>
+        <v>12.54</v>
       </c>
       <c r="G78" t="n">
-        <v>291.5</v>
+        <v>278.5</v>
       </c>
       <c r="H78" t="n">
-        <v>36.6</v>
+        <v>33.6</v>
       </c>
       <c r="I78" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>58.06</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>-95.52</v>
+        <v>13.17</v>
       </c>
       <c r="L78" t="n">
-        <v>111.78</v>
+        <v>91.91</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:54:43</t>
+          <t>07:48:55</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.8</v>
+        <v>3.68</v>
       </c>
       <c r="F79" t="n">
-        <v>10.58</v>
+        <v>8.18</v>
       </c>
       <c r="G79" t="n">
-        <v>280.3</v>
+        <v>278.4</v>
       </c>
       <c r="H79" t="n">
-        <v>36.3</v>
+        <v>43.3</v>
       </c>
       <c r="I79" t="n">
         <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>92.44</v>
+        <v>37.22</v>
       </c>
       <c r="K79" t="n">
-        <v>-5.08</v>
+        <v>-66.42</v>
       </c>
       <c r="L79" t="n">
-        <v>92.58</v>
+        <v>76.14</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:59:22</t>
+          <t>07:54:15</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>5.17</v>
+        <v>4.58</v>
       </c>
       <c r="F80" t="n">
-        <v>10.79</v>
+        <v>11.74</v>
       </c>
       <c r="G80" t="n">
-        <v>267.8</v>
+        <v>281.6</v>
       </c>
       <c r="H80" t="n">
-        <v>46.1</v>
+        <v>41.7</v>
       </c>
       <c r="I80" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>145.22</v>
+        <v>-143.63</v>
       </c>
       <c r="K80" t="n">
-        <v>18.57</v>
+        <v>59.87</v>
       </c>
       <c r="L80" t="n">
-        <v>146.41</v>
+        <v>155.6</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:01:13</t>
+          <t>07:56:40</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.71</v>
+        <v>4.79</v>
       </c>
       <c r="F81" t="n">
-        <v>10.78</v>
+        <v>12.54</v>
       </c>
       <c r="G81" t="n">
-        <v>287.2</v>
+        <v>279.9</v>
       </c>
       <c r="H81" t="n">
-        <v>43.8</v>
+        <v>35.7</v>
       </c>
       <c r="I81" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>55.44</v>
+        <v>-24.79</v>
       </c>
       <c r="K81" t="n">
-        <v>-97.15000000000001</v>
+        <v>-120.82</v>
       </c>
       <c r="L81" t="n">
-        <v>111.86</v>
+        <v>123.34</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:02:11</t>
+          <t>07:58:54</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.61</v>
+        <v>4.72</v>
       </c>
       <c r="F82" t="n">
-        <v>10.94</v>
+        <v>12.54</v>
       </c>
       <c r="G82" t="n">
-        <v>284</v>
+        <v>277.2</v>
       </c>
       <c r="H82" t="n">
-        <v>39</v>
+        <v>38.6</v>
       </c>
       <c r="I82" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J82" t="n">
-        <v>-125.2</v>
+        <v>-108.48</v>
       </c>
       <c r="K82" t="n">
-        <v>55.65</v>
+        <v>59.67</v>
       </c>
       <c r="L82" t="n">
-        <v>137.01</v>
+        <v>123.81</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:08:13</t>
+          <t>08:02:41</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.82</v>
+        <v>4.47</v>
       </c>
       <c r="F83" t="n">
-        <v>10.93</v>
+        <v>12.54</v>
       </c>
       <c r="G83" t="n">
-        <v>287.9</v>
+        <v>292.1</v>
       </c>
       <c r="H83" t="n">
-        <v>39.7</v>
+        <v>42.6</v>
       </c>
       <c r="I83" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>73.59999999999999</v>
+        <v>85</v>
       </c>
       <c r="K83" t="n">
-        <v>-178.6</v>
+        <v>-61.84</v>
       </c>
       <c r="L83" t="n">
-        <v>193.17</v>
+        <v>105.11</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:10:22</t>
+          <t>08:04:19</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.57</v>
+        <v>4.49</v>
       </c>
       <c r="F84" t="n">
-        <v>10.62</v>
+        <v>12.52</v>
       </c>
       <c r="G84" t="n">
-        <v>282.2</v>
+        <v>287.8</v>
       </c>
       <c r="H84" t="n">
-        <v>38.3</v>
+        <v>26.3</v>
       </c>
       <c r="I84" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-21.21</v>
+        <v>-95.14</v>
       </c>
       <c r="K84" t="n">
-        <v>-114.1</v>
+        <v>154.93</v>
       </c>
       <c r="L84" t="n">
-        <v>116.06</v>
+        <v>181.81</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:13:04</t>
+          <t>08:06:39</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>5.56</v>
+        <v>4.68</v>
       </c>
       <c r="F85" t="n">
-        <v>10.78</v>
+        <v>12.54</v>
       </c>
       <c r="G85" t="n">
-        <v>285.4</v>
+        <v>279.5</v>
       </c>
       <c r="H85" t="n">
-        <v>45.7</v>
+        <v>39.9</v>
       </c>
       <c r="I85" t="n">
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>1.54</v>
+        <v>-11.99</v>
       </c>
       <c r="K85" t="n">
-        <v>201.57</v>
+        <v>181.93</v>
       </c>
       <c r="L85" t="n">
-        <v>201.58</v>
+        <v>182.32</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:16:49</t>
+          <t>08:11:36</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.61</v>
+        <v>4.91</v>
       </c>
       <c r="F86" t="n">
-        <v>10.78</v>
+        <v>10.51</v>
       </c>
       <c r="G86" t="n">
-        <v>288.3</v>
+        <v>282.1</v>
       </c>
       <c r="H86" t="n">
-        <v>43.6</v>
+        <v>34.8</v>
       </c>
       <c r="I86" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>122.89</v>
+        <v>-166.4</v>
       </c>
       <c r="K86" t="n">
-        <v>-182.99</v>
+        <v>372.24</v>
       </c>
       <c r="L86" t="n">
-        <v>220.42</v>
+        <v>407.73</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:18:56</t>
+          <t>08:13:37</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.94</v>
+        <v>4.51</v>
       </c>
       <c r="F87" t="n">
-        <v>11.02</v>
+        <v>12.54</v>
       </c>
       <c r="G87" t="n">
-        <v>274.2</v>
+        <v>273.3</v>
       </c>
       <c r="H87" t="n">
-        <v>39.5</v>
+        <v>50.5</v>
       </c>
       <c r="I87" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J87" t="n">
-        <v>233.94</v>
+        <v>-216.86</v>
       </c>
       <c r="K87" t="n">
-        <v>172.57</v>
+        <v>256.21</v>
       </c>
       <c r="L87" t="n">
-        <v>290.71</v>
+        <v>335.67</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:20:48</t>
+          <t>08:14:26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.91</v>
+        <v>4.76</v>
       </c>
       <c r="F88" t="n">
-        <v>10.7</v>
+        <v>11.41</v>
       </c>
       <c r="G88" t="n">
-        <v>280.5</v>
+        <v>283.7</v>
       </c>
       <c r="H88" t="n">
-        <v>40.8</v>
+        <v>45.6</v>
       </c>
       <c r="I88" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>158.17</v>
+        <v>-156.34</v>
       </c>
       <c r="K88" t="n">
-        <v>242</v>
+        <v>211.21</v>
       </c>
       <c r="L88" t="n">
-        <v>289.1</v>
+        <v>262.78</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-06.xlsx
+++ b/output/2024-07-06.xlsx
@@ -640,13 +640,13 @@
         <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>-25.78</v>
+        <v>-24.12</v>
       </c>
       <c r="K14" t="n">
-        <v>-76.79000000000001</v>
+        <v>-71.86</v>
       </c>
       <c r="L14" t="n">
-        <v>81</v>
+        <v>75.81</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>27</v>
       </c>
       <c r="J15" t="n">
-        <v>14.28</v>
+        <v>13.32</v>
       </c>
       <c r="K15" t="n">
-        <v>61.61</v>
+        <v>57.46</v>
       </c>
       <c r="L15" t="n">
-        <v>63.25</v>
+        <v>58.98</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>-22.15</v>
+        <v>-23.36</v>
       </c>
       <c r="K16" t="n">
-        <v>33.18</v>
+        <v>34.99</v>
       </c>
       <c r="L16" t="n">
-        <v>39.9</v>
+        <v>42.07</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>10.25</v>
+        <v>10.45</v>
       </c>
       <c r="K17" t="n">
-        <v>75.23999999999999</v>
+        <v>76.70999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>75.93000000000001</v>
+        <v>77.42</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.44</v>
+        <v>-1.38</v>
       </c>
       <c r="K18" t="n">
-        <v>77.81999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>77.84</v>
+        <v>74.41</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>27</v>
       </c>
       <c r="J19" t="n">
-        <v>-65.37</v>
+        <v>-60.94</v>
       </c>
       <c r="K19" t="n">
-        <v>-40.73</v>
+        <v>-37.97</v>
       </c>
       <c r="L19" t="n">
-        <v>77.02</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-30.47</v>
+        <v>-29.82</v>
       </c>
       <c r="K20" t="n">
-        <v>-90.93000000000001</v>
+        <v>-89</v>
       </c>
       <c r="L20" t="n">
-        <v>95.90000000000001</v>
+        <v>93.87</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>-33.19</v>
+        <v>-31.07</v>
       </c>
       <c r="K21" t="n">
-        <v>-94.09999999999999</v>
+        <v>-88.09</v>
       </c>
       <c r="L21" t="n">
-        <v>99.78</v>
+        <v>93.41</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>-24.23</v>
+        <v>-22.63</v>
       </c>
       <c r="K22" t="n">
-        <v>107.04</v>
+        <v>99.98</v>
       </c>
       <c r="L22" t="n">
-        <v>109.75</v>
+        <v>102.51</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>80.61</v>
+        <v>80.67</v>
       </c>
       <c r="K23" t="n">
-        <v>-169.38</v>
+        <v>-169.51</v>
       </c>
       <c r="L23" t="n">
-        <v>187.59</v>
+        <v>187.72</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.12</v>
+        <v>-2.2</v>
       </c>
       <c r="K24" t="n">
-        <v>-142.91</v>
+        <v>-148.55</v>
       </c>
       <c r="L24" t="n">
-        <v>142.92</v>
+        <v>148.57</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>26</v>
       </c>
       <c r="J25" t="n">
-        <v>39.59</v>
+        <v>37.98</v>
       </c>
       <c r="K25" t="n">
-        <v>-112.38</v>
+        <v>-107.82</v>
       </c>
       <c r="L25" t="n">
-        <v>119.15</v>
+        <v>114.32</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-186.54</v>
+        <v>-194.51</v>
       </c>
       <c r="K26" t="n">
-        <v>-227.05</v>
+        <v>-236.75</v>
       </c>
       <c r="L26" t="n">
-        <v>293.86</v>
+        <v>306.4</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>-93.56999999999999</v>
+        <v>-98.91</v>
       </c>
       <c r="K27" t="n">
-        <v>179.11</v>
+        <v>189.33</v>
       </c>
       <c r="L27" t="n">
-        <v>202.08</v>
+        <v>213.62</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>27</v>
       </c>
       <c r="J28" t="n">
-        <v>-239.27</v>
+        <v>-225.62</v>
       </c>
       <c r="K28" t="n">
-        <v>22.99</v>
+        <v>21.68</v>
       </c>
       <c r="L28" t="n">
-        <v>240.37</v>
+        <v>226.66</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>78.40000000000001</v>
+        <v>80.84</v>
       </c>
       <c r="K29" t="n">
-        <v>-24.61</v>
+        <v>-25.38</v>
       </c>
       <c r="L29" t="n">
-        <v>82.17</v>
+        <v>84.73</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>56.45</v>
+        <v>52.7</v>
       </c>
       <c r="K30" t="n">
-        <v>27.9</v>
+        <v>26.05</v>
       </c>
       <c r="L30" t="n">
-        <v>62.97</v>
+        <v>58.79</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>-1.01</v>
+        <v>-1.03</v>
       </c>
       <c r="K31" t="n">
-        <v>71.56999999999999</v>
+        <v>72.95</v>
       </c>
       <c r="L31" t="n">
-        <v>71.58</v>
+        <v>72.95999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>113.04</v>
+        <v>114.47</v>
       </c>
       <c r="K32" t="n">
-        <v>-39.86</v>
+        <v>-40.37</v>
       </c>
       <c r="L32" t="n">
-        <v>119.86</v>
+        <v>121.38</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>-62.69</v>
+        <v>-64.77</v>
       </c>
       <c r="K33" t="n">
-        <v>83.45</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>104.38</v>
+        <v>107.83</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>4.51</v>
+        <v>4.58</v>
       </c>
       <c r="K34" t="n">
-        <v>-24.96</v>
+        <v>-25.32</v>
       </c>
       <c r="L34" t="n">
-        <v>25.37</v>
+        <v>25.74</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>26</v>
       </c>
       <c r="J35" t="n">
-        <v>-61.1</v>
+        <v>-58.53</v>
       </c>
       <c r="K35" t="n">
-        <v>-78.61</v>
+        <v>-75.3</v>
       </c>
       <c r="L35" t="n">
-        <v>99.56</v>
+        <v>95.37</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>97.40000000000001</v>
+        <v>99.23</v>
       </c>
       <c r="K36" t="n">
-        <v>90.48</v>
+        <v>92.18000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>132.94</v>
+        <v>135.44</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>-10</v>
+        <v>-9.57</v>
       </c>
       <c r="K37" t="n">
-        <v>-85.31</v>
+        <v>-81.7</v>
       </c>
       <c r="L37" t="n">
-        <v>85.90000000000001</v>
+        <v>82.26000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>126.04</v>
+        <v>126.05</v>
       </c>
       <c r="K38" t="n">
         <v>53.22</v>
       </c>
       <c r="L38" t="n">
-        <v>136.81</v>
+        <v>136.82</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>-134.6</v>
+        <v>-126.96</v>
       </c>
       <c r="K39" t="n">
-        <v>-63.51</v>
+        <v>-59.91</v>
       </c>
       <c r="L39" t="n">
-        <v>148.84</v>
+        <v>140.38</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>156.45</v>
+        <v>159.67</v>
       </c>
       <c r="K40" t="n">
-        <v>-27.86</v>
+        <v>-28.44</v>
       </c>
       <c r="L40" t="n">
-        <v>158.91</v>
+        <v>162.18</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>64.45999999999999</v>
+        <v>62.69</v>
       </c>
       <c r="K41" t="n">
-        <v>-202.78</v>
+        <v>-197.22</v>
       </c>
       <c r="L41" t="n">
-        <v>212.78</v>
+        <v>206.95</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>109.44</v>
+        <v>110.18</v>
       </c>
       <c r="K42" t="n">
-        <v>-196.02</v>
+        <v>-197.35</v>
       </c>
       <c r="L42" t="n">
-        <v>224.5</v>
+        <v>226.02</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>106.66</v>
+        <v>109.31</v>
       </c>
       <c r="K43" t="n">
-        <v>152.04</v>
+        <v>155.82</v>
       </c>
       <c r="L43" t="n">
-        <v>185.72</v>
+        <v>190.34</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>26</v>
       </c>
       <c r="J44" t="n">
-        <v>83.31</v>
+        <v>79.52</v>
       </c>
       <c r="K44" t="n">
-        <v>36</v>
+        <v>34.36</v>
       </c>
       <c r="L44" t="n">
-        <v>90.75</v>
+        <v>86.63</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>-55.88</v>
+        <v>-55.74</v>
       </c>
       <c r="K45" t="n">
-        <v>18.06</v>
+        <v>18.02</v>
       </c>
       <c r="L45" t="n">
-        <v>58.72</v>
+        <v>58.58</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>4.46</v>
+        <v>4.44</v>
       </c>
       <c r="K46" t="n">
-        <v>86.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>86.91</v>
+        <v>86.51000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>21</v>
       </c>
       <c r="J47" t="n">
-        <v>28.84</v>
+        <v>30.34</v>
       </c>
       <c r="K47" t="n">
-        <v>-63.84</v>
+        <v>-67.16</v>
       </c>
       <c r="L47" t="n">
-        <v>70.05</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>-92.16</v>
+        <v>-90.04000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>-33.41</v>
+        <v>-32.64</v>
       </c>
       <c r="L48" t="n">
-        <v>98.03</v>
+        <v>95.78</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>-60.95</v>
+        <v>-59.36</v>
       </c>
       <c r="K49" t="n">
-        <v>19.76</v>
+        <v>19.24</v>
       </c>
       <c r="L49" t="n">
-        <v>64.06999999999999</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>35.59</v>
+        <v>34.06</v>
       </c>
       <c r="K50" t="n">
-        <v>116.08</v>
+        <v>111.1</v>
       </c>
       <c r="L50" t="n">
-        <v>121.41</v>
+        <v>116.21</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>-182.44</v>
+        <v>-182.17</v>
       </c>
       <c r="K51" t="n">
-        <v>-104.97</v>
+        <v>-104.82</v>
       </c>
       <c r="L51" t="n">
-        <v>210.48</v>
+        <v>210.18</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>110.04</v>
+        <v>112.06</v>
       </c>
       <c r="K52" t="n">
-        <v>-66.36</v>
+        <v>-67.56999999999999</v>
       </c>
       <c r="L52" t="n">
-        <v>128.5</v>
+        <v>130.85</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>-113.34</v>
+        <v>-108.75</v>
       </c>
       <c r="K53" t="n">
-        <v>72</v>
+        <v>69.08</v>
       </c>
       <c r="L53" t="n">
-        <v>134.27</v>
+        <v>128.84</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>27</v>
       </c>
       <c r="J54" t="n">
-        <v>36.18</v>
+        <v>33.9</v>
       </c>
       <c r="K54" t="n">
-        <v>148.53</v>
+        <v>139.15</v>
       </c>
       <c r="L54" t="n">
-        <v>152.87</v>
+        <v>143.22</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>-169.69</v>
+        <v>-179.41</v>
       </c>
       <c r="K55" t="n">
-        <v>-18.9</v>
+        <v>-19.98</v>
       </c>
       <c r="L55" t="n">
-        <v>170.74</v>
+        <v>180.52</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>141.82</v>
+        <v>146.84</v>
       </c>
       <c r="K56" t="n">
-        <v>-246.3</v>
+        <v>-255.02</v>
       </c>
       <c r="L56" t="n">
-        <v>284.21</v>
+        <v>294.27</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>114.36</v>
+        <v>110.35</v>
       </c>
       <c r="K57" t="n">
-        <v>297.33</v>
+        <v>286.92</v>
       </c>
       <c r="L57" t="n">
-        <v>318.57</v>
+        <v>307.41</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>-226.52</v>
+        <v>-218.65</v>
       </c>
       <c r="K58" t="n">
-        <v>211.32</v>
+        <v>203.98</v>
       </c>
       <c r="L58" t="n">
-        <v>309.78</v>
+        <v>299.03</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>6.42</v>
+        <v>6.12</v>
       </c>
       <c r="K59" t="n">
-        <v>-23.25</v>
+        <v>-22.16</v>
       </c>
       <c r="L59" t="n">
-        <v>24.12</v>
+        <v>22.99</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>10.72</v>
+        <v>10.2</v>
       </c>
       <c r="K60" t="n">
-        <v>68.19</v>
+        <v>64.92</v>
       </c>
       <c r="L60" t="n">
-        <v>69.02</v>
+        <v>65.70999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>-88.36</v>
+        <v>-89.53</v>
       </c>
       <c r="K61" t="n">
         <v>-0.7</v>
       </c>
       <c r="L61" t="n">
-        <v>88.36</v>
+        <v>89.53</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-76.69</v>
+        <v>-76.34</v>
       </c>
       <c r="K62" t="n">
-        <v>-35.23</v>
+        <v>-35.06</v>
       </c>
       <c r="L62" t="n">
-        <v>84.40000000000001</v>
+        <v>84</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>10.35</v>
+        <v>10.27</v>
       </c>
       <c r="K63" t="n">
-        <v>112.43</v>
+        <v>111.54</v>
       </c>
       <c r="L63" t="n">
-        <v>112.9</v>
+        <v>112.01</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>-66.39</v>
+        <v>-63.4</v>
       </c>
       <c r="K64" t="n">
-        <v>25.73</v>
+        <v>24.57</v>
       </c>
       <c r="L64" t="n">
-        <v>71.2</v>
+        <v>67.98999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-93.97</v>
+        <v>-97.36</v>
       </c>
       <c r="K65" t="n">
-        <v>53.92</v>
+        <v>55.87</v>
       </c>
       <c r="L65" t="n">
-        <v>108.34</v>
+        <v>112.25</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>-108.78</v>
+        <v>-114.83</v>
       </c>
       <c r="K66" t="n">
-        <v>107.22</v>
+        <v>113.19</v>
       </c>
       <c r="L66" t="n">
-        <v>152.74</v>
+        <v>161.24</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>21</v>
       </c>
       <c r="J67" t="n">
-        <v>131.46</v>
+        <v>138.48</v>
       </c>
       <c r="K67" t="n">
-        <v>69.36</v>
+        <v>73.06</v>
       </c>
       <c r="L67" t="n">
-        <v>148.63</v>
+        <v>156.57</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>23</v>
       </c>
       <c r="J68" t="n">
-        <v>69.7</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="K68" t="n">
-        <v>-313.8</v>
+        <v>-320.34</v>
       </c>
       <c r="L68" t="n">
-        <v>321.45</v>
+        <v>328.15</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>21</v>
       </c>
       <c r="J69" t="n">
-        <v>99.31999999999999</v>
+        <v>105.91</v>
       </c>
       <c r="K69" t="n">
-        <v>156.16</v>
+        <v>166.51</v>
       </c>
       <c r="L69" t="n">
-        <v>185.07</v>
+        <v>197.34</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>180.05</v>
+        <v>187.24</v>
       </c>
       <c r="K70" t="n">
-        <v>143.52</v>
+        <v>149.25</v>
       </c>
       <c r="L70" t="n">
-        <v>230.25</v>
+        <v>239.44</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>-247.59</v>
+        <v>-263.32</v>
       </c>
       <c r="K71" t="n">
-        <v>-19.7</v>
+        <v>-20.95</v>
       </c>
       <c r="L71" t="n">
-        <v>248.38</v>
+        <v>264.15</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>23</v>
       </c>
       <c r="J72" t="n">
-        <v>-215.04</v>
+        <v>-220.65</v>
       </c>
       <c r="K72" t="n">
-        <v>-243.31</v>
+        <v>-249.66</v>
       </c>
       <c r="L72" t="n">
-        <v>324.72</v>
+        <v>333.19</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>416.32</v>
+        <v>446.33</v>
       </c>
       <c r="K73" t="n">
-        <v>-249.18</v>
+        <v>-267.14</v>
       </c>
       <c r="L73" t="n">
-        <v>485.2</v>
+        <v>520.16</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>27</v>
       </c>
       <c r="J74" t="n">
-        <v>-48.19</v>
+        <v>-45.04</v>
       </c>
       <c r="K74" t="n">
-        <v>-34.57</v>
+        <v>-32.31</v>
       </c>
       <c r="L74" t="n">
-        <v>59.31</v>
+        <v>55.43</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>-47.19</v>
+        <v>-44.99</v>
       </c>
       <c r="K75" t="n">
-        <v>-54.61</v>
+        <v>-52.07</v>
       </c>
       <c r="L75" t="n">
-        <v>72.17</v>
+        <v>68.81999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>51.82</v>
+        <v>50.46</v>
       </c>
       <c r="K76" t="n">
-        <v>-85.06999999999999</v>
+        <v>-82.84</v>
       </c>
       <c r="L76" t="n">
-        <v>99.61</v>
+        <v>97</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>93.40000000000001</v>
+        <v>86.83</v>
       </c>
       <c r="K77" t="n">
-        <v>-5.4</v>
+        <v>-5.02</v>
       </c>
       <c r="L77" t="n">
-        <v>93.56</v>
+        <v>86.98</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>90.95999999999999</v>
+        <v>90.19</v>
       </c>
       <c r="K78" t="n">
-        <v>13.17</v>
+        <v>13.06</v>
       </c>
       <c r="L78" t="n">
-        <v>91.91</v>
+        <v>91.13</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>37.22</v>
+        <v>35.59</v>
       </c>
       <c r="K79" t="n">
-        <v>-66.42</v>
+        <v>-63.52</v>
       </c>
       <c r="L79" t="n">
-        <v>76.14</v>
+        <v>72.81</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>-143.63</v>
+        <v>-146.14</v>
       </c>
       <c r="K80" t="n">
-        <v>59.87</v>
+        <v>60.91</v>
       </c>
       <c r="L80" t="n">
-        <v>155.6</v>
+        <v>158.32</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-24.79</v>
+        <v>-23.15</v>
       </c>
       <c r="K81" t="n">
-        <v>-120.82</v>
+        <v>-112.84</v>
       </c>
       <c r="L81" t="n">
-        <v>123.34</v>
+        <v>115.19</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>27</v>
       </c>
       <c r="J82" t="n">
-        <v>-108.48</v>
+        <v>-101.33</v>
       </c>
       <c r="K82" t="n">
-        <v>59.67</v>
+        <v>55.73</v>
       </c>
       <c r="L82" t="n">
-        <v>123.81</v>
+        <v>115.64</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>85</v>
+        <v>79.69</v>
       </c>
       <c r="K83" t="n">
-        <v>-61.84</v>
+        <v>-57.97</v>
       </c>
       <c r="L83" t="n">
-        <v>105.11</v>
+        <v>98.54000000000001</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-95.14</v>
+        <v>-100.67</v>
       </c>
       <c r="K84" t="n">
-        <v>154.93</v>
+        <v>163.93</v>
       </c>
       <c r="L84" t="n">
-        <v>181.81</v>
+        <v>192.37</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>-11.99</v>
+        <v>-11.84</v>
       </c>
       <c r="K85" t="n">
-        <v>181.93</v>
+        <v>179.65</v>
       </c>
       <c r="L85" t="n">
-        <v>182.32</v>
+        <v>180.04</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>-166.4</v>
+        <v>-165.91</v>
       </c>
       <c r="K86" t="n">
-        <v>372.24</v>
+        <v>371.14</v>
       </c>
       <c r="L86" t="n">
-        <v>407.73</v>
+        <v>406.54</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>26</v>
       </c>
       <c r="J87" t="n">
-        <v>-216.86</v>
+        <v>-210.96</v>
       </c>
       <c r="K87" t="n">
-        <v>256.21</v>
+        <v>249.24</v>
       </c>
       <c r="L87" t="n">
-        <v>335.67</v>
+        <v>326.54</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-156.34</v>
+        <v>-167.98</v>
       </c>
       <c r="K88" t="n">
-        <v>211.21</v>
+        <v>226.94</v>
       </c>
       <c r="L88" t="n">
-        <v>262.78</v>
+        <v>282.34</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-06.xlsx
+++ b/output/2024-07-06.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.32</v>
+        <v>3.59</v>
       </c>
       <c r="F14" t="n">
-        <v>7.89</v>
+        <v>11.38</v>
       </c>
       <c r="G14" t="n">
-        <v>295.8</v>
+        <v>280.6</v>
       </c>
       <c r="H14" t="n">
-        <v>44.4</v>
+        <v>62.3</v>
       </c>
       <c r="I14" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>-24.12</v>
+        <v>12.23</v>
       </c>
       <c r="K14" t="n">
-        <v>-71.86</v>
+        <v>-65.75</v>
       </c>
       <c r="L14" t="n">
-        <v>75.81</v>
+        <v>66.88</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:40:14</t>
+          <t>04:40:08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>4.05</v>
+        <v>3.07</v>
       </c>
       <c r="F15" t="n">
-        <v>12.54</v>
+        <v>4.89</v>
       </c>
       <c r="G15" t="n">
-        <v>286.8</v>
+        <v>277.1</v>
       </c>
       <c r="H15" t="n">
-        <v>48.5</v>
+        <v>51.7</v>
       </c>
       <c r="I15" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>13.32</v>
+        <v>-55.64</v>
       </c>
       <c r="K15" t="n">
-        <v>57.46</v>
+        <v>24.03</v>
       </c>
       <c r="L15" t="n">
-        <v>58.98</v>
+        <v>60.61</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:43:04</t>
+          <t>04:41:33</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.69</v>
+        <v>3.85</v>
       </c>
       <c r="F16" t="n">
-        <v>10.07</v>
+        <v>8.41</v>
       </c>
       <c r="G16" t="n">
-        <v>280.7</v>
+        <v>273.8</v>
       </c>
       <c r="H16" t="n">
-        <v>42.5</v>
+        <v>60.5</v>
       </c>
       <c r="I16" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-23.36</v>
+        <v>60.98</v>
       </c>
       <c r="K16" t="n">
-        <v>34.99</v>
+        <v>34.21</v>
       </c>
       <c r="L16" t="n">
-        <v>42.07</v>
+        <v>69.92</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:47:11</t>
+          <t>04:46:36</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.13</v>
+        <v>3.87</v>
       </c>
       <c r="F17" t="n">
-        <v>7.34</v>
+        <v>7.17</v>
       </c>
       <c r="G17" t="n">
-        <v>278.3</v>
+        <v>284.1</v>
       </c>
       <c r="H17" t="n">
-        <v>38.8</v>
+        <v>60.6</v>
       </c>
       <c r="I17" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>10.45</v>
+        <v>-102.46</v>
       </c>
       <c r="K17" t="n">
-        <v>76.70999999999999</v>
+        <v>-14.64</v>
       </c>
       <c r="L17" t="n">
-        <v>77.42</v>
+        <v>103.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:49:19</t>
+          <t>04:47:55</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.75</v>
+        <v>3.34</v>
       </c>
       <c r="F18" t="n">
-        <v>10.03</v>
+        <v>10.5</v>
       </c>
       <c r="G18" t="n">
         <v>278.1</v>
       </c>
       <c r="H18" t="n">
-        <v>37.5</v>
+        <v>43.1</v>
       </c>
       <c r="I18" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.38</v>
+        <v>-38.66</v>
       </c>
       <c r="K18" t="n">
-        <v>74.40000000000001</v>
+        <v>35.26</v>
       </c>
       <c r="L18" t="n">
-        <v>74.41</v>
+        <v>52.32</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:50:36</t>
+          <t>04:50:03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>4.12</v>
+        <v>3.48</v>
       </c>
       <c r="F19" t="n">
-        <v>12.54</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>266.3</v>
+        <v>290.7</v>
       </c>
       <c r="H19" t="n">
-        <v>35.3</v>
+        <v>17</v>
       </c>
       <c r="I19" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J19" t="n">
-        <v>-60.94</v>
+        <v>-126.54</v>
       </c>
       <c r="K19" t="n">
-        <v>-37.97</v>
+        <v>4.56</v>
       </c>
       <c r="L19" t="n">
-        <v>71.8</v>
+        <v>126.63</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:54:27</t>
+          <t>04:53:30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.73</v>
+        <v>4.45</v>
       </c>
       <c r="F20" t="n">
-        <v>6.67</v>
+        <v>7.01</v>
       </c>
       <c r="G20" t="n">
-        <v>280.8</v>
+        <v>282.8</v>
       </c>
       <c r="H20" t="n">
-        <v>35.1</v>
+        <v>78</v>
       </c>
       <c r="I20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>-29.82</v>
+        <v>-156.53</v>
       </c>
       <c r="K20" t="n">
-        <v>-89</v>
+        <v>80.86</v>
       </c>
       <c r="L20" t="n">
-        <v>93.87</v>
+        <v>176.19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:55:16</t>
+          <t>04:55:13</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.06</v>
+        <v>3.84</v>
       </c>
       <c r="F21" t="n">
-        <v>6.23</v>
+        <v>6.92</v>
       </c>
       <c r="G21" t="n">
-        <v>269.3</v>
+        <v>274.3</v>
       </c>
       <c r="H21" t="n">
-        <v>33.2</v>
+        <v>67.3</v>
       </c>
       <c r="I21" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-31.07</v>
+        <v>1.19</v>
       </c>
       <c r="K21" t="n">
-        <v>-88.09</v>
+        <v>-163.53</v>
       </c>
       <c r="L21" t="n">
-        <v>93.41</v>
+        <v>163.53</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:57:30</t>
+          <t>04:57:11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>4.71</v>
+        <v>4.34</v>
       </c>
       <c r="F22" t="n">
-        <v>8.710000000000001</v>
+        <v>12.54</v>
       </c>
       <c r="G22" t="n">
-        <v>282.2</v>
+        <v>280.2</v>
       </c>
       <c r="H22" t="n">
-        <v>40.7</v>
+        <v>60.9</v>
       </c>
       <c r="I22" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>-22.63</v>
+        <v>-62.38</v>
       </c>
       <c r="K22" t="n">
-        <v>99.98</v>
+        <v>137.81</v>
       </c>
       <c r="L22" t="n">
-        <v>102.51</v>
+        <v>151.28</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:02:35</t>
+          <t>05:00:48</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.87</v>
+        <v>3.62</v>
       </c>
       <c r="F23" t="n">
-        <v>5.99</v>
+        <v>5.61</v>
       </c>
       <c r="G23" t="n">
-        <v>288.1</v>
+        <v>274.2</v>
       </c>
       <c r="H23" t="n">
-        <v>46</v>
+        <v>62.3</v>
       </c>
       <c r="I23" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J23" t="n">
-        <v>80.67</v>
+        <v>-166.88</v>
       </c>
       <c r="K23" t="n">
-        <v>-169.51</v>
+        <v>152.16</v>
       </c>
       <c r="L23" t="n">
-        <v>187.72</v>
+        <v>225.84</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:04:51</t>
+          <t>05:02:06</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>4.12</v>
+        <v>3.46</v>
       </c>
       <c r="F24" t="n">
-        <v>8.960000000000001</v>
+        <v>5.3</v>
       </c>
       <c r="G24" t="n">
-        <v>282.4</v>
+        <v>281.2</v>
       </c>
       <c r="H24" t="n">
-        <v>50.6</v>
+        <v>53.2</v>
       </c>
       <c r="I24" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.2</v>
+        <v>-112.44</v>
       </c>
       <c r="K24" t="n">
-        <v>-148.55</v>
+        <v>-101.89</v>
       </c>
       <c r="L24" t="n">
-        <v>148.57</v>
+        <v>151.74</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:06:40</t>
+          <t>05:04:24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>4.26</v>
+        <v>3.68</v>
       </c>
       <c r="F25" t="n">
-        <v>9.4</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>274.2</v>
+        <v>281.5</v>
       </c>
       <c r="H25" t="n">
-        <v>43.9</v>
+        <v>69.8</v>
       </c>
       <c r="I25" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J25" t="n">
-        <v>37.98</v>
+        <v>2.39</v>
       </c>
       <c r="K25" t="n">
-        <v>-107.82</v>
+        <v>-221.77</v>
       </c>
       <c r="L25" t="n">
-        <v>114.32</v>
+        <v>221.79</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:10:58</t>
+          <t>05:08:41</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.75</v>
+        <v>4.02</v>
       </c>
       <c r="F26" t="n">
-        <v>7.47</v>
+        <v>9.32</v>
       </c>
       <c r="G26" t="n">
-        <v>282.7</v>
+        <v>289.9</v>
       </c>
       <c r="H26" t="n">
-        <v>31.2</v>
+        <v>63.1</v>
       </c>
       <c r="I26" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J26" t="n">
-        <v>-194.51</v>
+        <v>-231.31</v>
       </c>
       <c r="K26" t="n">
-        <v>-236.75</v>
+        <v>139.61</v>
       </c>
       <c r="L26" t="n">
-        <v>306.4</v>
+        <v>270.17</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:12:43</t>
+          <t>05:10:15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="F27" t="n">
-        <v>7.68</v>
+        <v>11.26</v>
       </c>
       <c r="G27" t="n">
-        <v>275.6</v>
+        <v>276.2</v>
       </c>
       <c r="H27" t="n">
-        <v>34.8</v>
+        <v>47.8</v>
       </c>
       <c r="I27" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J27" t="n">
-        <v>-98.91</v>
+        <v>-63.44</v>
       </c>
       <c r="K27" t="n">
-        <v>189.33</v>
+        <v>-290.85</v>
       </c>
       <c r="L27" t="n">
-        <v>213.62</v>
+        <v>297.69</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:15:06</t>
+          <t>05:12:03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>4.22</v>
+        <v>4.36</v>
       </c>
       <c r="F28" t="n">
-        <v>7.42</v>
+        <v>12.54</v>
       </c>
       <c r="G28" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H28" t="n">
-        <v>37.1</v>
+        <v>53</v>
       </c>
       <c r="I28" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-225.62</v>
+        <v>-277.87</v>
       </c>
       <c r="K28" t="n">
-        <v>21.68</v>
+        <v>-20.78</v>
       </c>
       <c r="L28" t="n">
-        <v>226.66</v>
+        <v>278.65</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:24:30</t>
+          <t>05:21:58</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>4.77</v>
+        <v>4.03</v>
       </c>
       <c r="F29" t="n">
-        <v>11.69</v>
+        <v>10.01</v>
       </c>
       <c r="G29" t="n">
-        <v>287.8</v>
+        <v>293.4</v>
       </c>
       <c r="H29" t="n">
-        <v>45.1</v>
+        <v>90.7</v>
       </c>
       <c r="I29" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>80.84</v>
+        <v>58.4</v>
       </c>
       <c r="K29" t="n">
-        <v>-25.38</v>
+        <v>-48.46</v>
       </c>
       <c r="L29" t="n">
-        <v>84.73</v>
+        <v>75.89</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:25:50</t>
+          <t>05:23:22</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.82</v>
+        <v>3.67</v>
       </c>
       <c r="F30" t="n">
-        <v>10.35</v>
+        <v>8.58</v>
       </c>
       <c r="G30" t="n">
-        <v>284.4</v>
+        <v>278.9</v>
       </c>
       <c r="H30" t="n">
-        <v>31.2</v>
+        <v>56.6</v>
       </c>
       <c r="I30" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>52.7</v>
+        <v>-58.07</v>
       </c>
       <c r="K30" t="n">
-        <v>26.05</v>
+        <v>-58.81</v>
       </c>
       <c r="L30" t="n">
-        <v>58.79</v>
+        <v>82.65000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:26:34</t>
+          <t>05:23:59</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.32</v>
+        <v>3.61</v>
       </c>
       <c r="F31" t="n">
-        <v>8.470000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G31" t="n">
-        <v>292.8</v>
+        <v>274.2</v>
       </c>
       <c r="H31" t="n">
-        <v>42.4</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-1.03</v>
+        <v>30.81</v>
       </c>
       <c r="K31" t="n">
-        <v>72.95</v>
+        <v>-50.9</v>
       </c>
       <c r="L31" t="n">
-        <v>72.95999999999999</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:30:56</t>
+          <t>05:28:23</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>4.73</v>
+        <v>3.44</v>
       </c>
       <c r="F32" t="n">
-        <v>11.96</v>
+        <v>6.27</v>
       </c>
       <c r="G32" t="n">
-        <v>282.8</v>
+        <v>284.9</v>
       </c>
       <c r="H32" t="n">
-        <v>41.8</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I32" t="n">
         <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>114.47</v>
+        <v>-38.19</v>
       </c>
       <c r="K32" t="n">
-        <v>-40.37</v>
+        <v>-75.56999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>121.38</v>
+        <v>84.67</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:33:06</t>
+          <t>05:30:51</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.35</v>
+        <v>4.36</v>
       </c>
       <c r="F33" t="n">
-        <v>8.43</v>
+        <v>12.54</v>
       </c>
       <c r="G33" t="n">
-        <v>285.4</v>
+        <v>295.2</v>
       </c>
       <c r="H33" t="n">
-        <v>37.9</v>
+        <v>43.5</v>
       </c>
       <c r="I33" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>-64.77</v>
+        <v>-60.07</v>
       </c>
       <c r="K33" t="n">
-        <v>86.20999999999999</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>107.83</v>
+        <v>96.73</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:33:43</t>
+          <t>05:32:57</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.33</v>
+        <v>3.73</v>
       </c>
       <c r="F34" t="n">
-        <v>11.04</v>
+        <v>10.66</v>
       </c>
       <c r="G34" t="n">
-        <v>286.4</v>
+        <v>289</v>
       </c>
       <c r="H34" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I34" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J34" t="n">
-        <v>4.58</v>
+        <v>88.48</v>
       </c>
       <c r="K34" t="n">
-        <v>-25.32</v>
+        <v>78.64</v>
       </c>
       <c r="L34" t="n">
-        <v>25.74</v>
+        <v>118.37</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:38:38</t>
+          <t>05:36:59</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.46</v>
+        <v>4.22</v>
       </c>
       <c r="F35" t="n">
-        <v>7.87</v>
+        <v>11.97</v>
       </c>
       <c r="G35" t="n">
-        <v>291</v>
+        <v>283.8</v>
       </c>
       <c r="H35" t="n">
-        <v>41.6</v>
+        <v>50.1</v>
       </c>
       <c r="I35" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>-58.53</v>
+        <v>125.8</v>
       </c>
       <c r="K35" t="n">
-        <v>-75.3</v>
+        <v>67.13</v>
       </c>
       <c r="L35" t="n">
-        <v>95.37</v>
+        <v>142.59</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:40:42</t>
+          <t>05:38:36</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.69</v>
+        <v>3.87</v>
       </c>
       <c r="F36" t="n">
-        <v>8.83</v>
+        <v>11.13</v>
       </c>
       <c r="G36" t="n">
-        <v>283.4</v>
+        <v>286.6</v>
       </c>
       <c r="H36" t="n">
-        <v>42.4</v>
+        <v>63</v>
       </c>
       <c r="I36" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>99.23</v>
+        <v>-170.02</v>
       </c>
       <c r="K36" t="n">
-        <v>92.18000000000001</v>
+        <v>1.72</v>
       </c>
       <c r="L36" t="n">
-        <v>135.44</v>
+        <v>170.03</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:42:55</t>
+          <t>05:41:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.67</v>
+        <v>4.65</v>
       </c>
       <c r="F37" t="n">
-        <v>9.6</v>
+        <v>12.54</v>
       </c>
       <c r="G37" t="n">
-        <v>280.6</v>
+        <v>261.7</v>
       </c>
       <c r="H37" t="n">
-        <v>41.5</v>
+        <v>32.4</v>
       </c>
       <c r="I37" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>-9.57</v>
+        <v>-193.57</v>
       </c>
       <c r="K37" t="n">
-        <v>-81.7</v>
+        <v>98.47</v>
       </c>
       <c r="L37" t="n">
-        <v>82.26000000000001</v>
+        <v>217.18</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:46:27</t>
+          <t>05:44:16</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.29</v>
+        <v>3.7</v>
       </c>
       <c r="F38" t="n">
-        <v>7.59</v>
+        <v>7.66</v>
       </c>
       <c r="G38" t="n">
-        <v>284.7</v>
+        <v>270.4</v>
       </c>
       <c r="H38" t="n">
-        <v>43.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>126.05</v>
+        <v>-193.07</v>
       </c>
       <c r="K38" t="n">
-        <v>53.22</v>
+        <v>-103.29</v>
       </c>
       <c r="L38" t="n">
-        <v>136.82</v>
+        <v>218.96</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:48:18</t>
+          <t>05:45:53</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>4.53</v>
+        <v>4</v>
       </c>
       <c r="F39" t="n">
-        <v>10.16</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>286.6</v>
+        <v>285.1</v>
       </c>
       <c r="H39" t="n">
-        <v>35.2</v>
+        <v>51</v>
       </c>
       <c r="I39" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-126.96</v>
+        <v>29.77</v>
       </c>
       <c r="K39" t="n">
-        <v>-59.91</v>
+        <v>230.21</v>
       </c>
       <c r="L39" t="n">
-        <v>140.38</v>
+        <v>232.13</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:49:21</t>
+          <t>05:46:34</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>4.03</v>
+        <v>3.71</v>
       </c>
       <c r="F40" t="n">
-        <v>6.56</v>
+        <v>7.99</v>
       </c>
       <c r="G40" t="n">
-        <v>263.9</v>
+        <v>285.6</v>
       </c>
       <c r="H40" t="n">
-        <v>41.9</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J40" t="n">
-        <v>159.67</v>
+        <v>135.37</v>
       </c>
       <c r="K40" t="n">
-        <v>-28.44</v>
+        <v>13.33</v>
       </c>
       <c r="L40" t="n">
-        <v>162.18</v>
+        <v>136.03</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:55:04</t>
+          <t>05:52:35</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>4.48</v>
+        <v>4.02</v>
       </c>
       <c r="F41" t="n">
-        <v>12.54</v>
+        <v>11.47</v>
       </c>
       <c r="G41" t="n">
-        <v>280.2</v>
+        <v>282.4</v>
       </c>
       <c r="H41" t="n">
-        <v>30.6</v>
+        <v>53.7</v>
       </c>
       <c r="I41" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>62.69</v>
+        <v>-279.03</v>
       </c>
       <c r="K41" t="n">
-        <v>-197.22</v>
+        <v>3.98</v>
       </c>
       <c r="L41" t="n">
-        <v>206.95</v>
+        <v>279.06</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05:57:30</t>
+          <t>05:55:00</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.15</v>
+        <v>3.76</v>
       </c>
       <c r="F42" t="n">
-        <v>10.24</v>
+        <v>11.08</v>
       </c>
       <c r="G42" t="n">
-        <v>276.7</v>
+        <v>281.9</v>
       </c>
       <c r="H42" t="n">
-        <v>50.6</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>110.18</v>
+        <v>-308.07</v>
       </c>
       <c r="K42" t="n">
-        <v>-197.35</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>226.02</v>
+        <v>308.23</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05:58:54</t>
+          <t>05:55:56</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.9</v>
+        <v>4.47</v>
       </c>
       <c r="F43" t="n">
-        <v>7.93</v>
+        <v>12.54</v>
       </c>
       <c r="G43" t="n">
-        <v>283.5</v>
+        <v>281.2</v>
       </c>
       <c r="H43" t="n">
-        <v>40.7</v>
+        <v>39.8</v>
       </c>
       <c r="I43" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>109.31</v>
+        <v>-211.98</v>
       </c>
       <c r="K43" t="n">
-        <v>155.82</v>
+        <v>-235.99</v>
       </c>
       <c r="L43" t="n">
-        <v>190.34</v>
+        <v>317.21</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:08:03</t>
+          <t>06:05:16</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>4.06</v>
+        <v>4.45</v>
       </c>
       <c r="F44" t="n">
-        <v>9.58</v>
+        <v>10.47</v>
       </c>
       <c r="G44" t="n">
-        <v>278.9</v>
+        <v>277.4</v>
       </c>
       <c r="H44" t="n">
-        <v>37.7</v>
+        <v>47.3</v>
       </c>
       <c r="I44" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>79.52</v>
+        <v>-90.89</v>
       </c>
       <c r="K44" t="n">
-        <v>34.36</v>
+        <v>-19.46</v>
       </c>
       <c r="L44" t="n">
-        <v>86.63</v>
+        <v>92.95</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:10:25</t>
+          <t>06:06:37</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.75</v>
+        <v>4.03</v>
       </c>
       <c r="F45" t="n">
-        <v>8.77</v>
+        <v>9.34</v>
       </c>
       <c r="G45" t="n">
-        <v>265</v>
+        <v>270.3</v>
       </c>
       <c r="H45" t="n">
-        <v>43.7</v>
+        <v>42.9</v>
       </c>
       <c r="I45" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>-55.74</v>
+        <v>-8.6</v>
       </c>
       <c r="K45" t="n">
-        <v>18.02</v>
+        <v>-69.81999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>58.58</v>
+        <v>70.34999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:11:38</t>
+          <t>06:08:47</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>4.22</v>
+        <v>3.88</v>
       </c>
       <c r="F46" t="n">
-        <v>10.44</v>
+        <v>10.14</v>
       </c>
       <c r="G46" t="n">
-        <v>283.2</v>
+        <v>281.2</v>
       </c>
       <c r="H46" t="n">
         <v>44.4</v>
       </c>
       <c r="I46" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>4.44</v>
+        <v>-75.95999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>86.40000000000001</v>
+        <v>24.25</v>
       </c>
       <c r="L46" t="n">
-        <v>86.51000000000001</v>
+        <v>79.73999999999999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:15:10</t>
+          <t>06:14:12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.16</v>
+        <v>4.11</v>
       </c>
       <c r="F47" t="n">
-        <v>7.55</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G47" t="n">
-        <v>279.9</v>
+        <v>265</v>
       </c>
       <c r="H47" t="n">
-        <v>38.2</v>
+        <v>47.9</v>
       </c>
       <c r="I47" t="n">
         <v>21</v>
       </c>
       <c r="J47" t="n">
-        <v>30.34</v>
+        <v>14.28</v>
       </c>
       <c r="K47" t="n">
-        <v>-67.16</v>
+        <v>-110.54</v>
       </c>
       <c r="L47" t="n">
-        <v>73.7</v>
+        <v>111.46</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:16:17</t>
+          <t>06:16:35</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.79</v>
+        <v>4.43</v>
       </c>
       <c r="F48" t="n">
-        <v>11.69</v>
+        <v>12.54</v>
       </c>
       <c r="G48" t="n">
-        <v>282.7</v>
+        <v>288.1</v>
       </c>
       <c r="H48" t="n">
-        <v>35.7</v>
+        <v>43.8</v>
       </c>
       <c r="I48" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>-90.04000000000001</v>
+        <v>-103.1</v>
       </c>
       <c r="K48" t="n">
-        <v>-32.64</v>
+        <v>-53.82</v>
       </c>
       <c r="L48" t="n">
-        <v>95.78</v>
+        <v>116.31</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:17:35</t>
+          <t>06:18:45</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4.51</v>
+        <v>3.21</v>
       </c>
       <c r="F49" t="n">
-        <v>10.14</v>
+        <v>7.37</v>
       </c>
       <c r="G49" t="n">
-        <v>274.5</v>
+        <v>290.4</v>
       </c>
       <c r="H49" t="n">
-        <v>40.2</v>
+        <v>54.6</v>
       </c>
       <c r="I49" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>-59.36</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>19.24</v>
+        <v>-66.16</v>
       </c>
       <c r="L49" t="n">
-        <v>62.4</v>
+        <v>93.48</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:21:44</t>
+          <t>06:22:36</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.99</v>
+        <v>4.34</v>
       </c>
       <c r="F50" t="n">
-        <v>12.02</v>
+        <v>9.59</v>
       </c>
       <c r="G50" t="n">
-        <v>274.7</v>
+        <v>266.4</v>
       </c>
       <c r="H50" t="n">
-        <v>46.8</v>
+        <v>38.9</v>
       </c>
       <c r="I50" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>34.06</v>
+        <v>-56.9</v>
       </c>
       <c r="K50" t="n">
-        <v>111.1</v>
+        <v>-121.16</v>
       </c>
       <c r="L50" t="n">
-        <v>116.21</v>
+        <v>133.86</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:23:09</t>
+          <t>06:24:12</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.1</v>
+        <v>3.96</v>
       </c>
       <c r="F51" t="n">
-        <v>11.85</v>
+        <v>9.56</v>
       </c>
       <c r="G51" t="n">
-        <v>282.4</v>
+        <v>268.6</v>
       </c>
       <c r="H51" t="n">
-        <v>46.4</v>
+        <v>46.3</v>
       </c>
       <c r="I51" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>-182.17</v>
+        <v>-138.85</v>
       </c>
       <c r="K51" t="n">
-        <v>-104.82</v>
+        <v>-75.65000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>210.18</v>
+        <v>158.12</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:25:28</t>
+          <t>06:24:58</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4</v>
+        <v>3.42</v>
       </c>
       <c r="F52" t="n">
-        <v>11.42</v>
+        <v>10.39</v>
       </c>
       <c r="G52" t="n">
-        <v>276.8</v>
+        <v>295.6</v>
       </c>
       <c r="H52" t="n">
-        <v>34.9</v>
+        <v>57.7</v>
       </c>
       <c r="I52" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J52" t="n">
-        <v>112.06</v>
+        <v>118.08</v>
       </c>
       <c r="K52" t="n">
-        <v>-67.56999999999999</v>
+        <v>-28.78</v>
       </c>
       <c r="L52" t="n">
-        <v>130.85</v>
+        <v>121.54</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:29:25</t>
+          <t>06:29:20</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.31</v>
+        <v>3.94</v>
       </c>
       <c r="F53" t="n">
-        <v>12.37</v>
+        <v>10.65</v>
       </c>
       <c r="G53" t="n">
-        <v>267.2</v>
+        <v>288.3</v>
       </c>
       <c r="H53" t="n">
-        <v>40</v>
+        <v>37.2</v>
       </c>
       <c r="I53" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>-108.75</v>
+        <v>-176.1</v>
       </c>
       <c r="K53" t="n">
-        <v>69.08</v>
+        <v>-170.74</v>
       </c>
       <c r="L53" t="n">
-        <v>128.84</v>
+        <v>245.28</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:31:24</t>
+          <t>06:30:24</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.9</v>
+        <v>4.38</v>
       </c>
       <c r="F54" t="n">
-        <v>9.960000000000001</v>
+        <v>10.03</v>
       </c>
       <c r="G54" t="n">
-        <v>277.1</v>
+        <v>283.2</v>
       </c>
       <c r="H54" t="n">
-        <v>36.4</v>
+        <v>32</v>
       </c>
       <c r="I54" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>33.9</v>
+        <v>183.71</v>
       </c>
       <c r="K54" t="n">
-        <v>139.15</v>
+        <v>118.55</v>
       </c>
       <c r="L54" t="n">
-        <v>143.22</v>
+        <v>218.64</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:32:50</t>
+          <t>06:32:20</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.8</v>
+        <v>4.63</v>
       </c>
       <c r="F55" t="n">
-        <v>8.640000000000001</v>
+        <v>12.1</v>
       </c>
       <c r="G55" t="n">
-        <v>276.9</v>
+        <v>288.8</v>
       </c>
       <c r="H55" t="n">
-        <v>39.4</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>-179.41</v>
+        <v>-194.38</v>
       </c>
       <c r="K55" t="n">
-        <v>-19.98</v>
+        <v>-15.05</v>
       </c>
       <c r="L55" t="n">
-        <v>180.52</v>
+        <v>194.96</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:36:33</t>
+          <t>06:37:19</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.56</v>
+        <v>4.08</v>
       </c>
       <c r="F56" t="n">
-        <v>12.19</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="G56" t="n">
-        <v>279.3</v>
+        <v>282.5</v>
       </c>
       <c r="H56" t="n">
-        <v>45.6</v>
+        <v>69</v>
       </c>
       <c r="I56" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J56" t="n">
-        <v>146.84</v>
+        <v>206.62</v>
       </c>
       <c r="K56" t="n">
-        <v>-255.02</v>
+        <v>128.18</v>
       </c>
       <c r="L56" t="n">
-        <v>294.27</v>
+        <v>243.15</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:37:30</t>
+          <t>06:39:57</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4.17</v>
+        <v>4.24</v>
       </c>
       <c r="F57" t="n">
-        <v>7.77</v>
+        <v>10.45</v>
       </c>
       <c r="G57" t="n">
-        <v>270.7</v>
+        <v>272.2</v>
       </c>
       <c r="H57" t="n">
-        <v>38.6</v>
+        <v>41.9</v>
       </c>
       <c r="I57" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>110.35</v>
+        <v>-344.54</v>
       </c>
       <c r="K57" t="n">
-        <v>286.92</v>
+        <v>16.86</v>
       </c>
       <c r="L57" t="n">
-        <v>307.41</v>
+        <v>344.95</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:39:25</t>
+          <t>06:41:12</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.22</v>
+        <v>4.55</v>
       </c>
       <c r="F58" t="n">
-        <v>11.42</v>
+        <v>12.54</v>
       </c>
       <c r="G58" t="n">
-        <v>265.4</v>
+        <v>283.8</v>
       </c>
       <c r="H58" t="n">
-        <v>38.6</v>
+        <v>75.8</v>
       </c>
       <c r="I58" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>-218.65</v>
+        <v>309.34</v>
       </c>
       <c r="K58" t="n">
-        <v>203.98</v>
+        <v>-142.01</v>
       </c>
       <c r="L58" t="n">
-        <v>299.03</v>
+        <v>340.38</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:50:15</t>
+          <t>06:51:52</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.41</v>
+        <v>3.86</v>
       </c>
       <c r="F59" t="n">
-        <v>11.83</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="G59" t="n">
-        <v>276.7</v>
+        <v>274.7</v>
       </c>
       <c r="H59" t="n">
-        <v>46.2</v>
+        <v>62.7</v>
       </c>
       <c r="I59" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>6.12</v>
+        <v>-25.17</v>
       </c>
       <c r="K59" t="n">
-        <v>-22.16</v>
+        <v>64.61</v>
       </c>
       <c r="L59" t="n">
-        <v>22.99</v>
+        <v>69.34</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:51:56</t>
+          <t>06:54:33</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.65</v>
+        <v>5.04</v>
       </c>
       <c r="F60" t="n">
-        <v>9.359999999999999</v>
+        <v>10.82</v>
       </c>
       <c r="G60" t="n">
-        <v>279.4</v>
+        <v>291.4</v>
       </c>
       <c r="H60" t="n">
-        <v>41.9</v>
+        <v>81.3</v>
       </c>
       <c r="I60" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>10.2</v>
+        <v>-130.18</v>
       </c>
       <c r="K60" t="n">
-        <v>64.92</v>
+        <v>-14.46</v>
       </c>
       <c r="L60" t="n">
-        <v>65.70999999999999</v>
+        <v>130.98</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06:54:02</t>
+          <t>06:55:37</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.58</v>
+        <v>3.95</v>
       </c>
       <c r="F61" t="n">
-        <v>11.72</v>
+        <v>12.54</v>
       </c>
       <c r="G61" t="n">
-        <v>279.9</v>
+        <v>283</v>
       </c>
       <c r="H61" t="n">
-        <v>33.4</v>
+        <v>28.4</v>
       </c>
       <c r="I61" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J61" t="n">
-        <v>-89.53</v>
+        <v>-48.25</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.7</v>
+        <v>-0.25</v>
       </c>
       <c r="L61" t="n">
-        <v>89.53</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06:58:56</t>
+          <t>07:00:08</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.23</v>
+        <v>4.19</v>
       </c>
       <c r="F62" t="n">
-        <v>9.449999999999999</v>
+        <v>12.37</v>
       </c>
       <c r="G62" t="n">
-        <v>269.8</v>
+        <v>281.5</v>
       </c>
       <c r="H62" t="n">
-        <v>34.4</v>
+        <v>57.4</v>
       </c>
       <c r="I62" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>-76.34</v>
+        <v>10.97</v>
       </c>
       <c r="K62" t="n">
-        <v>-35.06</v>
+        <v>-124.3</v>
       </c>
       <c r="L62" t="n">
-        <v>84</v>
+        <v>124.78</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06:59:42</t>
+          <t>07:02:38</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.99</v>
+        <v>4.75</v>
       </c>
       <c r="F63" t="n">
-        <v>12.54</v>
+        <v>11.07</v>
       </c>
       <c r="G63" t="n">
-        <v>270.1</v>
+        <v>277.6</v>
       </c>
       <c r="H63" t="n">
-        <v>44.2</v>
+        <v>32.9</v>
       </c>
       <c r="I63" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>10.27</v>
+        <v>-106.38</v>
       </c>
       <c r="K63" t="n">
-        <v>111.54</v>
+        <v>20.18</v>
       </c>
       <c r="L63" t="n">
-        <v>112.01</v>
+        <v>108.28</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:00:57</t>
+          <t>07:03:46</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.99</v>
+        <v>4.46</v>
       </c>
       <c r="F64" t="n">
-        <v>10.98</v>
+        <v>11.35</v>
       </c>
       <c r="G64" t="n">
-        <v>286.2</v>
+        <v>277.3</v>
       </c>
       <c r="H64" t="n">
-        <v>42.6</v>
+        <v>23.7</v>
       </c>
       <c r="I64" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J64" t="n">
-        <v>-63.4</v>
+        <v>136.66</v>
       </c>
       <c r="K64" t="n">
-        <v>24.57</v>
+        <v>53.27</v>
       </c>
       <c r="L64" t="n">
-        <v>67.98999999999999</v>
+        <v>146.67</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:05:47</t>
+          <t>07:09:43</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.71</v>
+        <v>4.81</v>
       </c>
       <c r="F65" t="n">
-        <v>12.19</v>
+        <v>12.54</v>
       </c>
       <c r="G65" t="n">
-        <v>282</v>
+        <v>263.9</v>
       </c>
       <c r="H65" t="n">
-        <v>47.6</v>
+        <v>34</v>
       </c>
       <c r="I65" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>-97.36</v>
+        <v>-94.87</v>
       </c>
       <c r="K65" t="n">
-        <v>55.87</v>
+        <v>-185.02</v>
       </c>
       <c r="L65" t="n">
-        <v>112.25</v>
+        <v>207.93</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:07:00</t>
+          <t>07:11:48</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.75</v>
+        <v>4.14</v>
       </c>
       <c r="F66" t="n">
-        <v>11.67</v>
+        <v>12.54</v>
       </c>
       <c r="G66" t="n">
-        <v>282.5</v>
+        <v>273.1</v>
       </c>
       <c r="H66" t="n">
-        <v>40.4</v>
+        <v>65.2</v>
       </c>
       <c r="I66" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J66" t="n">
-        <v>-114.83</v>
+        <v>-75.92</v>
       </c>
       <c r="K66" t="n">
-        <v>113.19</v>
+        <v>-130.22</v>
       </c>
       <c r="L66" t="n">
-        <v>161.24</v>
+        <v>150.73</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:09:06</t>
+          <t>07:12:25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.89</v>
+        <v>4.57</v>
       </c>
       <c r="F67" t="n">
         <v>12.54</v>
       </c>
       <c r="G67" t="n">
-        <v>295.6</v>
+        <v>264.4</v>
       </c>
       <c r="H67" t="n">
-        <v>39.6</v>
+        <v>58.5</v>
       </c>
       <c r="I67" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>138.48</v>
+        <v>95.61</v>
       </c>
       <c r="K67" t="n">
-        <v>73.06</v>
+        <v>149.05</v>
       </c>
       <c r="L67" t="n">
-        <v>156.57</v>
+        <v>177.08</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:15:26</t>
+          <t>07:17:26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.3</v>
+        <v>3.83</v>
       </c>
       <c r="F68" t="n">
-        <v>11.66</v>
+        <v>12.48</v>
       </c>
       <c r="G68" t="n">
-        <v>291.8</v>
+        <v>266</v>
       </c>
       <c r="H68" t="n">
-        <v>39.7</v>
+        <v>63</v>
       </c>
       <c r="I68" t="n">
         <v>23</v>
       </c>
       <c r="J68" t="n">
-        <v>71.15000000000001</v>
+        <v>-212.6</v>
       </c>
       <c r="K68" t="n">
-        <v>-320.34</v>
+        <v>254.73</v>
       </c>
       <c r="L68" t="n">
-        <v>328.15</v>
+        <v>331.79</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:17:35</t>
+          <t>07:18:24</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>5.04</v>
+        <v>4.87</v>
       </c>
       <c r="F69" t="n">
         <v>12.54</v>
       </c>
       <c r="G69" t="n">
-        <v>278.7</v>
+        <v>260.9</v>
       </c>
       <c r="H69" t="n">
-        <v>42.8</v>
+        <v>55</v>
       </c>
       <c r="I69" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>105.91</v>
+        <v>-40.9</v>
       </c>
       <c r="K69" t="n">
-        <v>166.51</v>
+        <v>288.73</v>
       </c>
       <c r="L69" t="n">
-        <v>197.34</v>
+        <v>291.61</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:19:42</t>
+          <t>07:19:43</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.49</v>
+        <v>4.29</v>
       </c>
       <c r="F70" t="n">
-        <v>12.54</v>
+        <v>12.34</v>
       </c>
       <c r="G70" t="n">
-        <v>288.7</v>
+        <v>291.7</v>
       </c>
       <c r="H70" t="n">
-        <v>39.6</v>
+        <v>40.7</v>
       </c>
       <c r="I70" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>187.24</v>
+        <v>-116.16</v>
       </c>
       <c r="K70" t="n">
-        <v>149.25</v>
+        <v>290.36</v>
       </c>
       <c r="L70" t="n">
-        <v>239.44</v>
+        <v>312.73</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:22:45</t>
+          <t>07:23:24</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.11</v>
+        <v>4.54</v>
       </c>
       <c r="F71" t="n">
-        <v>7.5</v>
+        <v>9.81</v>
       </c>
       <c r="G71" t="n">
-        <v>295.9</v>
+        <v>279.4</v>
       </c>
       <c r="H71" t="n">
-        <v>37.3</v>
+        <v>5.2</v>
       </c>
       <c r="I71" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>-263.32</v>
+        <v>-210.3</v>
       </c>
       <c r="K71" t="n">
-        <v>-20.95</v>
+        <v>180.47</v>
       </c>
       <c r="L71" t="n">
-        <v>264.15</v>
+        <v>277.12</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:24:08</t>
+          <t>07:25:14</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.08</v>
+        <v>3.67</v>
       </c>
       <c r="F72" t="n">
-        <v>10.17</v>
+        <v>9.77</v>
       </c>
       <c r="G72" t="n">
-        <v>283</v>
+        <v>281.9</v>
       </c>
       <c r="H72" t="n">
-        <v>37.1</v>
+        <v>23.9</v>
       </c>
       <c r="I72" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>-220.65</v>
+        <v>-250.2</v>
       </c>
       <c r="K72" t="n">
-        <v>-249.66</v>
+        <v>254.72</v>
       </c>
       <c r="L72" t="n">
-        <v>333.19</v>
+        <v>357.05</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:26:05</t>
+          <t>07:26:38</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.45</v>
+        <v>4.29</v>
       </c>
       <c r="F73" t="n">
-        <v>12.54</v>
+        <v>10.79</v>
       </c>
       <c r="G73" t="n">
-        <v>288.8</v>
+        <v>294.6</v>
       </c>
       <c r="H73" t="n">
-        <v>46.4</v>
+        <v>34.5</v>
       </c>
       <c r="I73" t="n">
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>446.33</v>
+        <v>-226.12</v>
       </c>
       <c r="K73" t="n">
-        <v>-267.14</v>
+        <v>-48.01</v>
       </c>
       <c r="L73" t="n">
-        <v>520.16</v>
+        <v>231.16</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:37:17</t>
+          <t>07:39:20</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.61</v>
+        <v>5.14</v>
       </c>
       <c r="F74" t="n">
-        <v>10.29</v>
+        <v>12.54</v>
       </c>
       <c r="G74" t="n">
-        <v>286.4</v>
+        <v>281.1</v>
       </c>
       <c r="H74" t="n">
-        <v>39.8</v>
+        <v>34.2</v>
       </c>
       <c r="I74" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J74" t="n">
-        <v>-45.04</v>
+        <v>-15.2</v>
       </c>
       <c r="K74" t="n">
-        <v>-32.31</v>
+        <v>-111.62</v>
       </c>
       <c r="L74" t="n">
-        <v>55.43</v>
+        <v>112.65</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:38:32</t>
+          <t>07:41:22</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.31</v>
+        <v>4.41</v>
       </c>
       <c r="F75" t="n">
-        <v>10.61</v>
+        <v>10.86</v>
       </c>
       <c r="G75" t="n">
-        <v>279.2</v>
+        <v>275.2</v>
       </c>
       <c r="H75" t="n">
-        <v>42.4</v>
+        <v>16.4</v>
       </c>
       <c r="I75" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-44.99</v>
+        <v>-61.83</v>
       </c>
       <c r="K75" t="n">
-        <v>-52.07</v>
+        <v>-59.92</v>
       </c>
       <c r="L75" t="n">
-        <v>68.81999999999999</v>
+        <v>86.09999999999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:40:17</t>
+          <t>07:42:37</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4.49</v>
+        <v>4.53</v>
       </c>
       <c r="F76" t="n">
-        <v>10.51</v>
+        <v>12.39</v>
       </c>
       <c r="G76" t="n">
-        <v>296.2</v>
+        <v>281.3</v>
       </c>
       <c r="H76" t="n">
-        <v>45.5</v>
+        <v>46.2</v>
       </c>
       <c r="I76" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>50.46</v>
+        <v>13.68</v>
       </c>
       <c r="K76" t="n">
-        <v>-82.84</v>
+        <v>-106.16</v>
       </c>
       <c r="L76" t="n">
-        <v>97</v>
+        <v>107.04</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:45:33</t>
+          <t>07:47:11</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.77</v>
+        <v>3.81</v>
       </c>
       <c r="F77" t="n">
-        <v>12.54</v>
+        <v>10.69</v>
       </c>
       <c r="G77" t="n">
-        <v>274.3</v>
+        <v>263.9</v>
       </c>
       <c r="H77" t="n">
-        <v>39.8</v>
+        <v>42.3</v>
       </c>
       <c r="I77" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>86.83</v>
+        <v>78.38</v>
       </c>
       <c r="K77" t="n">
-        <v>-5.02</v>
+        <v>40.53</v>
       </c>
       <c r="L77" t="n">
-        <v>86.98</v>
+        <v>88.23999999999999</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:47:28</t>
+          <t>07:48:53</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>5.14</v>
+        <v>4.64</v>
       </c>
       <c r="F78" t="n">
         <v>12.54</v>
       </c>
       <c r="G78" t="n">
-        <v>278.5</v>
+        <v>279.1</v>
       </c>
       <c r="H78" t="n">
-        <v>33.6</v>
+        <v>47.3</v>
       </c>
       <c r="I78" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>90.19</v>
+        <v>-157.75</v>
       </c>
       <c r="K78" t="n">
-        <v>13.06</v>
+        <v>-41.2</v>
       </c>
       <c r="L78" t="n">
-        <v>91.13</v>
+        <v>163.04</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:48:55</t>
+          <t>07:50:27</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.68</v>
+        <v>4.29</v>
       </c>
       <c r="F79" t="n">
-        <v>8.18</v>
+        <v>11.09</v>
       </c>
       <c r="G79" t="n">
-        <v>278.4</v>
+        <v>279.9</v>
       </c>
       <c r="H79" t="n">
-        <v>43.3</v>
+        <v>46.5</v>
       </c>
       <c r="I79" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>35.59</v>
+        <v>-127.64</v>
       </c>
       <c r="K79" t="n">
-        <v>-63.52</v>
+        <v>-68.19</v>
       </c>
       <c r="L79" t="n">
-        <v>72.81</v>
+        <v>144.71</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:54:15</t>
+          <t>07:54:58</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>4.58</v>
+        <v>4.44</v>
       </c>
       <c r="F80" t="n">
-        <v>11.74</v>
+        <v>11.82</v>
       </c>
       <c r="G80" t="n">
-        <v>281.6</v>
+        <v>286.9</v>
       </c>
       <c r="H80" t="n">
-        <v>41.7</v>
+        <v>26.3</v>
       </c>
       <c r="I80" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>-146.14</v>
+        <v>14.05</v>
       </c>
       <c r="K80" t="n">
-        <v>60.91</v>
+        <v>162.42</v>
       </c>
       <c r="L80" t="n">
-        <v>158.32</v>
+        <v>163.02</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07:56:40</t>
+          <t>07:55:43</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.79</v>
+        <v>4.34</v>
       </c>
       <c r="F81" t="n">
         <v>12.54</v>
       </c>
       <c r="G81" t="n">
-        <v>279.9</v>
+        <v>284.9</v>
       </c>
       <c r="H81" t="n">
-        <v>35.7</v>
+        <v>55.6</v>
       </c>
       <c r="I81" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>-23.15</v>
+        <v>-200.09</v>
       </c>
       <c r="K81" t="n">
-        <v>-112.84</v>
+        <v>-99.14</v>
       </c>
       <c r="L81" t="n">
-        <v>115.19</v>
+        <v>223.31</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07:58:54</t>
+          <t>07:56:44</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.72</v>
+        <v>4.41</v>
       </c>
       <c r="F82" t="n">
-        <v>12.54</v>
+        <v>10.91</v>
       </c>
       <c r="G82" t="n">
-        <v>277.2</v>
+        <v>288.1</v>
       </c>
       <c r="H82" t="n">
-        <v>38.6</v>
+        <v>52.3</v>
       </c>
       <c r="I82" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-101.33</v>
+        <v>200.29</v>
       </c>
       <c r="K82" t="n">
-        <v>55.73</v>
+        <v>-43.2</v>
       </c>
       <c r="L82" t="n">
-        <v>115.64</v>
+        <v>204.9</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:02:41</t>
+          <t>08:02:38</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3526,31 +3526,31 @@
         <v>4.47</v>
       </c>
       <c r="F83" t="n">
-        <v>12.54</v>
+        <v>11.06</v>
       </c>
       <c r="G83" t="n">
-        <v>292.1</v>
+        <v>270.2</v>
       </c>
       <c r="H83" t="n">
-        <v>42.6</v>
+        <v>57.2</v>
       </c>
       <c r="I83" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>79.69</v>
+        <v>76.56</v>
       </c>
       <c r="K83" t="n">
-        <v>-57.97</v>
+        <v>-121.76</v>
       </c>
       <c r="L83" t="n">
-        <v>98.54000000000001</v>
+        <v>143.83</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:04:19</t>
+          <t>08:03:44</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.49</v>
+        <v>4.65</v>
       </c>
       <c r="F84" t="n">
-        <v>12.52</v>
+        <v>12.54</v>
       </c>
       <c r="G84" t="n">
-        <v>287.8</v>
+        <v>293.2</v>
       </c>
       <c r="H84" t="n">
-        <v>26.3</v>
+        <v>43.6</v>
       </c>
       <c r="I84" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>-100.67</v>
+        <v>-129.95</v>
       </c>
       <c r="K84" t="n">
-        <v>163.93</v>
+        <v>249.08</v>
       </c>
       <c r="L84" t="n">
-        <v>192.37</v>
+        <v>280.94</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:06:39</t>
+          <t>08:06:00</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="F85" t="n">
         <v>12.54</v>
       </c>
       <c r="G85" t="n">
-        <v>279.5</v>
+        <v>299</v>
       </c>
       <c r="H85" t="n">
-        <v>39.9</v>
+        <v>52.8</v>
       </c>
       <c r="I85" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>-11.84</v>
+        <v>-264.03</v>
       </c>
       <c r="K85" t="n">
-        <v>179.65</v>
+        <v>355.2</v>
       </c>
       <c r="L85" t="n">
-        <v>180.04</v>
+        <v>442.58</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:11:36</t>
+          <t>08:11:04</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.91</v>
+        <v>4.19</v>
       </c>
       <c r="F86" t="n">
-        <v>10.51</v>
+        <v>10.84</v>
       </c>
       <c r="G86" t="n">
-        <v>282.1</v>
+        <v>279.3</v>
       </c>
       <c r="H86" t="n">
-        <v>34.8</v>
+        <v>54.6</v>
       </c>
       <c r="I86" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>-165.91</v>
+        <v>-24.9</v>
       </c>
       <c r="K86" t="n">
-        <v>371.14</v>
+        <v>293.24</v>
       </c>
       <c r="L86" t="n">
-        <v>406.54</v>
+        <v>294.29</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:13:37</t>
+          <t>08:12:32</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.51</v>
+        <v>4.67</v>
       </c>
       <c r="F87" t="n">
         <v>12.54</v>
       </c>
       <c r="G87" t="n">
-        <v>273.3</v>
+        <v>287.2</v>
       </c>
       <c r="H87" t="n">
-        <v>50.5</v>
+        <v>42.1</v>
       </c>
       <c r="I87" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J87" t="n">
-        <v>-210.96</v>
+        <v>264.89</v>
       </c>
       <c r="K87" t="n">
-        <v>249.24</v>
+        <v>-423.42</v>
       </c>
       <c r="L87" t="n">
-        <v>326.54</v>
+        <v>499.45</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:14:26</t>
+          <t>08:15:06</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.76</v>
+        <v>4.21</v>
       </c>
       <c r="F88" t="n">
-        <v>11.41</v>
+        <v>11.56</v>
       </c>
       <c r="G88" t="n">
-        <v>283.7</v>
+        <v>288</v>
       </c>
       <c r="H88" t="n">
-        <v>45.6</v>
+        <v>43.7</v>
       </c>
       <c r="I88" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J88" t="n">
-        <v>-167.98</v>
+        <v>-349.01</v>
       </c>
       <c r="K88" t="n">
-        <v>226.94</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="L88" t="n">
-        <v>282.34</v>
+        <v>363.02</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-06.xlsx
+++ b/output/2024-07-06.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.59</v>
+        <v>3.57</v>
       </c>
       <c r="F14" t="n">
-        <v>11.38</v>
+        <v>7.74</v>
       </c>
       <c r="G14" t="n">
-        <v>280.6</v>
+        <v>275.2</v>
       </c>
       <c r="H14" t="n">
-        <v>62.3</v>
+        <v>42.1</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>12.23</v>
+        <v>-51.18</v>
       </c>
       <c r="K14" t="n">
-        <v>-65.75</v>
+        <v>2.47</v>
       </c>
       <c r="L14" t="n">
-        <v>66.88</v>
+        <v>51.24</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:40:08</t>
+          <t>04:40:12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.07</v>
+        <v>3.99</v>
       </c>
       <c r="F15" t="n">
-        <v>4.89</v>
+        <v>7.07</v>
       </c>
       <c r="G15" t="n">
-        <v>277.1</v>
+        <v>273.2</v>
       </c>
       <c r="H15" t="n">
-        <v>51.7</v>
+        <v>55.2</v>
       </c>
       <c r="I15" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>-55.64</v>
+        <v>-70.45999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>24.03</v>
+        <v>30.66</v>
       </c>
       <c r="L15" t="n">
-        <v>60.61</v>
+        <v>76.84</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:41:33</t>
+          <t>04:42:12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="F16" t="n">
-        <v>8.41</v>
+        <v>9.48</v>
       </c>
       <c r="G16" t="n">
-        <v>273.8</v>
+        <v>282.8</v>
       </c>
       <c r="H16" t="n">
-        <v>60.5</v>
+        <v>79.7</v>
       </c>
       <c r="I16" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J16" t="n">
-        <v>60.98</v>
+        <v>-70.25</v>
       </c>
       <c r="K16" t="n">
-        <v>34.21</v>
+        <v>12.3</v>
       </c>
       <c r="L16" t="n">
-        <v>69.92</v>
+        <v>71.31999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:46:36</t>
+          <t>04:48:26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.87</v>
+        <v>3.88</v>
       </c>
       <c r="F17" t="n">
-        <v>7.17</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>284.1</v>
+        <v>275.7</v>
       </c>
       <c r="H17" t="n">
-        <v>60.6</v>
+        <v>40.3</v>
       </c>
       <c r="I17" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>-102.46</v>
+        <v>59.76</v>
       </c>
       <c r="K17" t="n">
-        <v>-14.64</v>
+        <v>-34.59</v>
       </c>
       <c r="L17" t="n">
-        <v>103.5</v>
+        <v>69.05</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:47:55</t>
+          <t>04:49:02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.34</v>
+        <v>3.89</v>
       </c>
       <c r="F18" t="n">
-        <v>10.5</v>
+        <v>10.09</v>
       </c>
       <c r="G18" t="n">
-        <v>278.1</v>
+        <v>284.4</v>
       </c>
       <c r="H18" t="n">
-        <v>43.1</v>
+        <v>65</v>
       </c>
       <c r="I18" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>-38.66</v>
+        <v>37.92</v>
       </c>
       <c r="K18" t="n">
-        <v>35.26</v>
+        <v>34.19</v>
       </c>
       <c r="L18" t="n">
-        <v>52.32</v>
+        <v>51.06</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:50:03</t>
+          <t>04:51:30</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="F19" t="n">
-        <v>9.859999999999999</v>
+        <v>6.85</v>
       </c>
       <c r="G19" t="n">
-        <v>290.7</v>
+        <v>298.6</v>
       </c>
       <c r="H19" t="n">
-        <v>17</v>
+        <v>21.9</v>
       </c>
       <c r="I19" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>-126.54</v>
+        <v>-41.98</v>
       </c>
       <c r="K19" t="n">
-        <v>4.56</v>
+        <v>23.33</v>
       </c>
       <c r="L19" t="n">
-        <v>126.63</v>
+        <v>48.03</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:53:30</t>
+          <t>04:55:55</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>4.45</v>
+        <v>3.66</v>
       </c>
       <c r="F20" t="n">
-        <v>7.01</v>
+        <v>7.23</v>
       </c>
       <c r="G20" t="n">
-        <v>282.8</v>
+        <v>278.7</v>
       </c>
       <c r="H20" t="n">
-        <v>78</v>
+        <v>41.9</v>
       </c>
       <c r="I20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-156.53</v>
+        <v>115.64</v>
       </c>
       <c r="K20" t="n">
-        <v>80.86</v>
+        <v>-34.86</v>
       </c>
       <c r="L20" t="n">
-        <v>176.19</v>
+        <v>120.78</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:55:13</t>
+          <t>04:58:16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.84</v>
+        <v>3.96</v>
       </c>
       <c r="F21" t="n">
-        <v>6.92</v>
+        <v>6.95</v>
       </c>
       <c r="G21" t="n">
-        <v>274.3</v>
+        <v>292.5</v>
       </c>
       <c r="H21" t="n">
-        <v>67.3</v>
+        <v>61.1</v>
       </c>
       <c r="I21" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>1.19</v>
+        <v>127.65</v>
       </c>
       <c r="K21" t="n">
-        <v>-163.53</v>
+        <v>-17.94</v>
       </c>
       <c r="L21" t="n">
-        <v>163.53</v>
+        <v>128.91</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:57:11</t>
+          <t>05:00:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>4.34</v>
+        <v>4.35</v>
       </c>
       <c r="F22" t="n">
-        <v>12.54</v>
+        <v>9.08</v>
       </c>
       <c r="G22" t="n">
-        <v>280.2</v>
+        <v>290.1</v>
       </c>
       <c r="H22" t="n">
-        <v>60.9</v>
+        <v>53</v>
       </c>
       <c r="I22" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>-62.38</v>
+        <v>13.77</v>
       </c>
       <c r="K22" t="n">
-        <v>137.81</v>
+        <v>72.02</v>
       </c>
       <c r="L22" t="n">
-        <v>151.28</v>
+        <v>73.31999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:00:48</t>
+          <t>05:05:36</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.62</v>
+        <v>4.18</v>
       </c>
       <c r="F23" t="n">
-        <v>5.61</v>
+        <v>12.54</v>
       </c>
       <c r="G23" t="n">
-        <v>274.2</v>
+        <v>291.8</v>
       </c>
       <c r="H23" t="n">
-        <v>62.3</v>
+        <v>82.5</v>
       </c>
       <c r="I23" t="n">
         <v>20</v>
       </c>
       <c r="J23" t="n">
-        <v>-166.88</v>
+        <v>165.05</v>
       </c>
       <c r="K23" t="n">
-        <v>152.16</v>
+        <v>-62.79</v>
       </c>
       <c r="L23" t="n">
-        <v>225.84</v>
+        <v>176.59</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:02:06</t>
+          <t>05:07:33</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.46</v>
+        <v>3.66</v>
       </c>
       <c r="F24" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="G24" t="n">
-        <v>281.2</v>
+        <v>280</v>
       </c>
       <c r="H24" t="n">
-        <v>53.2</v>
+        <v>39.3</v>
       </c>
       <c r="I24" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J24" t="n">
-        <v>-112.44</v>
+        <v>-194.86</v>
       </c>
       <c r="K24" t="n">
-        <v>-101.89</v>
+        <v>103.52</v>
       </c>
       <c r="L24" t="n">
-        <v>151.74</v>
+        <v>220.65</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:04:24</t>
+          <t>05:09:11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.68</v>
+        <v>4.29</v>
       </c>
       <c r="F25" t="n">
-        <v>9.289999999999999</v>
+        <v>11.51</v>
       </c>
       <c r="G25" t="n">
-        <v>281.5</v>
+        <v>295.4</v>
       </c>
       <c r="H25" t="n">
-        <v>69.8</v>
+        <v>22.1</v>
       </c>
       <c r="I25" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>2.39</v>
+        <v>-35.28</v>
       </c>
       <c r="K25" t="n">
-        <v>-221.77</v>
+        <v>162.27</v>
       </c>
       <c r="L25" t="n">
-        <v>221.79</v>
+        <v>166.06</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:08:41</t>
+          <t>05:12:27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>4.02</v>
+        <v>4.09</v>
       </c>
       <c r="F26" t="n">
-        <v>9.32</v>
+        <v>10.93</v>
       </c>
       <c r="G26" t="n">
-        <v>289.9</v>
+        <v>291.6</v>
       </c>
       <c r="H26" t="n">
-        <v>63.1</v>
+        <v>16.2</v>
       </c>
       <c r="I26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J26" t="n">
-        <v>-231.31</v>
+        <v>262.19</v>
       </c>
       <c r="K26" t="n">
-        <v>139.61</v>
+        <v>-141.8</v>
       </c>
       <c r="L26" t="n">
-        <v>270.17</v>
+        <v>298.08</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:10:15</t>
+          <t>05:13:43</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.1</v>
+        <v>3.93</v>
       </c>
       <c r="F27" t="n">
-        <v>11.26</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>276.2</v>
+        <v>286</v>
       </c>
       <c r="H27" t="n">
-        <v>47.8</v>
+        <v>37.5</v>
       </c>
       <c r="I27" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J27" t="n">
-        <v>-63.44</v>
+        <v>200.79</v>
       </c>
       <c r="K27" t="n">
-        <v>-290.85</v>
+        <v>-151.97</v>
       </c>
       <c r="L27" t="n">
-        <v>297.69</v>
+        <v>251.82</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:12:03</t>
+          <t>05:15:04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>4.36</v>
+        <v>3.99</v>
       </c>
       <c r="F28" t="n">
-        <v>12.54</v>
+        <v>8.35</v>
       </c>
       <c r="G28" t="n">
-        <v>281</v>
+        <v>278.8</v>
       </c>
       <c r="H28" t="n">
-        <v>53</v>
+        <v>20.5</v>
       </c>
       <c r="I28" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>-277.87</v>
+        <v>146.45</v>
       </c>
       <c r="K28" t="n">
-        <v>-20.78</v>
+        <v>127.99</v>
       </c>
       <c r="L28" t="n">
-        <v>278.65</v>
+        <v>194.49</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:21:58</t>
+          <t>05:26:18</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>4.03</v>
+        <v>4.24</v>
       </c>
       <c r="F29" t="n">
-        <v>10.01</v>
+        <v>10.5</v>
       </c>
       <c r="G29" t="n">
-        <v>293.4</v>
+        <v>290</v>
       </c>
       <c r="H29" t="n">
-        <v>90.7</v>
+        <v>22</v>
       </c>
       <c r="I29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J29" t="n">
-        <v>58.4</v>
+        <v>-38.89</v>
       </c>
       <c r="K29" t="n">
-        <v>-48.46</v>
+        <v>54.19</v>
       </c>
       <c r="L29" t="n">
-        <v>75.89</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:23:22</t>
+          <t>05:27:47</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.67</v>
+        <v>3.9</v>
       </c>
       <c r="F30" t="n">
-        <v>8.58</v>
+        <v>10.72</v>
       </c>
       <c r="G30" t="n">
-        <v>278.9</v>
+        <v>278.6</v>
       </c>
       <c r="H30" t="n">
-        <v>56.6</v>
+        <v>29.9</v>
       </c>
       <c r="I30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>-58.07</v>
+        <v>20.07</v>
       </c>
       <c r="K30" t="n">
-        <v>-58.81</v>
+        <v>-42.54</v>
       </c>
       <c r="L30" t="n">
-        <v>82.65000000000001</v>
+        <v>47.04</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:23:59</t>
+          <t>05:28:49</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.61</v>
+        <v>3.45</v>
       </c>
       <c r="F31" t="n">
-        <v>9.699999999999999</v>
+        <v>9.27</v>
       </c>
       <c r="G31" t="n">
-        <v>274.2</v>
+        <v>261.7</v>
       </c>
       <c r="H31" t="n">
-        <v>84.59999999999999</v>
+        <v>23.9</v>
       </c>
       <c r="I31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J31" t="n">
-        <v>30.81</v>
+        <v>-34.99</v>
       </c>
       <c r="K31" t="n">
-        <v>-50.9</v>
+        <v>-52.28</v>
       </c>
       <c r="L31" t="n">
-        <v>59.5</v>
+        <v>62.91</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:28:23</t>
+          <t>05:34:59</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.44</v>
+        <v>4.13</v>
       </c>
       <c r="F32" t="n">
-        <v>6.27</v>
+        <v>10.31</v>
       </c>
       <c r="G32" t="n">
-        <v>284.9</v>
+        <v>268.8</v>
       </c>
       <c r="H32" t="n">
-        <v>73.40000000000001</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J32" t="n">
-        <v>-38.19</v>
+        <v>-19.45</v>
       </c>
       <c r="K32" t="n">
-        <v>-75.56999999999999</v>
+        <v>-79.18000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>84.67</v>
+        <v>81.54000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:30:51</t>
+          <t>05:37:05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.36</v>
+        <v>4.27</v>
       </c>
       <c r="F33" t="n">
-        <v>12.54</v>
+        <v>7.98</v>
       </c>
       <c r="G33" t="n">
-        <v>295.2</v>
+        <v>293.5</v>
       </c>
       <c r="H33" t="n">
-        <v>43.5</v>
+        <v>17.5</v>
       </c>
       <c r="I33" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>-60.07</v>
+        <v>15.64</v>
       </c>
       <c r="K33" t="n">
-        <v>75.81999999999999</v>
+        <v>44.34</v>
       </c>
       <c r="L33" t="n">
-        <v>96.73</v>
+        <v>47.02</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:32:57</t>
+          <t>05:37:56</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.73</v>
+        <v>3.9</v>
       </c>
       <c r="F34" t="n">
-        <v>10.66</v>
+        <v>11.79</v>
       </c>
       <c r="G34" t="n">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="H34" t="n">
-        <v>50</v>
+        <v>50.6</v>
       </c>
       <c r="I34" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>88.48</v>
+        <v>-87.34999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>78.64</v>
+        <v>22.11</v>
       </c>
       <c r="L34" t="n">
-        <v>118.37</v>
+        <v>90.09999999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:36:59</t>
+          <t>05:43:30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>4.22</v>
+        <v>3.98</v>
       </c>
       <c r="F35" t="n">
-        <v>11.97</v>
+        <v>11.36</v>
       </c>
       <c r="G35" t="n">
-        <v>283.8</v>
+        <v>264.9</v>
       </c>
       <c r="H35" t="n">
-        <v>50.1</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J35" t="n">
-        <v>125.8</v>
+        <v>114.14</v>
       </c>
       <c r="K35" t="n">
-        <v>67.13</v>
+        <v>7.56</v>
       </c>
       <c r="L35" t="n">
-        <v>142.59</v>
+        <v>114.39</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:38:36</t>
+          <t>05:44:45</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.87</v>
+        <v>4.36</v>
       </c>
       <c r="F36" t="n">
-        <v>11.13</v>
+        <v>11.52</v>
       </c>
       <c r="G36" t="n">
-        <v>286.6</v>
+        <v>277</v>
       </c>
       <c r="H36" t="n">
-        <v>63</v>
+        <v>53.4</v>
       </c>
       <c r="I36" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>-170.02</v>
+        <v>-35.32</v>
       </c>
       <c r="K36" t="n">
-        <v>1.72</v>
+        <v>133.53</v>
       </c>
       <c r="L36" t="n">
-        <v>170.03</v>
+        <v>138.12</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:41:00</t>
+          <t>05:47:05</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>4.65</v>
+        <v>3.51</v>
       </c>
       <c r="F37" t="n">
-        <v>12.54</v>
+        <v>7.82</v>
       </c>
       <c r="G37" t="n">
-        <v>261.7</v>
+        <v>286.4</v>
       </c>
       <c r="H37" t="n">
-        <v>32.4</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>-193.57</v>
+        <v>80.79000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>98.47</v>
+        <v>-69.23999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>217.18</v>
+        <v>106.4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:44:16</t>
+          <t>05:52:00</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="F38" t="n">
-        <v>7.66</v>
+        <v>9.66</v>
       </c>
       <c r="G38" t="n">
-        <v>270.4</v>
+        <v>267</v>
       </c>
       <c r="H38" t="n">
-        <v>82.59999999999999</v>
+        <v>19.6</v>
       </c>
       <c r="I38" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J38" t="n">
-        <v>-193.07</v>
+        <v>174.04</v>
       </c>
       <c r="K38" t="n">
-        <v>-103.29</v>
+        <v>-109.72</v>
       </c>
       <c r="L38" t="n">
-        <v>218.96</v>
+        <v>205.74</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:45:53</t>
+          <t>05:53:46</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>4</v>
+        <v>4.04</v>
       </c>
       <c r="F39" t="n">
-        <v>9.720000000000001</v>
+        <v>9.18</v>
       </c>
       <c r="G39" t="n">
-        <v>285.1</v>
+        <v>283.2</v>
       </c>
       <c r="H39" t="n">
-        <v>51</v>
+        <v>16.9</v>
       </c>
       <c r="I39" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>29.77</v>
+        <v>82.38</v>
       </c>
       <c r="K39" t="n">
-        <v>230.21</v>
+        <v>197.79</v>
       </c>
       <c r="L39" t="n">
-        <v>232.13</v>
+        <v>214.26</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:46:34</t>
+          <t>05:55:41</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.71</v>
+        <v>4.03</v>
       </c>
       <c r="F40" t="n">
-        <v>7.99</v>
+        <v>10.48</v>
       </c>
       <c r="G40" t="n">
-        <v>285.6</v>
+        <v>279.6</v>
       </c>
       <c r="H40" t="n">
-        <v>95.09999999999999</v>
+        <v>48</v>
       </c>
       <c r="I40" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>135.37</v>
+        <v>-220.23</v>
       </c>
       <c r="K40" t="n">
-        <v>13.33</v>
+        <v>37.99</v>
       </c>
       <c r="L40" t="n">
-        <v>136.03</v>
+        <v>223.48</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:52:35</t>
+          <t>05:59:02</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>4.02</v>
+        <v>4.19</v>
       </c>
       <c r="F41" t="n">
-        <v>11.47</v>
+        <v>12.54</v>
       </c>
       <c r="G41" t="n">
-        <v>282.4</v>
+        <v>281.2</v>
       </c>
       <c r="H41" t="n">
-        <v>53.7</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J41" t="n">
-        <v>-279.03</v>
+        <v>250.63</v>
       </c>
       <c r="K41" t="n">
-        <v>3.98</v>
+        <v>-142.85</v>
       </c>
       <c r="L41" t="n">
-        <v>279.06</v>
+        <v>288.48</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05:55:00</t>
+          <t>06:00:08</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.76</v>
+        <v>4.21</v>
       </c>
       <c r="F42" t="n">
-        <v>11.08</v>
+        <v>11.24</v>
       </c>
       <c r="G42" t="n">
-        <v>281.9</v>
+        <v>274.5</v>
       </c>
       <c r="H42" t="n">
-        <v>65.59999999999999</v>
+        <v>42.8</v>
       </c>
       <c r="I42" t="n">
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>-308.07</v>
+        <v>143.32</v>
       </c>
       <c r="K42" t="n">
-        <v>9.859999999999999</v>
+        <v>-255.23</v>
       </c>
       <c r="L42" t="n">
-        <v>308.23</v>
+        <v>292.71</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05:55:56</t>
+          <t>06:02:27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.47</v>
+        <v>4.32</v>
       </c>
       <c r="F43" t="n">
-        <v>12.54</v>
+        <v>11.78</v>
       </c>
       <c r="G43" t="n">
-        <v>281.2</v>
+        <v>285.7</v>
       </c>
       <c r="H43" t="n">
-        <v>39.8</v>
+        <v>31</v>
       </c>
       <c r="I43" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>-211.98</v>
+        <v>-198.86</v>
       </c>
       <c r="K43" t="n">
-        <v>-235.99</v>
+        <v>148.88</v>
       </c>
       <c r="L43" t="n">
-        <v>317.21</v>
+        <v>248.41</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:05:16</t>
+          <t>06:16:00</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>4.45</v>
+        <v>4.3</v>
       </c>
       <c r="F44" t="n">
-        <v>10.47</v>
+        <v>12.54</v>
       </c>
       <c r="G44" t="n">
-        <v>277.4</v>
+        <v>296.1</v>
       </c>
       <c r="H44" t="n">
-        <v>47.3</v>
+        <v>57.8</v>
       </c>
       <c r="I44" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J44" t="n">
-        <v>-90.89</v>
+        <v>-61.74</v>
       </c>
       <c r="K44" t="n">
-        <v>-19.46</v>
+        <v>21.17</v>
       </c>
       <c r="L44" t="n">
-        <v>92.95</v>
+        <v>65.27</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:06:37</t>
+          <t>06:16:52</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.03</v>
+        <v>4.1</v>
       </c>
       <c r="F45" t="n">
-        <v>9.34</v>
+        <v>8.93</v>
       </c>
       <c r="G45" t="n">
-        <v>270.3</v>
+        <v>279.2</v>
       </c>
       <c r="H45" t="n">
-        <v>42.9</v>
+        <v>73</v>
       </c>
       <c r="I45" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>-8.6</v>
+        <v>-3.03</v>
       </c>
       <c r="K45" t="n">
-        <v>-69.81999999999999</v>
+        <v>-70.08</v>
       </c>
       <c r="L45" t="n">
-        <v>70.34999999999999</v>
+        <v>70.14</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:08:47</t>
+          <t>06:18:20</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.88</v>
+        <v>3.61</v>
       </c>
       <c r="F46" t="n">
-        <v>10.14</v>
+        <v>11.18</v>
       </c>
       <c r="G46" t="n">
-        <v>281.2</v>
+        <v>281.8</v>
       </c>
       <c r="H46" t="n">
-        <v>44.4</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>-75.95999999999999</v>
+        <v>-61.62</v>
       </c>
       <c r="K46" t="n">
-        <v>24.25</v>
+        <v>-4.99</v>
       </c>
       <c r="L46" t="n">
-        <v>79.73999999999999</v>
+        <v>61.83</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:14:12</t>
+          <t>06:21:50</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.11</v>
+        <v>4.29</v>
       </c>
       <c r="F47" t="n">
-        <v>9.470000000000001</v>
+        <v>11.04</v>
       </c>
       <c r="G47" t="n">
-        <v>265</v>
+        <v>281.8</v>
       </c>
       <c r="H47" t="n">
-        <v>47.9</v>
+        <v>43.5</v>
       </c>
       <c r="I47" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J47" t="n">
-        <v>14.28</v>
+        <v>-19.25</v>
       </c>
       <c r="K47" t="n">
-        <v>-110.54</v>
+        <v>-93.91</v>
       </c>
       <c r="L47" t="n">
-        <v>111.46</v>
+        <v>95.87</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:16:35</t>
+          <t>06:23:44</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.43</v>
+        <v>4.32</v>
       </c>
       <c r="F48" t="n">
-        <v>12.54</v>
+        <v>12.16</v>
       </c>
       <c r="G48" t="n">
-        <v>288.1</v>
+        <v>268.8</v>
       </c>
       <c r="H48" t="n">
-        <v>43.8</v>
+        <v>61.9</v>
       </c>
       <c r="I48" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>-103.1</v>
+        <v>97.26000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>-53.82</v>
+        <v>-50.38</v>
       </c>
       <c r="L48" t="n">
-        <v>116.31</v>
+        <v>109.53</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:18:45</t>
+          <t>06:25:52</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.21</v>
+        <v>4.63</v>
       </c>
       <c r="F49" t="n">
-        <v>7.37</v>
+        <v>10.39</v>
       </c>
       <c r="G49" t="n">
-        <v>290.4</v>
+        <v>285.9</v>
       </c>
       <c r="H49" t="n">
-        <v>54.6</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>66.04000000000001</v>
+        <v>-123.12</v>
       </c>
       <c r="K49" t="n">
-        <v>-66.16</v>
+        <v>29.74</v>
       </c>
       <c r="L49" t="n">
-        <v>93.48</v>
+        <v>126.66</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:22:36</t>
+          <t>06:30:25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.34</v>
+        <v>4.1</v>
       </c>
       <c r="F50" t="n">
-        <v>9.59</v>
+        <v>12.54</v>
       </c>
       <c r="G50" t="n">
-        <v>266.4</v>
+        <v>279.2</v>
       </c>
       <c r="H50" t="n">
-        <v>38.9</v>
+        <v>21.5</v>
       </c>
       <c r="I50" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>-56.9</v>
+        <v>133.2</v>
       </c>
       <c r="K50" t="n">
-        <v>-121.16</v>
+        <v>1.94</v>
       </c>
       <c r="L50" t="n">
-        <v>133.86</v>
+        <v>133.22</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:24:12</t>
+          <t>06:31:55</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.96</v>
+        <v>3.97</v>
       </c>
       <c r="F51" t="n">
-        <v>9.56</v>
+        <v>12.54</v>
       </c>
       <c r="G51" t="n">
-        <v>268.6</v>
+        <v>277.1</v>
       </c>
       <c r="H51" t="n">
-        <v>46.3</v>
+        <v>58.2</v>
       </c>
       <c r="I51" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J51" t="n">
-        <v>-138.85</v>
+        <v>-34.93</v>
       </c>
       <c r="K51" t="n">
-        <v>-75.65000000000001</v>
+        <v>174.26</v>
       </c>
       <c r="L51" t="n">
-        <v>158.12</v>
+        <v>177.73</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:24:58</t>
+          <t>06:34:45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.42</v>
+        <v>3.21</v>
       </c>
       <c r="F52" t="n">
-        <v>10.39</v>
+        <v>11.87</v>
       </c>
       <c r="G52" t="n">
-        <v>295.6</v>
+        <v>293.9</v>
       </c>
       <c r="H52" t="n">
-        <v>57.7</v>
+        <v>59.4</v>
       </c>
       <c r="I52" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J52" t="n">
-        <v>118.08</v>
+        <v>-78.39</v>
       </c>
       <c r="K52" t="n">
-        <v>-28.78</v>
+        <v>28.65</v>
       </c>
       <c r="L52" t="n">
-        <v>121.54</v>
+        <v>83.45999999999999</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:29:20</t>
+          <t>06:40:32</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="F53" t="n">
-        <v>10.65</v>
+        <v>7.05</v>
       </c>
       <c r="G53" t="n">
-        <v>288.3</v>
+        <v>283.3</v>
       </c>
       <c r="H53" t="n">
-        <v>37.2</v>
+        <v>37.5</v>
       </c>
       <c r="I53" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J53" t="n">
-        <v>-176.1</v>
+        <v>90.14</v>
       </c>
       <c r="K53" t="n">
-        <v>-170.74</v>
+        <v>-167.73</v>
       </c>
       <c r="L53" t="n">
-        <v>245.28</v>
+        <v>190.42</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:30:24</t>
+          <t>06:41:39</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.38</v>
+        <v>4.55</v>
       </c>
       <c r="F54" t="n">
-        <v>10.03</v>
+        <v>9.43</v>
       </c>
       <c r="G54" t="n">
-        <v>283.2</v>
+        <v>288</v>
       </c>
       <c r="H54" t="n">
-        <v>32</v>
+        <v>69.5</v>
       </c>
       <c r="I54" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>183.71</v>
+        <v>165</v>
       </c>
       <c r="K54" t="n">
-        <v>118.55</v>
+        <v>99.56</v>
       </c>
       <c r="L54" t="n">
-        <v>218.64</v>
+        <v>192.71</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:32:20</t>
+          <t>06:44:15</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.63</v>
+        <v>3.94</v>
       </c>
       <c r="F55" t="n">
-        <v>12.1</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="G55" t="n">
-        <v>288.8</v>
+        <v>277.7</v>
       </c>
       <c r="H55" t="n">
-        <v>80.59999999999999</v>
+        <v>45.3</v>
       </c>
       <c r="I55" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-194.38</v>
+        <v>-48.22</v>
       </c>
       <c r="K55" t="n">
-        <v>-15.05</v>
+        <v>227.38</v>
       </c>
       <c r="L55" t="n">
-        <v>194.96</v>
+        <v>232.44</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:37:19</t>
+          <t>06:50:19</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.08</v>
+        <v>4.53</v>
       </c>
       <c r="F56" t="n">
-        <v>9.529999999999999</v>
+        <v>11.95</v>
       </c>
       <c r="G56" t="n">
-        <v>282.5</v>
+        <v>280.7</v>
       </c>
       <c r="H56" t="n">
-        <v>69</v>
+        <v>38.4</v>
       </c>
       <c r="I56" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>206.62</v>
+        <v>139.42</v>
       </c>
       <c r="K56" t="n">
-        <v>128.18</v>
+        <v>-318.32</v>
       </c>
       <c r="L56" t="n">
-        <v>243.15</v>
+        <v>347.51</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:39:57</t>
+          <t>06:51:10</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4.24</v>
+        <v>4.27</v>
       </c>
       <c r="F57" t="n">
-        <v>10.45</v>
+        <v>12.54</v>
       </c>
       <c r="G57" t="n">
-        <v>272.2</v>
+        <v>279</v>
       </c>
       <c r="H57" t="n">
-        <v>41.9</v>
+        <v>41.1</v>
       </c>
       <c r="I57" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>-344.54</v>
+        <v>-187.93</v>
       </c>
       <c r="K57" t="n">
-        <v>16.86</v>
+        <v>-167.31</v>
       </c>
       <c r="L57" t="n">
-        <v>344.95</v>
+        <v>251.61</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:41:12</t>
+          <t>06:53:05</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.55</v>
+        <v>3.99</v>
       </c>
       <c r="F58" t="n">
-        <v>12.54</v>
+        <v>8.99</v>
       </c>
       <c r="G58" t="n">
-        <v>283.8</v>
+        <v>279.6</v>
       </c>
       <c r="H58" t="n">
-        <v>75.8</v>
+        <v>52.5</v>
       </c>
       <c r="I58" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J58" t="n">
-        <v>309.34</v>
+        <v>-236.82</v>
       </c>
       <c r="K58" t="n">
-        <v>-142.01</v>
+        <v>113.41</v>
       </c>
       <c r="L58" t="n">
-        <v>340.38</v>
+        <v>262.57</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:51:52</t>
+          <t>07:04:20</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.86</v>
+        <v>5.13</v>
       </c>
       <c r="F59" t="n">
-        <v>8.880000000000001</v>
+        <v>12.39</v>
       </c>
       <c r="G59" t="n">
-        <v>274.7</v>
+        <v>265</v>
       </c>
       <c r="H59" t="n">
-        <v>62.7</v>
+        <v>47.9</v>
       </c>
       <c r="I59" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>-25.17</v>
+        <v>33.33</v>
       </c>
       <c r="K59" t="n">
-        <v>64.61</v>
+        <v>-89.69</v>
       </c>
       <c r="L59" t="n">
-        <v>69.34</v>
+        <v>95.68000000000001</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:54:33</t>
+          <t>07:06:47</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>5.04</v>
+        <v>4.6</v>
       </c>
       <c r="F60" t="n">
-        <v>10.82</v>
+        <v>12.54</v>
       </c>
       <c r="G60" t="n">
-        <v>291.4</v>
+        <v>288.1</v>
       </c>
       <c r="H60" t="n">
-        <v>81.3</v>
+        <v>43.8</v>
       </c>
       <c r="I60" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J60" t="n">
-        <v>-130.18</v>
+        <v>-69.86</v>
       </c>
       <c r="K60" t="n">
-        <v>-14.46</v>
+        <v>-10.87</v>
       </c>
       <c r="L60" t="n">
-        <v>130.98</v>
+        <v>70.7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06:55:37</t>
+          <t>07:08:44</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.95</v>
+        <v>4.36</v>
       </c>
       <c r="F61" t="n">
-        <v>12.54</v>
+        <v>7.33</v>
       </c>
       <c r="G61" t="n">
-        <v>283</v>
+        <v>290.2</v>
       </c>
       <c r="H61" t="n">
-        <v>28.4</v>
+        <v>37.7</v>
       </c>
       <c r="I61" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J61" t="n">
-        <v>-48.25</v>
+        <v>-62.81</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.25</v>
+        <v>45.02</v>
       </c>
       <c r="L61" t="n">
-        <v>48.25</v>
+        <v>77.28</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:00:08</t>
+          <t>07:12:20</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.19</v>
+        <v>4.7</v>
       </c>
       <c r="F62" t="n">
-        <v>12.37</v>
+        <v>12.54</v>
       </c>
       <c r="G62" t="n">
-        <v>281.5</v>
+        <v>273.5</v>
       </c>
       <c r="H62" t="n">
-        <v>57.4</v>
+        <v>42.1</v>
       </c>
       <c r="I62" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>10.97</v>
+        <v>-92.36</v>
       </c>
       <c r="K62" t="n">
-        <v>-124.3</v>
+        <v>31.87</v>
       </c>
       <c r="L62" t="n">
-        <v>124.78</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:02:38</t>
+          <t>07:14:39</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.75</v>
+        <v>4.49</v>
       </c>
       <c r="F63" t="n">
-        <v>11.07</v>
+        <v>10.93</v>
       </c>
       <c r="G63" t="n">
-        <v>277.6</v>
+        <v>274.2</v>
       </c>
       <c r="H63" t="n">
-        <v>32.9</v>
+        <v>41.2</v>
       </c>
       <c r="I63" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-106.38</v>
+        <v>22.44</v>
       </c>
       <c r="K63" t="n">
-        <v>20.18</v>
+        <v>-106.55</v>
       </c>
       <c r="L63" t="n">
-        <v>108.28</v>
+        <v>108.89</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:03:46</t>
+          <t>07:16:31</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.46</v>
+        <v>4.42</v>
       </c>
       <c r="F64" t="n">
-        <v>11.35</v>
+        <v>8.33</v>
       </c>
       <c r="G64" t="n">
-        <v>277.3</v>
+        <v>289.6</v>
       </c>
       <c r="H64" t="n">
-        <v>23.7</v>
+        <v>37.7</v>
       </c>
       <c r="I64" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>136.66</v>
+        <v>-20.64</v>
       </c>
       <c r="K64" t="n">
-        <v>53.27</v>
+        <v>118.97</v>
       </c>
       <c r="L64" t="n">
-        <v>146.67</v>
+        <v>120.74</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:09:43</t>
+          <t>07:21:16</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.81</v>
+        <v>4.16</v>
       </c>
       <c r="F65" t="n">
-        <v>12.54</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="G65" t="n">
-        <v>263.9</v>
+        <v>294.4</v>
       </c>
       <c r="H65" t="n">
-        <v>34</v>
+        <v>55.6</v>
       </c>
       <c r="I65" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>-94.87</v>
+        <v>141.13</v>
       </c>
       <c r="K65" t="n">
-        <v>-185.02</v>
+        <v>12.26</v>
       </c>
       <c r="L65" t="n">
-        <v>207.93</v>
+        <v>141.67</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:11:48</t>
+          <t>07:23:47</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.14</v>
+        <v>4.32</v>
       </c>
       <c r="F66" t="n">
-        <v>12.54</v>
+        <v>11</v>
       </c>
       <c r="G66" t="n">
-        <v>273.1</v>
+        <v>281.9</v>
       </c>
       <c r="H66" t="n">
-        <v>65.2</v>
+        <v>60.5</v>
       </c>
       <c r="I66" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-75.92</v>
+        <v>-137.18</v>
       </c>
       <c r="K66" t="n">
-        <v>-130.22</v>
+        <v>10.65</v>
       </c>
       <c r="L66" t="n">
-        <v>150.73</v>
+        <v>137.59</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:12:25</t>
+          <t>07:26:09</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.57</v>
+        <v>4.77</v>
       </c>
       <c r="F67" t="n">
-        <v>12.54</v>
+        <v>9.43</v>
       </c>
       <c r="G67" t="n">
-        <v>264.4</v>
+        <v>282.3</v>
       </c>
       <c r="H67" t="n">
-        <v>58.5</v>
+        <v>43.3</v>
       </c>
       <c r="I67" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J67" t="n">
-        <v>95.61</v>
+        <v>-170.05</v>
       </c>
       <c r="K67" t="n">
-        <v>149.05</v>
+        <v>-18.87</v>
       </c>
       <c r="L67" t="n">
-        <v>177.08</v>
+        <v>171.09</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:17:26</t>
+          <t>07:29:15</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.83</v>
+        <v>4.65</v>
       </c>
       <c r="F68" t="n">
-        <v>12.48</v>
+        <v>10.95</v>
       </c>
       <c r="G68" t="n">
-        <v>266</v>
+        <v>276.3</v>
       </c>
       <c r="H68" t="n">
-        <v>63</v>
+        <v>42.1</v>
       </c>
       <c r="I68" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-212.6</v>
+        <v>-199.98</v>
       </c>
       <c r="K68" t="n">
-        <v>254.73</v>
+        <v>-120.29</v>
       </c>
       <c r="L68" t="n">
-        <v>331.79</v>
+        <v>233.37</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:18:24</t>
+          <t>07:31:16</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.87</v>
+        <v>4.55</v>
       </c>
       <c r="F69" t="n">
-        <v>12.54</v>
+        <v>11.71</v>
       </c>
       <c r="G69" t="n">
-        <v>260.9</v>
+        <v>278.7</v>
       </c>
       <c r="H69" t="n">
-        <v>55</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I69" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>-40.9</v>
+        <v>-101.89</v>
       </c>
       <c r="K69" t="n">
-        <v>288.73</v>
+        <v>-160.03</v>
       </c>
       <c r="L69" t="n">
-        <v>291.61</v>
+        <v>189.71</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:19:43</t>
+          <t>07:32:17</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.29</v>
+        <v>4.08</v>
       </c>
       <c r="F70" t="n">
-        <v>12.34</v>
+        <v>10.62</v>
       </c>
       <c r="G70" t="n">
-        <v>291.7</v>
+        <v>290.2</v>
       </c>
       <c r="H70" t="n">
-        <v>40.7</v>
+        <v>43.7</v>
       </c>
       <c r="I70" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>-116.16</v>
+        <v>-68.91</v>
       </c>
       <c r="K70" t="n">
-        <v>290.36</v>
+        <v>210.44</v>
       </c>
       <c r="L70" t="n">
-        <v>312.73</v>
+        <v>221.44</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:23:24</t>
+          <t>07:37:29</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.54</v>
+        <v>4.23</v>
       </c>
       <c r="F71" t="n">
-        <v>9.81</v>
+        <v>12.54</v>
       </c>
       <c r="G71" t="n">
-        <v>279.4</v>
+        <v>272.4</v>
       </c>
       <c r="H71" t="n">
-        <v>5.2</v>
+        <v>41.7</v>
       </c>
       <c r="I71" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>-210.3</v>
+        <v>267.94</v>
       </c>
       <c r="K71" t="n">
-        <v>180.47</v>
+        <v>178.61</v>
       </c>
       <c r="L71" t="n">
-        <v>277.12</v>
+        <v>322.02</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:25:14</t>
+          <t>07:38:58</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.67</v>
+        <v>4.11</v>
       </c>
       <c r="F72" t="n">
-        <v>9.77</v>
+        <v>10.58</v>
       </c>
       <c r="G72" t="n">
-        <v>281.9</v>
+        <v>273.1</v>
       </c>
       <c r="H72" t="n">
-        <v>23.9</v>
+        <v>69.8</v>
       </c>
       <c r="I72" t="n">
         <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>-250.2</v>
+        <v>-126.62</v>
       </c>
       <c r="K72" t="n">
-        <v>254.72</v>
+        <v>-151.9</v>
       </c>
       <c r="L72" t="n">
-        <v>357.05</v>
+        <v>197.75</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:26:38</t>
+          <t>07:40:45</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.29</v>
+        <v>4.52</v>
       </c>
       <c r="F73" t="n">
-        <v>10.79</v>
+        <v>12.14</v>
       </c>
       <c r="G73" t="n">
-        <v>294.6</v>
+        <v>274</v>
       </c>
       <c r="H73" t="n">
-        <v>34.5</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J73" t="n">
-        <v>-226.12</v>
+        <v>-257.58</v>
       </c>
       <c r="K73" t="n">
-        <v>-48.01</v>
+        <v>-31.32</v>
       </c>
       <c r="L73" t="n">
-        <v>231.16</v>
+        <v>259.48</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:39:20</t>
+          <t>07:52:19</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>5.14</v>
+        <v>4.63</v>
       </c>
       <c r="F74" t="n">
         <v>12.54</v>
       </c>
       <c r="G74" t="n">
-        <v>281.1</v>
+        <v>279.2</v>
       </c>
       <c r="H74" t="n">
-        <v>34.2</v>
+        <v>70.2</v>
       </c>
       <c r="I74" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>-15.2</v>
+        <v>82.47</v>
       </c>
       <c r="K74" t="n">
-        <v>-111.62</v>
+        <v>26.28</v>
       </c>
       <c r="L74" t="n">
-        <v>112.65</v>
+        <v>86.56</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:41:22</t>
+          <t>07:54:18</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.41</v>
+        <v>4.56</v>
       </c>
       <c r="F75" t="n">
-        <v>10.86</v>
+        <v>12.54</v>
       </c>
       <c r="G75" t="n">
-        <v>275.2</v>
+        <v>268</v>
       </c>
       <c r="H75" t="n">
-        <v>16.4</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="I75" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-61.83</v>
+        <v>42.58</v>
       </c>
       <c r="K75" t="n">
-        <v>-59.92</v>
+        <v>56.06</v>
       </c>
       <c r="L75" t="n">
-        <v>86.09999999999999</v>
+        <v>70.39</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:42:37</t>
+          <t>07:55:08</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4.53</v>
+        <v>4.55</v>
       </c>
       <c r="F76" t="n">
-        <v>12.39</v>
+        <v>12.15</v>
       </c>
       <c r="G76" t="n">
-        <v>281.3</v>
+        <v>284.6</v>
       </c>
       <c r="H76" t="n">
-        <v>46.2</v>
+        <v>58.6</v>
       </c>
       <c r="I76" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>13.68</v>
+        <v>18.22</v>
       </c>
       <c r="K76" t="n">
-        <v>-106.16</v>
+        <v>70.8</v>
       </c>
       <c r="L76" t="n">
-        <v>107.04</v>
+        <v>73.11</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:47:11</t>
+          <t>08:00:35</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.81</v>
+        <v>4.58</v>
       </c>
       <c r="F77" t="n">
-        <v>10.69</v>
+        <v>11.6</v>
       </c>
       <c r="G77" t="n">
-        <v>263.9</v>
+        <v>281.7</v>
       </c>
       <c r="H77" t="n">
-        <v>42.3</v>
+        <v>61</v>
       </c>
       <c r="I77" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>78.38</v>
+        <v>-39.27</v>
       </c>
       <c r="K77" t="n">
-        <v>40.53</v>
+        <v>61.02</v>
       </c>
       <c r="L77" t="n">
-        <v>88.23999999999999</v>
+        <v>72.56</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:48:53</t>
+          <t>08:02:53</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.64</v>
+        <v>4.4</v>
       </c>
       <c r="F78" t="n">
-        <v>12.54</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G78" t="n">
         <v>279.1</v>
       </c>
       <c r="H78" t="n">
-        <v>47.3</v>
+        <v>76</v>
       </c>
       <c r="I78" t="n">
         <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>-157.75</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>-41.2</v>
+        <v>-73.8</v>
       </c>
       <c r="L78" t="n">
-        <v>163.04</v>
+        <v>118.98</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:50:27</t>
+          <t>08:04:42</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.29</v>
+        <v>4.4</v>
       </c>
       <c r="F79" t="n">
-        <v>11.09</v>
+        <v>11.28</v>
       </c>
       <c r="G79" t="n">
-        <v>279.9</v>
+        <v>287</v>
       </c>
       <c r="H79" t="n">
-        <v>46.5</v>
+        <v>21.1</v>
       </c>
       <c r="I79" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>-127.64</v>
+        <v>-72.19</v>
       </c>
       <c r="K79" t="n">
-        <v>-68.19</v>
+        <v>-74.3</v>
       </c>
       <c r="L79" t="n">
-        <v>144.71</v>
+        <v>103.6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:54:58</t>
+          <t>08:08:18</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>4.44</v>
+        <v>4.66</v>
       </c>
       <c r="F80" t="n">
-        <v>11.82</v>
+        <v>12.54</v>
       </c>
       <c r="G80" t="n">
-        <v>286.9</v>
+        <v>280.9</v>
       </c>
       <c r="H80" t="n">
-        <v>26.3</v>
+        <v>19.7</v>
       </c>
       <c r="I80" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J80" t="n">
-        <v>14.05</v>
+        <v>-22.46</v>
       </c>
       <c r="K80" t="n">
-        <v>162.42</v>
+        <v>-104.9</v>
       </c>
       <c r="L80" t="n">
-        <v>163.02</v>
+        <v>107.28</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07:55:43</t>
+          <t>08:10:06</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.34</v>
+        <v>4.63</v>
       </c>
       <c r="F81" t="n">
         <v>12.54</v>
       </c>
       <c r="G81" t="n">
-        <v>284.9</v>
+        <v>289.1</v>
       </c>
       <c r="H81" t="n">
-        <v>55.6</v>
+        <v>43.8</v>
       </c>
       <c r="I81" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>-200.09</v>
+        <v>-65.03</v>
       </c>
       <c r="K81" t="n">
-        <v>-99.14</v>
+        <v>-65.84999999999999</v>
       </c>
       <c r="L81" t="n">
-        <v>223.31</v>
+        <v>92.54000000000001</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07:56:44</t>
+          <t>08:10:56</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.41</v>
+        <v>4.02</v>
       </c>
       <c r="F82" t="n">
-        <v>10.91</v>
+        <v>11.26</v>
       </c>
       <c r="G82" t="n">
-        <v>288.1</v>
+        <v>281.3</v>
       </c>
       <c r="H82" t="n">
-        <v>52.3</v>
+        <v>45.8</v>
       </c>
       <c r="I82" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J82" t="n">
-        <v>200.29</v>
+        <v>108.92</v>
       </c>
       <c r="K82" t="n">
-        <v>-43.2</v>
+        <v>-91.78</v>
       </c>
       <c r="L82" t="n">
-        <v>204.9</v>
+        <v>142.43</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:02:38</t>
+          <t>08:15:42</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.47</v>
+        <v>5.16</v>
       </c>
       <c r="F83" t="n">
-        <v>11.06</v>
+        <v>12.54</v>
       </c>
       <c r="G83" t="n">
-        <v>270.2</v>
+        <v>285.6</v>
       </c>
       <c r="H83" t="n">
-        <v>57.2</v>
+        <v>51.7</v>
       </c>
       <c r="I83" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J83" t="n">
-        <v>76.56</v>
+        <v>-167.11</v>
       </c>
       <c r="K83" t="n">
-        <v>-121.76</v>
+        <v>-218.11</v>
       </c>
       <c r="L83" t="n">
-        <v>143.83</v>
+        <v>274.77</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:03:44</t>
+          <t>08:17:24</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.65</v>
+        <v>3.99</v>
       </c>
       <c r="F84" t="n">
-        <v>12.54</v>
+        <v>11.04</v>
       </c>
       <c r="G84" t="n">
-        <v>293.2</v>
+        <v>283.4</v>
       </c>
       <c r="H84" t="n">
-        <v>43.6</v>
+        <v>75.3</v>
       </c>
       <c r="I84" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J84" t="n">
-        <v>-129.95</v>
+        <v>184.25</v>
       </c>
       <c r="K84" t="n">
-        <v>249.08</v>
+        <v>96.92</v>
       </c>
       <c r="L84" t="n">
-        <v>280.94</v>
+        <v>208.18</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:06:00</t>
+          <t>08:18:42</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.7</v>
+        <v>4.32</v>
       </c>
       <c r="F85" t="n">
-        <v>12.54</v>
+        <v>12.5</v>
       </c>
       <c r="G85" t="n">
-        <v>299</v>
+        <v>279.6</v>
       </c>
       <c r="H85" t="n">
-        <v>52.8</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I85" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J85" t="n">
-        <v>-264.03</v>
+        <v>-22.25</v>
       </c>
       <c r="K85" t="n">
-        <v>355.2</v>
+        <v>-246.49</v>
       </c>
       <c r="L85" t="n">
-        <v>442.58</v>
+        <v>247.49</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:11:04</t>
+          <t>08:21:49</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.19</v>
+        <v>4.57</v>
       </c>
       <c r="F86" t="n">
-        <v>10.84</v>
+        <v>11.58</v>
       </c>
       <c r="G86" t="n">
-        <v>279.3</v>
+        <v>277.3</v>
       </c>
       <c r="H86" t="n">
-        <v>54.6</v>
+        <v>91</v>
       </c>
       <c r="I86" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>-24.9</v>
+        <v>-136.32</v>
       </c>
       <c r="K86" t="n">
-        <v>293.24</v>
+        <v>259.08</v>
       </c>
       <c r="L86" t="n">
-        <v>294.29</v>
+        <v>292.76</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:12:32</t>
+          <t>08:22:56</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.67</v>
+        <v>4.72</v>
       </c>
       <c r="F87" t="n">
         <v>12.54</v>
       </c>
       <c r="G87" t="n">
-        <v>287.2</v>
+        <v>276.8</v>
       </c>
       <c r="H87" t="n">
-        <v>42.1</v>
+        <v>40.3</v>
       </c>
       <c r="I87" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J87" t="n">
-        <v>264.89</v>
+        <v>262.24</v>
       </c>
       <c r="K87" t="n">
-        <v>-423.42</v>
+        <v>23.23</v>
       </c>
       <c r="L87" t="n">
-        <v>499.45</v>
+        <v>263.26</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:15:06</t>
+          <t>08:25:15</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.21</v>
+        <v>4.38</v>
       </c>
       <c r="F88" t="n">
-        <v>11.56</v>
+        <v>10.35</v>
       </c>
       <c r="G88" t="n">
-        <v>288</v>
+        <v>280.3</v>
       </c>
       <c r="H88" t="n">
-        <v>43.7</v>
+        <v>53.1</v>
       </c>
       <c r="I88" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J88" t="n">
-        <v>-349.01</v>
+        <v>277.95</v>
       </c>
       <c r="K88" t="n">
-        <v>99.84999999999999</v>
+        <v>33.62</v>
       </c>
       <c r="L88" t="n">
-        <v>363.02</v>
+        <v>279.97</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-06.xlsx
+++ b/output/2024-07-06.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-62.96</v>
+        <v>-67.27</v>
       </c>
       <c r="K14" t="n">
-        <v>24.11</v>
+        <v>25.76</v>
       </c>
       <c r="L14" t="n">
-        <v>67.42</v>
+        <v>72.03</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>28</v>
       </c>
       <c r="J15" t="n">
-        <v>-58.67</v>
+        <v>-61.72</v>
       </c>
       <c r="K15" t="n">
-        <v>-16.64</v>
+        <v>-17.51</v>
       </c>
       <c r="L15" t="n">
-        <v>60.98</v>
+        <v>64.16</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>-20.15</v>
+        <v>-19.53</v>
       </c>
       <c r="K16" t="n">
-        <v>102.78</v>
+        <v>99.62</v>
       </c>
       <c r="L16" t="n">
-        <v>104.74</v>
+        <v>101.52</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>28</v>
       </c>
       <c r="J17" t="n">
-        <v>45.94</v>
+        <v>49.04</v>
       </c>
       <c r="K17" t="n">
-        <v>47.66</v>
+        <v>50.87</v>
       </c>
       <c r="L17" t="n">
-        <v>66.19</v>
+        <v>70.66</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>15.8</v>
+        <v>18.45</v>
       </c>
       <c r="K18" t="n">
-        <v>-11.51</v>
+        <v>-13.44</v>
       </c>
       <c r="L18" t="n">
-        <v>19.54</v>
+        <v>22.83</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-87.17</v>
+        <v>-89.40000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>31.03</v>
+        <v>31.82</v>
       </c>
       <c r="L19" t="n">
-        <v>92.53</v>
+        <v>94.89</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>96.31999999999999</v>
+        <v>101.16</v>
       </c>
       <c r="K20" t="n">
-        <v>112.12</v>
+        <v>117.75</v>
       </c>
       <c r="L20" t="n">
-        <v>147.81</v>
+        <v>155.23</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>28</v>
       </c>
       <c r="J21" t="n">
-        <v>20.48</v>
+        <v>22.21</v>
       </c>
       <c r="K21" t="n">
-        <v>-98.84</v>
+        <v>-107.15</v>
       </c>
       <c r="L21" t="n">
-        <v>100.94</v>
+        <v>109.43</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>74.58</v>
+        <v>84.36</v>
       </c>
       <c r="K22" t="n">
-        <v>-61.72</v>
+        <v>-69.81999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>96.81</v>
+        <v>109.51</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>-30.72</v>
+        <v>-33.19</v>
       </c>
       <c r="K23" t="n">
-        <v>184.98</v>
+        <v>199.83</v>
       </c>
       <c r="L23" t="n">
-        <v>187.52</v>
+        <v>202.57</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.58</v>
+        <v>-2.95</v>
       </c>
       <c r="K24" t="n">
-        <v>150.93</v>
+        <v>172.88</v>
       </c>
       <c r="L24" t="n">
-        <v>150.95</v>
+        <v>172.91</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>69.94</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>111.71</v>
+        <v>127.66</v>
       </c>
       <c r="L25" t="n">
-        <v>131.8</v>
+        <v>150.62</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>179.08</v>
+        <v>220.11</v>
       </c>
       <c r="K26" t="n">
-        <v>95.66</v>
+        <v>117.58</v>
       </c>
       <c r="L26" t="n">
-        <v>203.03</v>
+        <v>249.55</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>-146.16</v>
+        <v>-189.06</v>
       </c>
       <c r="K27" t="n">
-        <v>19.06</v>
+        <v>24.66</v>
       </c>
       <c r="L27" t="n">
-        <v>147.4</v>
+        <v>190.66</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-196.05</v>
+        <v>-218.97</v>
       </c>
       <c r="K28" t="n">
-        <v>-196.23</v>
+        <v>-219.16</v>
       </c>
       <c r="L28" t="n">
-        <v>277.39</v>
+        <v>309.81</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>-4.83</v>
+        <v>-5.27</v>
       </c>
       <c r="K29" t="n">
-        <v>51.72</v>
+        <v>56.44</v>
       </c>
       <c r="L29" t="n">
-        <v>51.95</v>
+        <v>56.69</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-65.33</v>
+        <v>-70.17</v>
       </c>
       <c r="K30" t="n">
-        <v>4.35</v>
+        <v>4.67</v>
       </c>
       <c r="L30" t="n">
-        <v>65.47</v>
+        <v>70.31999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>27</v>
       </c>
       <c r="J31" t="n">
-        <v>64.17</v>
+        <v>67.03</v>
       </c>
       <c r="K31" t="n">
-        <v>-20.07</v>
+        <v>-20.96</v>
       </c>
       <c r="L31" t="n">
-        <v>67.23999999999999</v>
+        <v>70.23</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>28</v>
       </c>
       <c r="J32" t="n">
-        <v>58.4</v>
+        <v>64.31</v>
       </c>
       <c r="K32" t="n">
-        <v>27.62</v>
+        <v>30.41</v>
       </c>
       <c r="L32" t="n">
-        <v>64.59999999999999</v>
+        <v>71.13</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>28</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.99</v>
+        <v>-1.06</v>
       </c>
       <c r="K33" t="n">
-        <v>67.3</v>
+        <v>72.13</v>
       </c>
       <c r="L33" t="n">
-        <v>67.31</v>
+        <v>72.14</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>106.44</v>
+        <v>109.3</v>
       </c>
       <c r="K34" t="n">
-        <v>-37.08</v>
+        <v>-38.08</v>
       </c>
       <c r="L34" t="n">
-        <v>112.71</v>
+        <v>115.74</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>-90.22</v>
+        <v>-98.83</v>
       </c>
       <c r="K35" t="n">
-        <v>118.45</v>
+        <v>129.75</v>
       </c>
       <c r="L35" t="n">
-        <v>148.9</v>
+        <v>163.1</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>5.28</v>
+        <v>6.6</v>
       </c>
       <c r="K36" t="n">
-        <v>-34.24</v>
+        <v>-42.82</v>
       </c>
       <c r="L36" t="n">
-        <v>34.65</v>
+        <v>43.33</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>-46.88</v>
+        <v>-54.51</v>
       </c>
       <c r="K37" t="n">
-        <v>-83.06999999999999</v>
+        <v>-96.59</v>
       </c>
       <c r="L37" t="n">
-        <v>95.39</v>
+        <v>110.91</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>131.49</v>
+        <v>150.74</v>
       </c>
       <c r="K38" t="n">
-        <v>111.08</v>
+        <v>127.35</v>
       </c>
       <c r="L38" t="n">
-        <v>172.13</v>
+        <v>197.33</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>18.16</v>
+        <v>23.48</v>
       </c>
       <c r="K39" t="n">
-        <v>-102.14</v>
+        <v>-132.07</v>
       </c>
       <c r="L39" t="n">
-        <v>103.74</v>
+        <v>134.14</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>121.95</v>
+        <v>144.32</v>
       </c>
       <c r="K40" t="n">
-        <v>32.43</v>
+        <v>38.38</v>
       </c>
       <c r="L40" t="n">
-        <v>126.19</v>
+        <v>149.33</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>-169.7</v>
+        <v>-221.81</v>
       </c>
       <c r="K41" t="n">
-        <v>-125.36</v>
+        <v>-163.85</v>
       </c>
       <c r="L41" t="n">
-        <v>210.98</v>
+        <v>275.76</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>22</v>
       </c>
       <c r="J42" t="n">
-        <v>246.45</v>
+        <v>298.02</v>
       </c>
       <c r="K42" t="n">
-        <v>-20.58</v>
+        <v>-24.89</v>
       </c>
       <c r="L42" t="n">
-        <v>247.31</v>
+        <v>299.05</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>102.28</v>
+        <v>138.01</v>
       </c>
       <c r="K43" t="n">
-        <v>-177.4</v>
+        <v>-239.37</v>
       </c>
       <c r="L43" t="n">
-        <v>204.78</v>
+        <v>276.31</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>48.12</v>
+        <v>52.43</v>
       </c>
       <c r="K44" t="n">
-        <v>-44.71</v>
+        <v>-48.72</v>
       </c>
       <c r="L44" t="n">
-        <v>65.69</v>
+        <v>71.58</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>51.41</v>
+        <v>57.94</v>
       </c>
       <c r="K45" t="n">
-        <v>24.04</v>
+        <v>27.09</v>
       </c>
       <c r="L45" t="n">
-        <v>56.76</v>
+        <v>63.96</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>84.01000000000001</v>
+        <v>83.19</v>
       </c>
       <c r="K46" t="n">
-        <v>35.75</v>
+        <v>35.4</v>
       </c>
       <c r="L46" t="n">
-        <v>91.3</v>
+        <v>90.40000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>-58.84</v>
+        <v>-66.84</v>
       </c>
       <c r="K47" t="n">
-        <v>20.91</v>
+        <v>23.75</v>
       </c>
       <c r="L47" t="n">
-        <v>62.44</v>
+        <v>70.93000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>5.36</v>
+        <v>5.56</v>
       </c>
       <c r="K48" t="n">
-        <v>100.87</v>
+        <v>104.72</v>
       </c>
       <c r="L48" t="n">
-        <v>101.01</v>
+        <v>104.87</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>29.79</v>
+        <v>33.82</v>
       </c>
       <c r="K49" t="n">
-        <v>-55.84</v>
+        <v>-63.4</v>
       </c>
       <c r="L49" t="n">
-        <v>63.29</v>
+        <v>71.84999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>-128.35</v>
+        <v>-141.68</v>
       </c>
       <c r="K50" t="n">
-        <v>-47.92</v>
+        <v>-52.89</v>
       </c>
       <c r="L50" t="n">
-        <v>137.01</v>
+        <v>151.23</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-92.36</v>
+        <v>-116.4</v>
       </c>
       <c r="K51" t="n">
-        <v>33.26</v>
+        <v>41.92</v>
       </c>
       <c r="L51" t="n">
-        <v>98.17</v>
+        <v>123.72</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>28</v>
       </c>
       <c r="J52" t="n">
-        <v>44.64</v>
+        <v>51.09</v>
       </c>
       <c r="K52" t="n">
-        <v>98.64</v>
+        <v>112.88</v>
       </c>
       <c r="L52" t="n">
-        <v>108.27</v>
+        <v>123.9</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>-221.92</v>
+        <v>-238.11</v>
       </c>
       <c r="K53" t="n">
-        <v>-132.33</v>
+        <v>-141.98</v>
       </c>
       <c r="L53" t="n">
-        <v>258.38</v>
+        <v>277.22</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>27</v>
       </c>
       <c r="J54" t="n">
-        <v>131.89</v>
+        <v>154.68</v>
       </c>
       <c r="K54" t="n">
-        <v>-75.90000000000001</v>
+        <v>-89.02</v>
       </c>
       <c r="L54" t="n">
-        <v>152.17</v>
+        <v>178.47</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>-56.67</v>
+        <v>-73.73</v>
       </c>
       <c r="K55" t="n">
-        <v>100.43</v>
+        <v>130.67</v>
       </c>
       <c r="L55" t="n">
-        <v>115.32</v>
+        <v>150.04</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>87.25</v>
+        <v>106.98</v>
       </c>
       <c r="K56" t="n">
-        <v>196.66</v>
+        <v>241.14</v>
       </c>
       <c r="L56" t="n">
-        <v>215.15</v>
+        <v>263.8</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>-196.37</v>
+        <v>-243.76</v>
       </c>
       <c r="K57" t="n">
-        <v>-29.8</v>
+        <v>-36.99</v>
       </c>
       <c r="L57" t="n">
-        <v>198.62</v>
+        <v>246.55</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>157.63</v>
+        <v>202</v>
       </c>
       <c r="K58" t="n">
-        <v>-198.73</v>
+        <v>-254.67</v>
       </c>
       <c r="L58" t="n">
-        <v>253.66</v>
+        <v>325.06</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>84.8</v>
+        <v>87.13</v>
       </c>
       <c r="K59" t="n">
-        <v>4.37</v>
+        <v>4.49</v>
       </c>
       <c r="L59" t="n">
-        <v>84.92</v>
+        <v>87.25</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>63.43</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="K60" t="n">
-        <v>25.12</v>
+        <v>26.15</v>
       </c>
       <c r="L60" t="n">
-        <v>68.23</v>
+        <v>71.03</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>61.69</v>
+        <v>65.17</v>
       </c>
       <c r="K61" t="n">
-        <v>39.36</v>
+        <v>41.58</v>
       </c>
       <c r="L61" t="n">
-        <v>73.17</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>55.46</v>
+        <v>59.34</v>
       </c>
       <c r="K62" t="n">
-        <v>-44.03</v>
+        <v>-47.12</v>
       </c>
       <c r="L62" t="n">
-        <v>70.81</v>
+        <v>75.77</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>-16.42</v>
+        <v>-19.49</v>
       </c>
       <c r="K63" t="n">
-        <v>49.29</v>
+        <v>58.51</v>
       </c>
       <c r="L63" t="n">
-        <v>51.95</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>98.42</v>
+        <v>99.44</v>
       </c>
       <c r="K64" t="n">
-        <v>-34.24</v>
+        <v>-34.6</v>
       </c>
       <c r="L64" t="n">
-        <v>104.21</v>
+        <v>105.28</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>-94.23</v>
+        <v>-108.71</v>
       </c>
       <c r="K65" t="n">
-        <v>-52.42</v>
+        <v>-60.48</v>
       </c>
       <c r="L65" t="n">
-        <v>107.83</v>
+        <v>124.4</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>114.5</v>
+        <v>131.4</v>
       </c>
       <c r="K66" t="n">
-        <v>-22.92</v>
+        <v>-26.31</v>
       </c>
       <c r="L66" t="n">
-        <v>116.77</v>
+        <v>134.01</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>-101.49</v>
+        <v>-106.11</v>
       </c>
       <c r="K67" t="n">
-        <v>-134.18</v>
+        <v>-140.29</v>
       </c>
       <c r="L67" t="n">
-        <v>168.24</v>
+        <v>175.9</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>195.78</v>
+        <v>237.38</v>
       </c>
       <c r="K68" t="n">
-        <v>-77.44</v>
+        <v>-93.90000000000001</v>
       </c>
       <c r="L68" t="n">
-        <v>210.54</v>
+        <v>255.27</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>-141.28</v>
+        <v>-176.06</v>
       </c>
       <c r="K69" t="n">
-        <v>52.28</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="L69" t="n">
-        <v>150.64</v>
+        <v>187.73</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>83.23</v>
+        <v>87.14</v>
       </c>
       <c r="K70" t="n">
-        <v>-307.57</v>
+        <v>-322.02</v>
       </c>
       <c r="L70" t="n">
-        <v>318.63</v>
+        <v>333.6</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>175.9</v>
+        <v>237.41</v>
       </c>
       <c r="K71" t="n">
-        <v>199.86</v>
+        <v>269.75</v>
       </c>
       <c r="L71" t="n">
-        <v>266.24</v>
+        <v>359.35</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>264.39</v>
+        <v>319.51</v>
       </c>
       <c r="K72" t="n">
-        <v>176.97</v>
+        <v>213.87</v>
       </c>
       <c r="L72" t="n">
-        <v>318.15</v>
+        <v>384.48</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-211.12</v>
+        <v>-265.44</v>
       </c>
       <c r="K73" t="n">
-        <v>-52.53</v>
+        <v>-66.05</v>
       </c>
       <c r="L73" t="n">
-        <v>217.56</v>
+        <v>273.54</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>-43.88</v>
+        <v>-44.61</v>
       </c>
       <c r="K74" t="n">
-        <v>-70.75</v>
+        <v>-71.93000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>83.25</v>
+        <v>84.64</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>103.64</v>
+        <v>99.48</v>
       </c>
       <c r="K75" t="n">
-        <v>-58.9</v>
+        <v>-56.54</v>
       </c>
       <c r="L75" t="n">
-        <v>119.21</v>
+        <v>114.42</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>-42.22</v>
+        <v>-45.9</v>
       </c>
       <c r="K76" t="n">
-        <v>-31.54</v>
+        <v>-34.29</v>
       </c>
       <c r="L76" t="n">
-        <v>52.7</v>
+        <v>57.29</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-57.49</v>
+        <v>-61.24</v>
       </c>
       <c r="K77" t="n">
-        <v>-66.43000000000001</v>
+        <v>-70.76000000000001</v>
       </c>
       <c r="L77" t="n">
-        <v>87.84999999999999</v>
+        <v>93.58</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>28</v>
       </c>
       <c r="J78" t="n">
-        <v>58.06</v>
+        <v>57.2</v>
       </c>
       <c r="K78" t="n">
-        <v>-95.52</v>
+        <v>-94.12</v>
       </c>
       <c r="L78" t="n">
-        <v>111.78</v>
+        <v>110.14</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>92.44</v>
+        <v>96.17</v>
       </c>
       <c r="K79" t="n">
-        <v>-5.08</v>
+        <v>-5.29</v>
       </c>
       <c r="L79" t="n">
-        <v>92.58</v>
+        <v>96.31</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>145.22</v>
+        <v>169.07</v>
       </c>
       <c r="K80" t="n">
-        <v>18.57</v>
+        <v>21.62</v>
       </c>
       <c r="L80" t="n">
-        <v>146.41</v>
+        <v>170.45</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>55.44</v>
+        <v>62.66</v>
       </c>
       <c r="K81" t="n">
-        <v>-97.15000000000001</v>
+        <v>-109.81</v>
       </c>
       <c r="L81" t="n">
-        <v>111.86</v>
+        <v>126.43</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-125.2</v>
+        <v>-139.75</v>
       </c>
       <c r="K82" t="n">
-        <v>55.65</v>
+        <v>62.12</v>
       </c>
       <c r="L82" t="n">
-        <v>137.01</v>
+        <v>152.93</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>73.59999999999999</v>
+        <v>88.41</v>
       </c>
       <c r="K83" t="n">
-        <v>-178.6</v>
+        <v>-214.54</v>
       </c>
       <c r="L83" t="n">
-        <v>193.17</v>
+        <v>232.05</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>-21.21</v>
+        <v>-27.69</v>
       </c>
       <c r="K84" t="n">
-        <v>-114.1</v>
+        <v>-148.97</v>
       </c>
       <c r="L84" t="n">
-        <v>116.06</v>
+        <v>151.52</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>1.54</v>
+        <v>1.98</v>
       </c>
       <c r="K85" t="n">
-        <v>201.57</v>
+        <v>259.7</v>
       </c>
       <c r="L85" t="n">
-        <v>201.58</v>
+        <v>259.71</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>122.89</v>
+        <v>165.4</v>
       </c>
       <c r="K86" t="n">
-        <v>-182.99</v>
+        <v>-246.3</v>
       </c>
       <c r="L86" t="n">
-        <v>220.42</v>
+        <v>296.68</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>233.94</v>
+        <v>301.65</v>
       </c>
       <c r="K87" t="n">
-        <v>172.57</v>
+        <v>222.51</v>
       </c>
       <c r="L87" t="n">
-        <v>290.71</v>
+        <v>374.84</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>158.17</v>
+        <v>180.7</v>
       </c>
       <c r="K88" t="n">
-        <v>242</v>
+        <v>276.47</v>
       </c>
       <c r="L88" t="n">
-        <v>289.1</v>
+        <v>330.29</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-06.xlsx
+++ b/output/2024-07-06.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-67.27</v>
+        <v>-74.31999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>25.76</v>
+        <v>28.47</v>
       </c>
       <c r="L14" t="n">
-        <v>72.03</v>
+        <v>79.58</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>28</v>
       </c>
       <c r="J15" t="n">
-        <v>-61.72</v>
+        <v>-70.43000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>-17.51</v>
+        <v>-19.98</v>
       </c>
       <c r="L15" t="n">
-        <v>64.16</v>
+        <v>73.20999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>-19.53</v>
+        <v>-24.23</v>
       </c>
       <c r="K16" t="n">
-        <v>99.62</v>
+        <v>123.62</v>
       </c>
       <c r="L16" t="n">
-        <v>101.52</v>
+        <v>125.97</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>28</v>
       </c>
       <c r="J17" t="n">
-        <v>49.04</v>
+        <v>52.33</v>
       </c>
       <c r="K17" t="n">
-        <v>50.87</v>
+        <v>54.28</v>
       </c>
       <c r="L17" t="n">
-        <v>70.66</v>
+        <v>75.40000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>18.45</v>
+        <v>21.13</v>
       </c>
       <c r="K18" t="n">
-        <v>-13.44</v>
+        <v>-15.4</v>
       </c>
       <c r="L18" t="n">
-        <v>22.83</v>
+        <v>26.14</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-89.40000000000001</v>
+        <v>-93</v>
       </c>
       <c r="K19" t="n">
-        <v>31.82</v>
+        <v>33.1</v>
       </c>
       <c r="L19" t="n">
-        <v>94.89</v>
+        <v>98.70999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1270,13 +1270,13 @@
         <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>-5.27</v>
+        <v>-5.58</v>
       </c>
       <c r="K29" t="n">
-        <v>56.44</v>
+        <v>59.74</v>
       </c>
       <c r="L29" t="n">
-        <v>56.69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-70.17</v>
+        <v>-89.40000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>4.67</v>
+        <v>5.95</v>
       </c>
       <c r="L30" t="n">
-        <v>70.31999999999999</v>
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>27</v>
       </c>
       <c r="J31" t="n">
-        <v>67.03</v>
+        <v>94.77</v>
       </c>
       <c r="K31" t="n">
-        <v>-20.96</v>
+        <v>-29.63</v>
       </c>
       <c r="L31" t="n">
-        <v>70.23</v>
+        <v>99.3</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>28</v>
       </c>
       <c r="J32" t="n">
-        <v>64.31</v>
+        <v>72.19</v>
       </c>
       <c r="K32" t="n">
-        <v>30.41</v>
+        <v>34.14</v>
       </c>
       <c r="L32" t="n">
-        <v>71.13</v>
+        <v>79.86</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>28</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.06</v>
+        <v>-1.1</v>
       </c>
       <c r="K33" t="n">
-        <v>72.13</v>
+        <v>75.25</v>
       </c>
       <c r="L33" t="n">
-        <v>72.14</v>
+        <v>75.25</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>109.3</v>
+        <v>140.96</v>
       </c>
       <c r="K34" t="n">
-        <v>-38.08</v>
+        <v>-49.11</v>
       </c>
       <c r="L34" t="n">
-        <v>115.74</v>
+        <v>149.27</v>
       </c>
     </row>
     <row r="35">
@@ -1900,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>52.43</v>
+        <v>66</v>
       </c>
       <c r="K44" t="n">
-        <v>-48.72</v>
+        <v>-61.33</v>
       </c>
       <c r="L44" t="n">
-        <v>71.58</v>
+        <v>90.09</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>57.94</v>
+        <v>69.16</v>
       </c>
       <c r="K45" t="n">
-        <v>27.09</v>
+        <v>32.33</v>
       </c>
       <c r="L45" t="n">
-        <v>63.96</v>
+        <v>76.34</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>83.19</v>
+        <v>102.17</v>
       </c>
       <c r="K46" t="n">
-        <v>35.4</v>
+        <v>43.48</v>
       </c>
       <c r="L46" t="n">
-        <v>90.40000000000001</v>
+        <v>111.04</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>-66.84</v>
+        <v>-74.13</v>
       </c>
       <c r="K47" t="n">
-        <v>23.75</v>
+        <v>26.34</v>
       </c>
       <c r="L47" t="n">
-        <v>70.93000000000001</v>
+        <v>78.67</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>5.56</v>
+        <v>6.64</v>
       </c>
       <c r="K48" t="n">
-        <v>104.72</v>
+        <v>125.04</v>
       </c>
       <c r="L48" t="n">
-        <v>104.87</v>
+        <v>125.21</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>33.82</v>
+        <v>40</v>
       </c>
       <c r="K49" t="n">
-        <v>-63.4</v>
+        <v>-75</v>
       </c>
       <c r="L49" t="n">
-        <v>71.84999999999999</v>
+        <v>85</v>
       </c>
     </row>
     <row r="50">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>87.13</v>
+        <v>110.34</v>
       </c>
       <c r="K59" t="n">
-        <v>4.49</v>
+        <v>5.68</v>
       </c>
       <c r="L59" t="n">
-        <v>87.25</v>
+        <v>110.49</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>66.04000000000001</v>
+        <v>90.11</v>
       </c>
       <c r="K60" t="n">
-        <v>26.15</v>
+        <v>35.68</v>
       </c>
       <c r="L60" t="n">
-        <v>71.03</v>
+        <v>96.92</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>65.17</v>
+        <v>92.86</v>
       </c>
       <c r="K61" t="n">
-        <v>41.58</v>
+        <v>59.25</v>
       </c>
       <c r="L61" t="n">
-        <v>77.3</v>
+        <v>110.15</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>59.34</v>
+        <v>64.84</v>
       </c>
       <c r="K62" t="n">
-        <v>-47.12</v>
+        <v>-51.48</v>
       </c>
       <c r="L62" t="n">
-        <v>75.77</v>
+        <v>82.78</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>-19.49</v>
+        <v>-23.28</v>
       </c>
       <c r="K63" t="n">
-        <v>58.51</v>
+        <v>69.86</v>
       </c>
       <c r="L63" t="n">
-        <v>61.67</v>
+        <v>73.63</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>99.44</v>
+        <v>113.01</v>
       </c>
       <c r="K64" t="n">
-        <v>-34.6</v>
+        <v>-39.32</v>
       </c>
       <c r="L64" t="n">
-        <v>105.28</v>
+        <v>119.65</v>
       </c>
     </row>
     <row r="65">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>-44.61</v>
+        <v>-55.35</v>
       </c>
       <c r="K74" t="n">
-        <v>-71.93000000000001</v>
+        <v>-89.26000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>84.64</v>
+        <v>105.03</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>99.48</v>
+        <v>132.78</v>
       </c>
       <c r="K75" t="n">
-        <v>-56.54</v>
+        <v>-75.45999999999999</v>
       </c>
       <c r="L75" t="n">
-        <v>114.42</v>
+        <v>152.72</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>-45.9</v>
+        <v>-51.32</v>
       </c>
       <c r="K76" t="n">
-        <v>-34.29</v>
+        <v>-38.34</v>
       </c>
       <c r="L76" t="n">
-        <v>57.29</v>
+        <v>64.06999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-61.24</v>
+        <v>-74.14</v>
       </c>
       <c r="K77" t="n">
-        <v>-70.76000000000001</v>
+        <v>-85.67</v>
       </c>
       <c r="L77" t="n">
-        <v>93.58</v>
+        <v>113.3</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>28</v>
       </c>
       <c r="J78" t="n">
-        <v>57.2</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>-94.12</v>
+        <v>-117.17</v>
       </c>
       <c r="L78" t="n">
-        <v>110.14</v>
+        <v>137.11</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>96.17</v>
+        <v>124.79</v>
       </c>
       <c r="K79" t="n">
-        <v>-5.29</v>
+        <v>-6.86</v>
       </c>
       <c r="L79" t="n">
-        <v>96.31</v>
+        <v>124.98</v>
       </c>
     </row>
     <row r="80">
